--- a/3k2s/Экономика IT-компании/Лабораторная работа 1 ОС_с.xlsx
+++ b/3k2s/Экономика IT-компании/Лабораторная работа 1 ОС_с.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Институт\Экономика ERP\Лабораторные работы студенты\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\УЧЁБА\3 курс\экономика\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F936256F-099B-4C3A-88E9-26BE47C4AE06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20633" windowHeight="7598" firstSheet="6" activeTab="6"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Задание 1 исх. данные, решение" sheetId="1" r:id="rId1"/>
@@ -21,10 +22,19 @@
     <sheet name="Задание 4 исх данные, решение" sheetId="9" r:id="rId7"/>
     <sheet name="Задание 4 порядок работы" sheetId="10" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -717,7 +727,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="[$-419]d\ mmm;@"/>
@@ -969,7 +979,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -990,6 +1000,12 @@
     </fill>
     <fill>
       <patternFill patternType="lightUp"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="5">
@@ -1054,7 +1070,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1071,7 +1087,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1111,7 +1127,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1164,10 +1180,8 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1176,11 +1190,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1192,10 +1202,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="8" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1493,19 +1504,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P111"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.5" customWidth="1"/>
-    <col min="3" max="3" width="12.19921875" customWidth="1"/>
-    <col min="5" max="5" width="10.796875" customWidth="1"/>
-    <col min="6" max="6" width="9.8984375" customWidth="1"/>
-    <col min="8" max="8" width="10.796875" customWidth="1"/>
-    <col min="16" max="16" width="9.8984375" customWidth="1"/>
+    <col min="1" max="1" width="28.44140625" customWidth="1"/>
+    <col min="3" max="3" width="12.21875" customWidth="1"/>
+    <col min="5" max="5" width="10.77734375" customWidth="1"/>
+    <col min="6" max="6" width="9.88671875" customWidth="1"/>
+    <col min="8" max="8" width="10.77734375" customWidth="1"/>
+    <col min="16" max="16" width="9.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>28</v>
       </c>
@@ -1525,72 +1536,72 @@
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="67" t="s">
+      <c r="A3" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="67" t="s">
+      <c r="B3" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="67" t="s">
+      <c r="C3" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="67" t="s">
+      <c r="D3" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="67" t="s">
+      <c r="E3" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="67" t="s">
+      <c r="F3" s="64" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="67" t="s">
+      <c r="G3" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="67" t="s">
+      <c r="H3" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="67" t="s">
+      <c r="I3" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="67" t="s">
+      <c r="J3" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="67" t="s">
+      <c r="K3" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="L3" s="67" t="s">
+      <c r="L3" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="67" t="s">
+      <c r="M3" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="N3" s="67" t="s">
+      <c r="N3" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="O3" s="67" t="s">
+      <c r="O3" s="64" t="s">
         <v>14</v>
       </c>
-      <c r="P3" s="67" t="s">
+      <c r="P3" s="64" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="40.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="68"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="68"/>
-      <c r="L4" s="68"/>
-      <c r="M4" s="68"/>
-      <c r="N4" s="68"/>
-      <c r="O4" s="68"/>
-      <c r="P4" s="68"/>
+    <row r="4" spans="1:16" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="65"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="65"/>
+      <c r="D4" s="65"/>
+      <c r="E4" s="65"/>
+      <c r="F4" s="65"/>
+      <c r="G4" s="65"/>
+      <c r="H4" s="65"/>
+      <c r="I4" s="65"/>
+      <c r="J4" s="65"/>
+      <c r="K4" s="65"/>
+      <c r="L4" s="65"/>
+      <c r="M4" s="65"/>
+      <c r="N4" s="65"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="65"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
@@ -1605,18 +1616,34 @@
       <c r="D5" s="13">
         <v>0</v>
       </c>
-      <c r="E5" s="12"/>
+      <c r="E5" s="12">
+        <v>0</v>
+      </c>
       <c r="F5" s="13">
         <v>24</v>
       </c>
       <c r="G5" s="14">
         <v>44986</v>
       </c>
-      <c r="H5" s="12"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="12"/>
+      <c r="H5" s="12">
+        <v>2</v>
+      </c>
+      <c r="I5" s="15">
+        <f>B5/B12*100</f>
+        <v>55.209260908281387</v>
+      </c>
+      <c r="J5" s="12">
+        <f>B5+C5-F5</f>
+        <v>3076</v>
+      </c>
+      <c r="K5" s="15">
+        <f>J5/J12*100</f>
+        <v>55.214503679770246</v>
+      </c>
+      <c r="L5" s="12">
+        <f>B5+C5*(E5/12)-F5*((12-H5)/12)</f>
+        <v>3080</v>
+      </c>
       <c r="M5" s="16"/>
       <c r="N5" s="16"/>
       <c r="O5" s="16"/>
@@ -1635,25 +1662,41 @@
       <c r="D6" s="14">
         <v>44958</v>
       </c>
-      <c r="E6" s="12"/>
+      <c r="E6" s="12">
+        <v>11</v>
+      </c>
       <c r="F6" s="13">
         <v>5</v>
       </c>
       <c r="G6" s="14">
         <v>45017</v>
       </c>
-      <c r="H6" s="12"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="12"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="12"/>
+      <c r="H6" s="12">
+        <v>3</v>
+      </c>
+      <c r="I6" s="15">
+        <f>B6/B12*100</f>
+        <v>3.5618878005342829</v>
+      </c>
+      <c r="J6" s="12">
+        <f t="shared" ref="J6:J11" si="0">B6+C6-F6</f>
+        <v>200</v>
+      </c>
+      <c r="K6" s="15">
+        <f>J6/J12*100</f>
+        <v>3.5900197451085982</v>
+      </c>
+      <c r="L6" s="12">
+        <f t="shared" ref="L6:L11" si="1">B6+C6*(E6/12)-F6*((12-H6)/12)</f>
+        <v>200.83333333333334</v>
+      </c>
       <c r="M6" s="16"/>
       <c r="N6" s="16"/>
       <c r="O6" s="16"/>
       <c r="P6" s="16"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="62" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="12">
@@ -1665,25 +1708,41 @@
       <c r="D7" s="14">
         <v>45047</v>
       </c>
-      <c r="E7" s="12"/>
+      <c r="E7" s="12">
+        <v>8</v>
+      </c>
       <c r="F7" s="13">
         <v>16</v>
       </c>
       <c r="G7" s="14">
         <v>45139</v>
       </c>
-      <c r="H7" s="12"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="12"/>
+      <c r="H7" s="12">
+        <v>7</v>
+      </c>
+      <c r="I7" s="15">
+        <f>B7/B12*100</f>
+        <v>17.097061442564559</v>
+      </c>
+      <c r="J7" s="12">
+        <f t="shared" si="0"/>
+        <v>960</v>
+      </c>
+      <c r="K7" s="15">
+        <f>J7/J12*100</f>
+        <v>17.232094776521269</v>
+      </c>
+      <c r="L7" s="63">
+        <f t="shared" si="1"/>
+        <v>964</v>
+      </c>
       <c r="M7" s="16"/>
       <c r="N7" s="16"/>
       <c r="O7" s="16"/>
       <c r="P7" s="16"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="62" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="12">
@@ -1695,18 +1754,34 @@
       <c r="D8" s="14">
         <v>45139</v>
       </c>
-      <c r="E8" s="12"/>
+      <c r="E8" s="12">
+        <v>5</v>
+      </c>
       <c r="F8" s="13">
         <v>17</v>
       </c>
       <c r="G8" s="14">
         <v>45170</v>
       </c>
-      <c r="H8" s="12"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="12"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="12"/>
+      <c r="H8" s="12">
+        <v>8</v>
+      </c>
+      <c r="I8" s="15">
+        <f>B8/B12*100</f>
+        <v>4.2742653606411398</v>
+      </c>
+      <c r="J8" s="12">
+        <f t="shared" si="0"/>
+        <v>233</v>
+      </c>
+      <c r="K8" s="15">
+        <f>J8/J12*100</f>
+        <v>4.1823730030515174</v>
+      </c>
+      <c r="L8" s="63">
+        <f t="shared" si="1"/>
+        <v>238.5</v>
+      </c>
       <c r="M8" s="16"/>
       <c r="N8" s="16"/>
       <c r="O8" s="16"/>
@@ -1725,25 +1800,41 @@
       <c r="D9" s="14">
         <v>45108</v>
       </c>
-      <c r="E9" s="12"/>
+      <c r="E9" s="12">
+        <v>6</v>
+      </c>
       <c r="F9" s="13">
         <v>11</v>
       </c>
       <c r="G9" s="14">
         <v>44958</v>
       </c>
-      <c r="H9" s="12"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="12"/>
-      <c r="K9" s="15"/>
-      <c r="L9" s="12"/>
+      <c r="H9" s="12">
+        <v>1</v>
+      </c>
+      <c r="I9" s="15">
+        <f>B9/B12*100</f>
+        <v>7.1237756010685658</v>
+      </c>
+      <c r="J9" s="12">
+        <f t="shared" si="0"/>
+        <v>401</v>
+      </c>
+      <c r="K9" s="15">
+        <f>J9/J12*100</f>
+        <v>7.1979895889427397</v>
+      </c>
+      <c r="L9" s="12">
+        <f t="shared" si="1"/>
+        <v>395.91666666666669</v>
+      </c>
       <c r="M9" s="16"/>
       <c r="N9" s="16"/>
       <c r="O9" s="16"/>
       <c r="P9" s="16"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="62" t="s">
         <v>21</v>
       </c>
       <c r="B10" s="12">
@@ -1755,18 +1846,34 @@
       <c r="D10" s="14">
         <v>45200</v>
       </c>
-      <c r="E10" s="12"/>
+      <c r="E10" s="12">
+        <v>3</v>
+      </c>
       <c r="F10" s="13">
         <v>9</v>
       </c>
       <c r="G10" s="14">
         <v>45047</v>
       </c>
-      <c r="H10" s="12"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="15"/>
-      <c r="L10" s="12"/>
+      <c r="H10" s="12">
+        <v>4</v>
+      </c>
+      <c r="I10" s="15">
+        <f>B10/B12*100</f>
+        <v>11.041852181656278</v>
+      </c>
+      <c r="J10" s="12">
+        <f t="shared" si="0"/>
+        <v>614</v>
+      </c>
+      <c r="K10" s="15">
+        <f>J10/J12*100</f>
+        <v>11.021360617483396</v>
+      </c>
+      <c r="L10" s="63">
+        <f t="shared" si="1"/>
+        <v>614.75</v>
+      </c>
       <c r="M10" s="16"/>
       <c r="N10" s="16"/>
       <c r="O10" s="16"/>
@@ -1785,18 +1892,34 @@
       <c r="D11" s="14">
         <v>45170</v>
       </c>
-      <c r="E11" s="12"/>
+      <c r="E11" s="12">
+        <v>4</v>
+      </c>
       <c r="F11" s="13">
         <v>8</v>
       </c>
       <c r="G11" s="14">
         <v>45231</v>
       </c>
-      <c r="H11" s="12"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="12"/>
+      <c r="H11" s="12">
+        <v>10</v>
+      </c>
+      <c r="I11" s="15">
+        <f>B11/B12*100</f>
+        <v>1.6918967052537845</v>
+      </c>
+      <c r="J11" s="12">
+        <f t="shared" si="0"/>
+        <v>87</v>
+      </c>
+      <c r="K11" s="15">
+        <f>J11/J12*100</f>
+        <v>1.5616585891222401</v>
+      </c>
+      <c r="L11" s="12">
+        <f t="shared" si="1"/>
+        <v>93.666666666666671</v>
+      </c>
       <c r="M11" s="16"/>
       <c r="N11" s="16"/>
       <c r="O11" s="16"/>
@@ -1806,94 +1929,127 @@
       <c r="A12" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
+      <c r="B12" s="18">
+        <f>SUM(B5:B11)</f>
+        <v>5615</v>
+      </c>
+      <c r="C12" s="18">
+        <f>SUM(C5:C11)</f>
+        <v>46</v>
+      </c>
       <c r="D12" s="16"/>
       <c r="E12" s="16"/>
-      <c r="F12" s="18"/>
+      <c r="F12" s="18">
+        <f>SUM(F5:F11)</f>
+        <v>90</v>
+      </c>
       <c r="G12" s="16"/>
       <c r="H12" s="16"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="18"/>
-      <c r="L12" s="18"/>
-      <c r="M12" s="20"/>
-      <c r="N12" s="20"/>
-      <c r="O12" s="19"/>
-      <c r="P12" s="19"/>
+      <c r="I12" s="19">
+        <f>SUM(I5:I11)</f>
+        <v>100</v>
+      </c>
+      <c r="J12" s="18">
+        <f>SUM(J5:J11)</f>
+        <v>5571</v>
+      </c>
+      <c r="K12" s="18">
+        <f>SUM(K5:K11)</f>
+        <v>100.00000000000001</v>
+      </c>
+      <c r="L12" s="18">
+        <f>SUM(L5:L11)</f>
+        <v>5587.6666666666679</v>
+      </c>
+      <c r="M12" s="20">
+        <f>C12/J12</f>
+        <v>8.2570454137497751E-3</v>
+      </c>
+      <c r="N12" s="20">
+        <f>F12/B12</f>
+        <v>1.6028495102404273E-2</v>
+      </c>
+      <c r="O12" s="19">
+        <f>(SUM(L7:L8,L10))/L12*100</f>
+        <v>32.522519835351659</v>
+      </c>
+      <c r="P12" s="19">
+        <f>(SUM(L5:L6,L9,L11))/L12*100</f>
+        <v>67.477480164648313</v>
+      </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="67" t="s">
+    <row r="14" spans="1:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="67" t="s">
+      <c r="B14" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="C14" s="67" t="s">
+      <c r="C14" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="67" t="s">
+      <c r="D14" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="67" t="s">
+      <c r="E14" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="67" t="s">
+      <c r="F14" s="64" t="s">
         <v>35</v>
       </c>
-      <c r="G14" s="67" t="s">
+      <c r="G14" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="H14" s="67" t="s">
+      <c r="H14" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="I14" s="67" t="s">
+      <c r="I14" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="67" t="s">
+      <c r="J14" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="K14" s="67" t="s">
+      <c r="K14" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="L14" s="67" t="s">
+      <c r="L14" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="M14" s="67" t="s">
+      <c r="M14" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="N14" s="67" t="s">
+      <c r="N14" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="O14" s="67" t="s">
+      <c r="O14" s="64" t="s">
         <v>14</v>
       </c>
-      <c r="P14" s="67" t="s">
+      <c r="P14" s="64" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="35.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="68"/>
-      <c r="B15" s="68"/>
-      <c r="C15" s="68"/>
-      <c r="D15" s="68"/>
-      <c r="E15" s="68"/>
-      <c r="F15" s="68"/>
-      <c r="G15" s="68"/>
-      <c r="H15" s="68"/>
-      <c r="I15" s="68"/>
-      <c r="J15" s="68"/>
-      <c r="K15" s="68"/>
-      <c r="L15" s="68"/>
-      <c r="M15" s="68"/>
-      <c r="N15" s="68"/>
-      <c r="O15" s="68"/>
-      <c r="P15" s="68"/>
+    <row r="15" spans="1:16" ht="35.549999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="65"/>
+      <c r="B15" s="65"/>
+      <c r="C15" s="65"/>
+      <c r="D15" s="65"/>
+      <c r="E15" s="65"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="65"/>
+      <c r="H15" s="65"/>
+      <c r="I15" s="65"/>
+      <c r="J15" s="65"/>
+      <c r="K15" s="65"/>
+      <c r="L15" s="65"/>
+      <c r="M15" s="65"/>
+      <c r="N15" s="65"/>
+      <c r="O15" s="65"/>
+      <c r="P15" s="65"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
@@ -2130,73 +2286,73 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="67" t="s">
+    <row r="25" spans="1:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="B25" s="67" t="s">
+      <c r="B25" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="C25" s="67" t="s">
+      <c r="C25" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="67" t="s">
+      <c r="D25" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="E25" s="67" t="s">
+      <c r="E25" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="F25" s="67" t="s">
+      <c r="F25" s="64" t="s">
         <v>35</v>
       </c>
-      <c r="G25" s="67" t="s">
+      <c r="G25" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="H25" s="67" t="s">
+      <c r="H25" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="I25" s="67" t="s">
+      <c r="I25" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="J25" s="67" t="s">
+      <c r="J25" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="K25" s="67" t="s">
+      <c r="K25" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="L25" s="67" t="s">
+      <c r="L25" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="M25" s="67" t="s">
+      <c r="M25" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="N25" s="67" t="s">
+      <c r="N25" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="O25" s="67" t="s">
+      <c r="O25" s="64" t="s">
         <v>14</v>
       </c>
-      <c r="P25" s="67" t="s">
+      <c r="P25" s="64" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="68"/>
-      <c r="B26" s="68"/>
-      <c r="C26" s="68"/>
-      <c r="D26" s="68"/>
-      <c r="E26" s="68"/>
-      <c r="F26" s="68"/>
-      <c r="G26" s="68"/>
-      <c r="H26" s="68"/>
-      <c r="I26" s="68"/>
-      <c r="J26" s="68"/>
-      <c r="K26" s="68"/>
-      <c r="L26" s="68"/>
-      <c r="M26" s="68"/>
-      <c r="N26" s="68"/>
-      <c r="O26" s="68"/>
-      <c r="P26" s="68"/>
+      <c r="A26" s="65"/>
+      <c r="B26" s="65"/>
+      <c r="C26" s="65"/>
+      <c r="D26" s="65"/>
+      <c r="E26" s="65"/>
+      <c r="F26" s="65"/>
+      <c r="G26" s="65"/>
+      <c r="H26" s="65"/>
+      <c r="I26" s="65"/>
+      <c r="J26" s="65"/>
+      <c r="K26" s="65"/>
+      <c r="L26" s="65"/>
+      <c r="M26" s="65"/>
+      <c r="N26" s="65"/>
+      <c r="O26" s="65"/>
+      <c r="P26" s="65"/>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
@@ -2433,73 +2589,73 @@
         <v>26</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="67" t="s">
+    <row r="36" spans="1:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="B36" s="67" t="s">
+      <c r="B36" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="C36" s="67" t="s">
+      <c r="C36" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="D36" s="67" t="s">
+      <c r="D36" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="E36" s="67" t="s">
+      <c r="E36" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="F36" s="67" t="s">
+      <c r="F36" s="64" t="s">
         <v>35</v>
       </c>
-      <c r="G36" s="67" t="s">
+      <c r="G36" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="H36" s="67" t="s">
+      <c r="H36" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="I36" s="67" t="s">
+      <c r="I36" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="J36" s="67" t="s">
+      <c r="J36" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="K36" s="67" t="s">
+      <c r="K36" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="L36" s="67" t="s">
+      <c r="L36" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="M36" s="67" t="s">
+      <c r="M36" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="N36" s="67" t="s">
+      <c r="N36" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="O36" s="67" t="s">
+      <c r="O36" s="64" t="s">
         <v>14</v>
       </c>
-      <c r="P36" s="67" t="s">
+      <c r="P36" s="64" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="68"/>
-      <c r="B37" s="68"/>
-      <c r="C37" s="68"/>
-      <c r="D37" s="68"/>
-      <c r="E37" s="68"/>
-      <c r="F37" s="68"/>
-      <c r="G37" s="68"/>
-      <c r="H37" s="68"/>
-      <c r="I37" s="68"/>
-      <c r="J37" s="68"/>
-      <c r="K37" s="68"/>
-      <c r="L37" s="68"/>
-      <c r="M37" s="68"/>
-      <c r="N37" s="68"/>
-      <c r="O37" s="68"/>
-      <c r="P37" s="68"/>
+      <c r="A37" s="65"/>
+      <c r="B37" s="65"/>
+      <c r="C37" s="65"/>
+      <c r="D37" s="65"/>
+      <c r="E37" s="65"/>
+      <c r="F37" s="65"/>
+      <c r="G37" s="65"/>
+      <c r="H37" s="65"/>
+      <c r="I37" s="65"/>
+      <c r="J37" s="65"/>
+      <c r="K37" s="65"/>
+      <c r="L37" s="65"/>
+      <c r="M37" s="65"/>
+      <c r="N37" s="65"/>
+      <c r="O37" s="65"/>
+      <c r="P37" s="65"/>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
@@ -2736,73 +2892,73 @@
         <v>27</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="67" t="s">
+    <row r="47" spans="1:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="B47" s="67" t="s">
+      <c r="B47" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="C47" s="67" t="s">
+      <c r="C47" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="D47" s="67" t="s">
+      <c r="D47" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="E47" s="67" t="s">
+      <c r="E47" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="F47" s="67" t="s">
+      <c r="F47" s="64" t="s">
         <v>35</v>
       </c>
-      <c r="G47" s="67" t="s">
+      <c r="G47" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="H47" s="67" t="s">
+      <c r="H47" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="I47" s="67" t="s">
+      <c r="I47" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="J47" s="67" t="s">
+      <c r="J47" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="K47" s="67" t="s">
+      <c r="K47" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="L47" s="67" t="s">
+      <c r="L47" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="M47" s="67" t="s">
+      <c r="M47" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="N47" s="67" t="s">
+      <c r="N47" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="O47" s="67" t="s">
+      <c r="O47" s="64" t="s">
         <v>14</v>
       </c>
-      <c r="P47" s="67" t="s">
+      <c r="P47" s="64" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="37.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="68"/>
-      <c r="B48" s="68"/>
-      <c r="C48" s="68"/>
-      <c r="D48" s="68"/>
-      <c r="E48" s="68"/>
-      <c r="F48" s="68"/>
-      <c r="G48" s="68"/>
-      <c r="H48" s="68"/>
-      <c r="I48" s="68"/>
-      <c r="J48" s="68"/>
-      <c r="K48" s="68"/>
-      <c r="L48" s="68"/>
-      <c r="M48" s="68"/>
-      <c r="N48" s="68"/>
-      <c r="O48" s="68"/>
-      <c r="P48" s="68"/>
+    <row r="48" spans="1:16" ht="37.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="65"/>
+      <c r="B48" s="65"/>
+      <c r="C48" s="65"/>
+      <c r="D48" s="65"/>
+      <c r="E48" s="65"/>
+      <c r="F48" s="65"/>
+      <c r="G48" s="65"/>
+      <c r="H48" s="65"/>
+      <c r="I48" s="65"/>
+      <c r="J48" s="65"/>
+      <c r="K48" s="65"/>
+      <c r="L48" s="65"/>
+      <c r="M48" s="65"/>
+      <c r="N48" s="65"/>
+      <c r="O48" s="65"/>
+      <c r="P48" s="65"/>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49" s="11" t="s">
@@ -3039,73 +3195,73 @@
         <v>29</v>
       </c>
     </row>
-    <row r="58" spans="1:16" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="67" t="s">
+    <row r="58" spans="1:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="B58" s="67" t="s">
+      <c r="B58" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="C58" s="67" t="s">
+      <c r="C58" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="D58" s="67" t="s">
+      <c r="D58" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="E58" s="67" t="s">
+      <c r="E58" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="F58" s="67" t="s">
+      <c r="F58" s="64" t="s">
         <v>35</v>
       </c>
-      <c r="G58" s="67" t="s">
+      <c r="G58" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="H58" s="67" t="s">
+      <c r="H58" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="I58" s="67" t="s">
+      <c r="I58" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="J58" s="67" t="s">
+      <c r="J58" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="K58" s="67" t="s">
+      <c r="K58" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="L58" s="67" t="s">
+      <c r="L58" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="M58" s="67" t="s">
+      <c r="M58" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="N58" s="67" t="s">
+      <c r="N58" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="O58" s="67" t="s">
+      <c r="O58" s="64" t="s">
         <v>14</v>
       </c>
-      <c r="P58" s="67" t="s">
+      <c r="P58" s="64" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="1:16" ht="43.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="68"/>
-      <c r="B59" s="68"/>
-      <c r="C59" s="68"/>
-      <c r="D59" s="68"/>
-      <c r="E59" s="68"/>
-      <c r="F59" s="68"/>
-      <c r="G59" s="68"/>
-      <c r="H59" s="68"/>
-      <c r="I59" s="68"/>
-      <c r="J59" s="68"/>
-      <c r="K59" s="68"/>
-      <c r="L59" s="68"/>
-      <c r="M59" s="68"/>
-      <c r="N59" s="68"/>
-      <c r="O59" s="68"/>
-      <c r="P59" s="68"/>
+    <row r="59" spans="1:16" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="65"/>
+      <c r="B59" s="65"/>
+      <c r="C59" s="65"/>
+      <c r="D59" s="65"/>
+      <c r="E59" s="65"/>
+      <c r="F59" s="65"/>
+      <c r="G59" s="65"/>
+      <c r="H59" s="65"/>
+      <c r="I59" s="65"/>
+      <c r="J59" s="65"/>
+      <c r="K59" s="65"/>
+      <c r="L59" s="65"/>
+      <c r="M59" s="65"/>
+      <c r="N59" s="65"/>
+      <c r="O59" s="65"/>
+      <c r="P59" s="65"/>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A60" s="11" t="s">
@@ -3342,73 +3498,73 @@
         <v>30</v>
       </c>
     </row>
-    <row r="69" spans="1:16" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="67" t="s">
+    <row r="69" spans="1:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="B69" s="67" t="s">
+      <c r="B69" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="C69" s="67" t="s">
+      <c r="C69" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="D69" s="67" t="s">
+      <c r="D69" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="E69" s="67" t="s">
+      <c r="E69" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="F69" s="67" t="s">
+      <c r="F69" s="64" t="s">
         <v>35</v>
       </c>
-      <c r="G69" s="67" t="s">
+      <c r="G69" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="H69" s="67" t="s">
+      <c r="H69" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="I69" s="67" t="s">
+      <c r="I69" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="J69" s="67" t="s">
+      <c r="J69" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="K69" s="67" t="s">
+      <c r="K69" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="L69" s="67" t="s">
+      <c r="L69" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="M69" s="67" t="s">
+      <c r="M69" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="N69" s="67" t="s">
+      <c r="N69" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="O69" s="67" t="s">
+      <c r="O69" s="64" t="s">
         <v>14</v>
       </c>
-      <c r="P69" s="67" t="s">
+      <c r="P69" s="64" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="70" spans="1:16" ht="39.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="68"/>
-      <c r="B70" s="68"/>
-      <c r="C70" s="68"/>
-      <c r="D70" s="68"/>
-      <c r="E70" s="68"/>
-      <c r="F70" s="68"/>
-      <c r="G70" s="68"/>
-      <c r="H70" s="68"/>
-      <c r="I70" s="68"/>
-      <c r="J70" s="68"/>
-      <c r="K70" s="68"/>
-      <c r="L70" s="68"/>
-      <c r="M70" s="68"/>
-      <c r="N70" s="68"/>
-      <c r="O70" s="68"/>
-      <c r="P70" s="68"/>
+    <row r="70" spans="1:16" ht="39.299999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="65"/>
+      <c r="B70" s="65"/>
+      <c r="C70" s="65"/>
+      <c r="D70" s="65"/>
+      <c r="E70" s="65"/>
+      <c r="F70" s="65"/>
+      <c r="G70" s="65"/>
+      <c r="H70" s="65"/>
+      <c r="I70" s="65"/>
+      <c r="J70" s="65"/>
+      <c r="K70" s="65"/>
+      <c r="L70" s="65"/>
+      <c r="M70" s="65"/>
+      <c r="N70" s="65"/>
+      <c r="O70" s="65"/>
+      <c r="P70" s="65"/>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A71" s="11" t="s">
@@ -3645,73 +3801,73 @@
         <v>31</v>
       </c>
     </row>
-    <row r="80" spans="1:16" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="67" t="s">
+    <row r="80" spans="1:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="B80" s="67" t="s">
+      <c r="B80" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="C80" s="67" t="s">
+      <c r="C80" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="D80" s="67" t="s">
+      <c r="D80" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="E80" s="67" t="s">
+      <c r="E80" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="F80" s="67" t="s">
+      <c r="F80" s="64" t="s">
         <v>35</v>
       </c>
-      <c r="G80" s="67" t="s">
+      <c r="G80" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="H80" s="67" t="s">
+      <c r="H80" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="I80" s="67" t="s">
+      <c r="I80" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="J80" s="67" t="s">
+      <c r="J80" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="K80" s="67" t="s">
+      <c r="K80" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="L80" s="67" t="s">
+      <c r="L80" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="M80" s="67" t="s">
+      <c r="M80" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="N80" s="67" t="s">
+      <c r="N80" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="O80" s="67" t="s">
+      <c r="O80" s="64" t="s">
         <v>14</v>
       </c>
-      <c r="P80" s="67" t="s">
+      <c r="P80" s="64" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="81" spans="1:16" ht="38.15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="68"/>
-      <c r="B81" s="68"/>
-      <c r="C81" s="68"/>
-      <c r="D81" s="68"/>
-      <c r="E81" s="68"/>
-      <c r="F81" s="68"/>
-      <c r="G81" s="68"/>
-      <c r="H81" s="68"/>
-      <c r="I81" s="68"/>
-      <c r="J81" s="68"/>
-      <c r="K81" s="68"/>
-      <c r="L81" s="68"/>
-      <c r="M81" s="68"/>
-      <c r="N81" s="68"/>
-      <c r="O81" s="68"/>
-      <c r="P81" s="68"/>
+    <row r="81" spans="1:16" ht="38.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="65"/>
+      <c r="B81" s="65"/>
+      <c r="C81" s="65"/>
+      <c r="D81" s="65"/>
+      <c r="E81" s="65"/>
+      <c r="F81" s="65"/>
+      <c r="G81" s="65"/>
+      <c r="H81" s="65"/>
+      <c r="I81" s="65"/>
+      <c r="J81" s="65"/>
+      <c r="K81" s="65"/>
+      <c r="L81" s="65"/>
+      <c r="M81" s="65"/>
+      <c r="N81" s="65"/>
+      <c r="O81" s="65"/>
+      <c r="P81" s="65"/>
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A82" s="11" t="s">
@@ -3948,73 +4104,73 @@
         <v>32</v>
       </c>
     </row>
-    <row r="91" spans="1:16" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="67" t="s">
+    <row r="91" spans="1:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="B91" s="67" t="s">
+      <c r="B91" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="C91" s="67" t="s">
+      <c r="C91" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="D91" s="67" t="s">
+      <c r="D91" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="E91" s="67" t="s">
+      <c r="E91" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="F91" s="67" t="s">
+      <c r="F91" s="64" t="s">
         <v>35</v>
       </c>
-      <c r="G91" s="67" t="s">
+      <c r="G91" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="H91" s="67" t="s">
+      <c r="H91" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="I91" s="67" t="s">
+      <c r="I91" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="J91" s="67" t="s">
+      <c r="J91" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="K91" s="67" t="s">
+      <c r="K91" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="L91" s="67" t="s">
+      <c r="L91" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="M91" s="67" t="s">
+      <c r="M91" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="N91" s="67" t="s">
+      <c r="N91" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="O91" s="67" t="s">
+      <c r="O91" s="64" t="s">
         <v>14</v>
       </c>
-      <c r="P91" s="67" t="s">
+      <c r="P91" s="64" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="92" spans="1:16" ht="38.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="68"/>
-      <c r="B92" s="68"/>
-      <c r="C92" s="68"/>
-      <c r="D92" s="68"/>
-      <c r="E92" s="68"/>
-      <c r="F92" s="68"/>
-      <c r="G92" s="68"/>
-      <c r="H92" s="68"/>
-      <c r="I92" s="68"/>
-      <c r="J92" s="68"/>
-      <c r="K92" s="68"/>
-      <c r="L92" s="68"/>
-      <c r="M92" s="68"/>
-      <c r="N92" s="68"/>
-      <c r="O92" s="68"/>
-      <c r="P92" s="68"/>
+      <c r="A92" s="65"/>
+      <c r="B92" s="65"/>
+      <c r="C92" s="65"/>
+      <c r="D92" s="65"/>
+      <c r="E92" s="65"/>
+      <c r="F92" s="65"/>
+      <c r="G92" s="65"/>
+      <c r="H92" s="65"/>
+      <c r="I92" s="65"/>
+      <c r="J92" s="65"/>
+      <c r="K92" s="65"/>
+      <c r="L92" s="65"/>
+      <c r="M92" s="65"/>
+      <c r="N92" s="65"/>
+      <c r="O92" s="65"/>
+      <c r="P92" s="65"/>
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A93" s="11" t="s">
@@ -4251,73 +4407,73 @@
         <v>33</v>
       </c>
     </row>
-    <row r="102" spans="1:16" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="67" t="s">
+    <row r="102" spans="1:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="64" t="s">
         <v>2</v>
       </c>
-      <c r="B102" s="67" t="s">
+      <c r="B102" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="C102" s="67" t="s">
+      <c r="C102" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="D102" s="67" t="s">
+      <c r="D102" s="64" t="s">
         <v>4</v>
       </c>
-      <c r="E102" s="67" t="s">
+      <c r="E102" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="F102" s="67" t="s">
+      <c r="F102" s="64" t="s">
         <v>35</v>
       </c>
-      <c r="G102" s="67" t="s">
+      <c r="G102" s="64" t="s">
         <v>6</v>
       </c>
-      <c r="H102" s="67" t="s">
+      <c r="H102" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="I102" s="67" t="s">
+      <c r="I102" s="64" t="s">
         <v>8</v>
       </c>
-      <c r="J102" s="67" t="s">
+      <c r="J102" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="K102" s="67" t="s">
+      <c r="K102" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="L102" s="67" t="s">
+      <c r="L102" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="M102" s="67" t="s">
+      <c r="M102" s="64" t="s">
         <v>12</v>
       </c>
-      <c r="N102" s="67" t="s">
+      <c r="N102" s="64" t="s">
         <v>13</v>
       </c>
-      <c r="O102" s="67" t="s">
+      <c r="O102" s="64" t="s">
         <v>14</v>
       </c>
-      <c r="P102" s="67" t="s">
+      <c r="P102" s="64" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="103" spans="1:16" ht="39.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="68"/>
-      <c r="B103" s="68"/>
-      <c r="C103" s="68"/>
-      <c r="D103" s="68"/>
-      <c r="E103" s="68"/>
-      <c r="F103" s="68"/>
-      <c r="G103" s="68"/>
-      <c r="H103" s="68"/>
-      <c r="I103" s="68"/>
-      <c r="J103" s="68"/>
-      <c r="K103" s="68"/>
-      <c r="L103" s="68"/>
-      <c r="M103" s="68"/>
-      <c r="N103" s="68"/>
-      <c r="O103" s="68"/>
-      <c r="P103" s="68"/>
+    <row r="103" spans="1:16" ht="39.299999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="65"/>
+      <c r="B103" s="65"/>
+      <c r="C103" s="65"/>
+      <c r="D103" s="65"/>
+      <c r="E103" s="65"/>
+      <c r="F103" s="65"/>
+      <c r="G103" s="65"/>
+      <c r="H103" s="65"/>
+      <c r="I103" s="65"/>
+      <c r="J103" s="65"/>
+      <c r="K103" s="65"/>
+      <c r="L103" s="65"/>
+      <c r="M103" s="65"/>
+      <c r="N103" s="65"/>
+      <c r="O103" s="65"/>
+      <c r="P103" s="65"/>
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A104" s="11" t="s">
@@ -4551,25 +4707,123 @@
     </row>
   </sheetData>
   <mergeCells count="160">
-    <mergeCell ref="M102:M103"/>
-    <mergeCell ref="N102:N103"/>
-    <mergeCell ref="O102:O103"/>
-    <mergeCell ref="P102:P103"/>
-    <mergeCell ref="G102:G103"/>
-    <mergeCell ref="H102:H103"/>
-    <mergeCell ref="I102:I103"/>
-    <mergeCell ref="J102:J103"/>
-    <mergeCell ref="K102:K103"/>
-    <mergeCell ref="L102:L103"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="C102:C103"/>
-    <mergeCell ref="D102:D103"/>
-    <mergeCell ref="E102:E103"/>
-    <mergeCell ref="F102:F103"/>
-    <mergeCell ref="G91:G92"/>
-    <mergeCell ref="H91:H92"/>
-    <mergeCell ref="I91:I92"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="N14:N15"/>
+    <mergeCell ref="O14:O15"/>
+    <mergeCell ref="P14:P15"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="M25:M26"/>
+    <mergeCell ref="N25:N26"/>
+    <mergeCell ref="O25:O26"/>
+    <mergeCell ref="P25:P26"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="K25:K26"/>
+    <mergeCell ref="L25:L26"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="M36:M37"/>
+    <mergeCell ref="N36:N37"/>
+    <mergeCell ref="O36:O37"/>
+    <mergeCell ref="P36:P37"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="I36:I37"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="K36:K37"/>
+    <mergeCell ref="L36:L37"/>
+    <mergeCell ref="M47:M48"/>
+    <mergeCell ref="N47:N48"/>
+    <mergeCell ref="O47:O48"/>
+    <mergeCell ref="P47:P48"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="L47:L48"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="N58:N59"/>
+    <mergeCell ref="O58:O59"/>
+    <mergeCell ref="P58:P59"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="B69:B70"/>
+    <mergeCell ref="C69:C70"/>
+    <mergeCell ref="D69:D70"/>
+    <mergeCell ref="E69:E70"/>
+    <mergeCell ref="F69:F70"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="L58:L59"/>
+    <mergeCell ref="M69:M70"/>
+    <mergeCell ref="N69:N70"/>
+    <mergeCell ref="O69:O70"/>
+    <mergeCell ref="P69:P70"/>
+    <mergeCell ref="J69:J70"/>
+    <mergeCell ref="K69:K70"/>
+    <mergeCell ref="L69:L70"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C80:C81"/>
+    <mergeCell ref="D80:D81"/>
+    <mergeCell ref="E80:E81"/>
+    <mergeCell ref="F80:F81"/>
+    <mergeCell ref="G69:G70"/>
+    <mergeCell ref="H69:H70"/>
+    <mergeCell ref="I69:I70"/>
+    <mergeCell ref="M58:M59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="M80:M81"/>
     <mergeCell ref="N80:N81"/>
     <mergeCell ref="O80:O81"/>
     <mergeCell ref="P80:P81"/>
@@ -4594,137 +4848,39 @@
     <mergeCell ref="L91:L92"/>
     <mergeCell ref="A80:A81"/>
     <mergeCell ref="B80:B81"/>
-    <mergeCell ref="C80:C81"/>
-    <mergeCell ref="D80:D81"/>
-    <mergeCell ref="E80:E81"/>
-    <mergeCell ref="F80:F81"/>
-    <mergeCell ref="G69:G70"/>
-    <mergeCell ref="H69:H70"/>
-    <mergeCell ref="I69:I70"/>
-    <mergeCell ref="M58:M59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="E58:E59"/>
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="M80:M81"/>
-    <mergeCell ref="N58:N59"/>
-    <mergeCell ref="O58:O59"/>
-    <mergeCell ref="P58:P59"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="B69:B70"/>
-    <mergeCell ref="C69:C70"/>
-    <mergeCell ref="D69:D70"/>
-    <mergeCell ref="E69:E70"/>
-    <mergeCell ref="F69:F70"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="H58:H59"/>
-    <mergeCell ref="I58:I59"/>
-    <mergeCell ref="J58:J59"/>
-    <mergeCell ref="K58:K59"/>
-    <mergeCell ref="L58:L59"/>
-    <mergeCell ref="M69:M70"/>
-    <mergeCell ref="N69:N70"/>
-    <mergeCell ref="O69:O70"/>
-    <mergeCell ref="P69:P70"/>
-    <mergeCell ref="J69:J70"/>
-    <mergeCell ref="K69:K70"/>
-    <mergeCell ref="L69:L70"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="M36:M37"/>
-    <mergeCell ref="N36:N37"/>
-    <mergeCell ref="O36:O37"/>
-    <mergeCell ref="P36:P37"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="I36:I37"/>
-    <mergeCell ref="J36:J37"/>
-    <mergeCell ref="K36:K37"/>
-    <mergeCell ref="L36:L37"/>
-    <mergeCell ref="M47:M48"/>
-    <mergeCell ref="N47:N48"/>
-    <mergeCell ref="O47:O48"/>
-    <mergeCell ref="P47:P48"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="L47:L48"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="O14:O15"/>
-    <mergeCell ref="P14:P15"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="F25:F26"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="M25:M26"/>
-    <mergeCell ref="N25:N26"/>
-    <mergeCell ref="O25:O26"/>
-    <mergeCell ref="P25:P26"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="K25:K26"/>
-    <mergeCell ref="L25:L26"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="N14:N15"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="D102:D103"/>
+    <mergeCell ref="E102:E103"/>
+    <mergeCell ref="F102:F103"/>
+    <mergeCell ref="G91:G92"/>
+    <mergeCell ref="H91:H92"/>
+    <mergeCell ref="I91:I92"/>
+    <mergeCell ref="M102:M103"/>
+    <mergeCell ref="N102:N103"/>
+    <mergeCell ref="O102:O103"/>
+    <mergeCell ref="P102:P103"/>
+    <mergeCell ref="G102:G103"/>
+    <mergeCell ref="H102:H103"/>
+    <mergeCell ref="I102:I103"/>
+    <mergeCell ref="J102:J103"/>
+    <mergeCell ref="K102:K103"/>
+    <mergeCell ref="L102:L103"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A15"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="90.59765625" customWidth="1"/>
+    <col min="1" max="1" width="90.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="18.3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="18" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4760,27 +4916,27 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="23" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A11" s="24" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="23" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="62.35" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>45</v>
       </c>
@@ -4788,7 +4944,7 @@
     <row r="14" spans="1:1" ht="15.6" x14ac:dyDescent="0.35">
       <c r="A14" s="9"/>
     </row>
-    <row r="15" spans="1:1" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="26" t="s">
         <v>46</v>
       </c>
@@ -4799,14 +4955,14 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K20"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="49.296875" customWidth="1"/>
+    <col min="1" max="1" width="49.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>47</v>
       </c>
@@ -4821,7 +4977,7 @@
       <c r="J1" s="27"/>
       <c r="K1" s="27"/>
     </row>
-    <row r="2" spans="1:11" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
         <v>48</v>
       </c>
@@ -4837,24 +4993,24 @@
       <c r="K2" s="28"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="69" t="s">
+      <c r="A3" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="70" t="s">
+      <c r="B3" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
-      <c r="I3" s="70"/>
-      <c r="J3" s="70"/>
-      <c r="K3" s="70"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="67"/>
+      <c r="K3" s="67"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="69"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="29">
         <v>1</v>
       </c>
@@ -5135,7 +5291,9 @@
       <c r="A12" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="B12" s="33"/>
+      <c r="B12" s="33">
+        <v>9</v>
+      </c>
       <c r="C12" s="33"/>
       <c r="D12" s="33"/>
       <c r="E12" s="33"/>
@@ -5220,7 +5378,9 @@
       <c r="A15" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="33"/>
+      <c r="B15" s="33">
+        <v>10.5</v>
+      </c>
       <c r="C15" s="33"/>
       <c r="D15" s="33"/>
       <c r="E15" s="33"/>
@@ -5231,7 +5391,7 @@
       <c r="J15" s="33"/>
       <c r="K15" s="33"/>
     </row>
-    <row r="16" spans="1:11" ht="16.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="16.649999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="34" t="s">
         <v>61</v>
       </c>
@@ -5270,7 +5430,10 @@
       <c r="A17" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="B17" s="36"/>
+      <c r="B17" s="36">
+        <f>(B5-SUM(B6:B9))+((B10/1000)*B12/12)-((B13/1000)*(12-B15)/12)</f>
+        <v>896</v>
+      </c>
       <c r="C17" s="36"/>
       <c r="D17" s="36"/>
       <c r="E17" s="36"/>
@@ -5285,7 +5448,10 @@
       <c r="A18" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="B18" s="36"/>
+      <c r="B18" s="36">
+        <f>B16*100/B17</f>
+        <v>11.383928571428571</v>
+      </c>
       <c r="C18" s="36"/>
       <c r="D18" s="36"/>
       <c r="E18" s="36"/>
@@ -5297,37 +5463,37 @@
       <c r="K18" s="36"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="60" t="s">
+      <c r="A19" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="B19" s="61">
+      <c r="B19" s="57">
         <v>4</v>
       </c>
-      <c r="C19" s="61">
+      <c r="C19" s="57">
         <v>6</v>
       </c>
-      <c r="D19" s="61">
+      <c r="D19" s="57">
         <v>2</v>
       </c>
-      <c r="E19" s="61">
+      <c r="E19" s="57">
         <v>6.5</v>
       </c>
-      <c r="F19" s="61">
+      <c r="F19" s="57">
         <v>2.5</v>
       </c>
-      <c r="G19" s="61">
+      <c r="G19" s="57">
         <v>10</v>
       </c>
-      <c r="H19" s="61">
+      <c r="H19" s="57">
         <v>12</v>
       </c>
-      <c r="I19" s="61">
+      <c r="I19" s="57">
         <v>7</v>
       </c>
-      <c r="J19" s="61">
+      <c r="J19" s="57">
         <v>3.5</v>
       </c>
-      <c r="K19" s="61">
+      <c r="K19" s="57">
         <v>4.5</v>
       </c>
     </row>
@@ -5335,7 +5501,10 @@
       <c r="A20" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="B20" s="41"/>
+      <c r="B20" s="41">
+        <f>B16*B19/B17</f>
+        <v>0.45535714285714285</v>
+      </c>
       <c r="C20" s="41"/>
       <c r="D20" s="41"/>
       <c r="E20" s="41"/>
@@ -5356,11 +5525,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A13"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="92.796875" customWidth="1"/>
+    <col min="1" max="1" width="92.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
@@ -5381,17 +5550,17 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="23" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="31.2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A7" s="38" t="s">
         <v>67</v>
       </c>
@@ -5401,22 +5570,22 @@
         <v>68</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="17.75" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:1" ht="18" x14ac:dyDescent="0.4">
       <c r="A9" s="23" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="31.2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:1" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A10" s="39" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="42" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="23" t="s">
         <v>113</v>
       </c>
@@ -5430,16 +5599,17 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:W36"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.8984375" customWidth="1"/>
-    <col min="13" max="13" width="17.69921875" customWidth="1"/>
+    <col min="1" max="1" width="30.88671875" customWidth="1"/>
+    <col min="13" max="13" width="17.6640625" customWidth="1"/>
+    <col min="14" max="14" width="18.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="18.3" x14ac:dyDescent="0.4">
-      <c r="A1" s="55" t="s">
+    <row r="1" spans="1:23" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" s="53" t="s">
         <v>99</v>
       </c>
       <c r="B1" s="43"/>
@@ -5453,7 +5623,7 @@
       <c r="J1" s="43"/>
       <c r="K1" s="43"/>
     </row>
-    <row r="2" spans="1:23" ht="18.3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:23" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="25" t="s">
         <v>98</v>
       </c>
@@ -5467,7 +5637,7 @@
       <c r="I2" s="44"/>
       <c r="J2" s="44"/>
       <c r="K2" s="44"/>
-      <c r="M2" s="58" t="s">
+      <c r="M2" s="56" t="s">
         <v>101</v>
       </c>
       <c r="N2" s="45">
@@ -5501,26 +5671,29 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="11.3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="71" t="s">
+    <row r="3" spans="1:23" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="68" t="s">
         <v>100</v>
       </c>
-      <c r="B3" s="72" t="s">
+      <c r="B3" s="69" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="72"/>
-      <c r="K3" s="72"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="69"/>
+      <c r="K3" s="69"/>
       <c r="M3" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="N3" s="47"/>
+      <c r="N3" s="47">
+        <f>N15/N9*100</f>
+        <v>93.81808278867102</v>
+      </c>
       <c r="O3" s="47"/>
       <c r="P3" s="47"/>
       <c r="Q3" s="47"/>
@@ -5531,8 +5704,8 @@
       <c r="V3" s="47"/>
       <c r="W3" s="47"/>
     </row>
-    <row r="4" spans="1:23" ht="10.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="71"/>
+    <row r="4" spans="1:23" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="68"/>
       <c r="B4" s="48">
         <v>1</v>
       </c>
@@ -5566,7 +5739,10 @@
       <c r="M4" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="N4" s="47"/>
+      <c r="N4" s="47">
+        <f>N16/N10*100</f>
+        <v>106.58925979680696</v>
+      </c>
       <c r="O4" s="47"/>
       <c r="P4" s="47"/>
       <c r="Q4" s="47"/>
@@ -5577,7 +5753,7 @@
       <c r="V4" s="47"/>
       <c r="W4" s="47"/>
     </row>
-    <row r="5" spans="1:23" ht="10.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:23" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="48" t="s">
         <v>74</v>
       </c>
@@ -5594,7 +5770,10 @@
       <c r="M5" s="46" t="s">
         <v>75</v>
       </c>
-      <c r="N5" s="47"/>
+      <c r="N5" s="47">
+        <f>N17/N11*100</f>
+        <v>112.29946524064169</v>
+      </c>
       <c r="O5" s="47"/>
       <c r="P5" s="47"/>
       <c r="Q5" s="47"/>
@@ -5622,7 +5801,10 @@
       <c r="M6" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="N6" s="47"/>
+      <c r="N6" s="47">
+        <f>N18/N12*100</f>
+        <v>112.65846453012227</v>
+      </c>
       <c r="O6" s="47"/>
       <c r="P6" s="47"/>
       <c r="Q6" s="47"/>
@@ -5633,7 +5815,7 @@
       <c r="V6" s="47"/>
       <c r="W6" s="47"/>
     </row>
-    <row r="7" spans="1:23" ht="11.3" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="49" t="s">
         <v>78</v>
       </c>
@@ -5670,7 +5852,10 @@
       <c r="M7" s="46" t="s">
         <v>79</v>
       </c>
-      <c r="N7" s="47"/>
+      <c r="N7" s="47">
+        <f>N19/N13*100</f>
+        <v>76.919339164237115</v>
+      </c>
       <c r="O7" s="47"/>
       <c r="P7" s="47"/>
       <c r="Q7" s="47"/>
@@ -5681,7 +5866,7 @@
       <c r="V7" s="47"/>
       <c r="W7" s="47"/>
     </row>
-    <row r="8" spans="1:23" ht="12.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:23" ht="12.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="49" t="s">
         <v>80</v>
       </c>
@@ -5763,10 +5948,13 @@
       <c r="K9" s="49">
         <v>4000</v>
       </c>
-      <c r="M9" s="51" t="s">
+      <c r="M9" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="N9" s="47"/>
+      <c r="N9" s="47">
+        <f>(B7*B11+B8*B12+B9*B13)/(B18*1000)</f>
+        <v>1.5793548387096774</v>
+      </c>
       <c r="O9" s="47"/>
       <c r="P9" s="47"/>
       <c r="Q9" s="47"/>
@@ -5777,7 +5965,7 @@
       <c r="V9" s="47"/>
       <c r="W9" s="47"/>
     </row>
-    <row r="10" spans="1:23" ht="11.3" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:23" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="49" t="s">
         <v>84</v>
       </c>
@@ -5791,10 +5979,13 @@
       <c r="I10" s="49"/>
       <c r="J10" s="49"/>
       <c r="K10" s="49"/>
-      <c r="M10" s="51" t="s">
+      <c r="M10" s="46" t="s">
         <v>85</v>
       </c>
-      <c r="N10" s="47"/>
+      <c r="N10" s="47">
+        <f>B18*1000/(B7*B11+B8*B12+B9*B13)</f>
+        <v>0.63316993464052285</v>
+      </c>
       <c r="O10" s="47"/>
       <c r="P10" s="47"/>
       <c r="Q10" s="47"/>
@@ -5805,7 +5996,7 @@
       <c r="V10" s="47"/>
       <c r="W10" s="47"/>
     </row>
-    <row r="11" spans="1:23" ht="10.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:23" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="49" t="s">
         <v>78</v>
       </c>
@@ -5839,10 +6030,13 @@
       <c r="K11" s="49">
         <v>520</v>
       </c>
-      <c r="M11" s="51" t="s">
+      <c r="M11" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="N11" s="47"/>
+      <c r="N11" s="47">
+        <f>B18*1000/B20</f>
+        <v>349.88713318284425</v>
+      </c>
       <c r="O11" s="47"/>
       <c r="P11" s="47"/>
       <c r="Q11" s="47"/>
@@ -5853,7 +6047,7 @@
       <c r="V11" s="47"/>
       <c r="W11" s="47"/>
     </row>
-    <row r="12" spans="1:23" ht="12.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:23" ht="12.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="49" t="s">
         <v>80</v>
       </c>
@@ -5887,10 +6081,13 @@
       <c r="K12" s="49">
         <v>190</v>
       </c>
-      <c r="M12" s="51" t="s">
+      <c r="M12" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="N12" s="47"/>
+      <c r="N12" s="47">
+        <f>(B18-B19)*1000/B20</f>
+        <v>322.79909706546277</v>
+      </c>
       <c r="O12" s="47"/>
       <c r="P12" s="47"/>
       <c r="Q12" s="47"/>
@@ -5935,10 +6132,13 @@
       <c r="K13" s="49">
         <v>200</v>
       </c>
-      <c r="M13" s="51" t="s">
+      <c r="M13" s="46" t="s">
         <v>88</v>
       </c>
-      <c r="N13" s="47"/>
+      <c r="N13" s="47">
+        <f>((B11-B15)*B7+(B12-B16)*B8+(B13-B17)*B9)/(B18*1000)*100</f>
+        <v>50.580645161290327</v>
+      </c>
       <c r="O13" s="47"/>
       <c r="P13" s="47"/>
       <c r="Q13" s="47"/>
@@ -5949,7 +6149,7 @@
       <c r="V13" s="47"/>
       <c r="W13" s="47"/>
     </row>
-    <row r="14" spans="1:23" ht="10.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:23" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="49" t="s">
         <v>89</v>
       </c>
@@ -6011,10 +6211,13 @@
       <c r="K15" s="49">
         <v>450</v>
       </c>
-      <c r="M15" s="51" t="s">
+      <c r="M15" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="N15" s="47"/>
+      <c r="N15" s="47">
+        <f>(B23*B27+B24*B28+B25*B29)/(((B18*105)/100)*1000)</f>
+        <v>1.4817204301075269</v>
+      </c>
       <c r="O15" s="47"/>
       <c r="P15" s="47"/>
       <c r="Q15" s="47"/>
@@ -6059,10 +6262,13 @@
       <c r="K16" s="49">
         <v>140</v>
       </c>
-      <c r="M16" s="51" t="s">
+      <c r="M16" s="46" t="s">
         <v>85</v>
       </c>
-      <c r="N16" s="47"/>
+      <c r="N16" s="47">
+        <f>(((B18*(100+B34))/100)*1000)/(B23*B27+B24*B28+B25*B29)</f>
+        <v>0.67489114658925975</v>
+      </c>
       <c r="O16" s="47"/>
       <c r="P16" s="47"/>
       <c r="Q16" s="47"/>
@@ -6107,10 +6313,13 @@
       <c r="K17" s="49">
         <v>165</v>
       </c>
-      <c r="M17" s="51" t="s">
+      <c r="M17" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="N17" s="47"/>
+      <c r="N17" s="47">
+        <f>(((B18*(100+B34))/100)*1000)/((B20*(100-6.5))/100)</f>
+        <v>392.92137951014593</v>
+      </c>
       <c r="O17" s="47"/>
       <c r="P17" s="47"/>
       <c r="Q17" s="47"/>
@@ -6155,10 +6364,13 @@
       <c r="K18" s="49">
         <v>1570</v>
       </c>
-      <c r="M18" s="51" t="s">
+      <c r="M18" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="N18" s="47"/>
+      <c r="N18" s="47">
+        <f>((((B18*(100+B34))/100)*1000)-(((B19*(100+B35))/100)*1000))/((B20*(100-6.5))/100)</f>
+        <v>363.66050627104937</v>
+      </c>
       <c r="O18" s="47"/>
       <c r="P18" s="47"/>
       <c r="Q18" s="47"/>
@@ -6203,10 +6415,13 @@
       <c r="K19" s="49">
         <v>130</v>
       </c>
-      <c r="M19" s="51" t="s">
+      <c r="M19" s="46" t="s">
         <v>88</v>
       </c>
-      <c r="N19" s="47"/>
+      <c r="N19" s="47">
+        <f>((B27-B31)*B23+(B28-B32)*B24+(B29-B33)*B25)/(((B18*(100+B34))/100)*1000)*100</f>
+        <v>38.906298003072202</v>
+      </c>
       <c r="O19" s="47"/>
       <c r="P19" s="47"/>
       <c r="Q19" s="47"/>
@@ -6217,7 +6432,7 @@
       <c r="V19" s="47"/>
       <c r="W19" s="47"/>
     </row>
-    <row r="20" spans="1:23" ht="11.3" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:23" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="49" t="s">
         <v>93</v>
       </c>
@@ -6251,18 +6466,18 @@
       <c r="K20" s="49">
         <v>6900</v>
       </c>
-      <c r="N20" s="52"/>
-      <c r="O20" s="52"/>
-      <c r="P20" s="52"/>
-      <c r="Q20" s="52"/>
-      <c r="R20" s="52"/>
-      <c r="S20" s="52"/>
-      <c r="T20" s="52"/>
-      <c r="U20" s="52"/>
-      <c r="V20" s="52"/>
-      <c r="W20" s="52"/>
-    </row>
-    <row r="21" spans="1:23" ht="10.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N20" s="51"/>
+      <c r="O20" s="51"/>
+      <c r="P20" s="51"/>
+      <c r="Q20" s="51"/>
+      <c r="R20" s="51"/>
+      <c r="S20" s="51"/>
+      <c r="T20" s="51"/>
+      <c r="U20" s="51"/>
+      <c r="V20" s="51"/>
+      <c r="W20" s="51"/>
+    </row>
+    <row r="21" spans="1:23" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="48" t="s">
         <v>94</v>
       </c>
@@ -6277,7 +6492,7 @@
       <c r="J21" s="48"/>
       <c r="K21" s="48"/>
     </row>
-    <row r="22" spans="1:23" ht="13.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:23" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="49" t="s">
         <v>76</v>
       </c>
@@ -6327,7 +6542,7 @@
         <v>8100</v>
       </c>
     </row>
-    <row r="24" spans="1:23" ht="9.6999999999999993" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:23" ht="9.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="49" t="s">
         <v>80</v>
       </c>
@@ -6362,7 +6577,7 @@
         <v>5500</v>
       </c>
     </row>
-    <row r="25" spans="1:23" ht="10.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:23" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="49" t="s">
         <v>82</v>
       </c>
@@ -6397,7 +6612,7 @@
         <v>4300</v>
       </c>
     </row>
-    <row r="26" spans="1:23" ht="10.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:23" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="49" t="s">
         <v>84</v>
       </c>
@@ -6412,7 +6627,7 @@
       <c r="J26" s="49"/>
       <c r="K26" s="49"/>
     </row>
-    <row r="27" spans="1:23" ht="10.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:23" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="49" t="s">
         <v>78</v>
       </c>
@@ -6447,7 +6662,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="28" spans="1:23" ht="10.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:23" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="49" t="s">
         <v>80</v>
       </c>
@@ -6482,7 +6697,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="29" spans="1:23" ht="10.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:23" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="49" t="s">
         <v>82</v>
       </c>
@@ -6517,7 +6732,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="30" spans="1:23" ht="12.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:23" ht="12.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="49" t="s">
         <v>89</v>
       </c>
@@ -6532,7 +6747,7 @@
       <c r="J30" s="49"/>
       <c r="K30" s="49"/>
     </row>
-    <row r="31" spans="1:23" ht="10.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:23" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="49" t="s">
         <v>78</v>
       </c>
@@ -6567,7 +6782,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="32" spans="1:23" ht="10.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:23" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="49" t="s">
         <v>80</v>
       </c>
@@ -6602,7 +6817,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="11.3" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="49" t="s">
         <v>82</v>
       </c>
@@ -6637,7 +6852,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="11.3" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="49" t="s">
         <v>95</v>
       </c>
@@ -6671,10 +6886,9 @@
       <c r="K34" s="49">
         <v>4.5</v>
       </c>
-      <c r="L34" s="53"/>
-      <c r="M34" s="54"/>
-    </row>
-    <row r="35" spans="1:13" ht="11.3" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L34" s="52"/>
+    </row>
+    <row r="35" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="49" t="s">
         <v>96</v>
       </c>
@@ -6709,7 +6923,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="11.3" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="49" t="s">
         <v>97</v>
       </c>
@@ -6755,9 +6969,9 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:A11"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="86" customWidth="1"/>
   </cols>
@@ -6767,8 +6981,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="81.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="56" t="s">
+    <row r="2" spans="1:1" ht="81.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="54" t="s">
         <v>102</v>
       </c>
     </row>
@@ -6782,7 +6996,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="21.5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>104</v>
       </c>
@@ -6797,17 +7011,17 @@
         <v>106</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="17.75" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" ht="18" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="31.2" x14ac:dyDescent="0.35">
-      <c r="A9" s="57" t="s">
+    <row r="9" spans="1:1" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="55" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="23" t="s">
         <v>109</v>
       </c>
@@ -6821,19 +7035,20 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:K24"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="44.69921875" customWidth="1"/>
+    <col min="1" max="1" width="44.6640625" customWidth="1"/>
+    <col min="2" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="18.3" x14ac:dyDescent="0.4">
-      <c r="A1" s="55" t="s">
+    <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" s="53" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="25" t="s">
         <v>115</v>
       </c>
@@ -6849,52 +7064,52 @@
       <c r="K2" s="28"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="69" t="s">
+      <c r="A3" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="70" t="s">
+      <c r="B3" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
-      <c r="I3" s="70"/>
-      <c r="J3" s="70"/>
-      <c r="K3" s="70"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="67"/>
+      <c r="K3" s="67"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="69"/>
-      <c r="B4" s="59">
+      <c r="A4" s="66"/>
+      <c r="B4" s="29">
         <v>1</v>
       </c>
-      <c r="C4" s="59">
+      <c r="C4" s="29">
         <v>2</v>
       </c>
-      <c r="D4" s="59">
+      <c r="D4" s="29">
         <v>3</v>
       </c>
-      <c r="E4" s="59">
+      <c r="E4" s="29">
         <v>4</v>
       </c>
-      <c r="F4" s="59">
+      <c r="F4" s="29">
         <v>5</v>
       </c>
-      <c r="G4" s="59">
+      <c r="G4" s="29">
         <v>6</v>
       </c>
-      <c r="H4" s="59">
+      <c r="H4" s="29">
         <v>7</v>
       </c>
-      <c r="I4" s="59">
+      <c r="I4" s="29">
         <v>8</v>
       </c>
-      <c r="J4" s="59">
+      <c r="J4" s="29">
         <v>9</v>
       </c>
-      <c r="K4" s="59">
+      <c r="K4" s="29">
         <v>10</v>
       </c>
     </row>
@@ -7042,7 +7257,10 @@
       <c r="A9" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="B9" s="36"/>
+      <c r="B9" s="36">
+        <f>B8/B5*B7</f>
+        <v>2016</v>
+      </c>
       <c r="C9" s="36"/>
       <c r="D9" s="36"/>
       <c r="E9" s="36"/>
@@ -7057,7 +7275,10 @@
       <c r="A10" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="B10" s="36"/>
+      <c r="B10" s="36">
+        <f>B8/B6*B7</f>
+        <v>2371.7647058823532</v>
+      </c>
       <c r="C10" s="36"/>
       <c r="D10" s="36"/>
       <c r="E10" s="36"/>
@@ -7072,7 +7293,10 @@
       <c r="A11" s="35" t="s">
         <v>122</v>
       </c>
-      <c r="B11" s="36"/>
+      <c r="B11" s="36">
+        <f>B10-B9</f>
+        <v>355.76470588235316</v>
+      </c>
       <c r="C11" s="36"/>
       <c r="D11" s="36"/>
       <c r="E11" s="36"/>
@@ -7083,7 +7307,7 @@
       <c r="J11" s="36"/>
       <c r="K11" s="36"/>
     </row>
-    <row r="13" spans="1:11" ht="15.6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="25" t="s">
         <v>123</v>
       </c>
@@ -7099,52 +7323,52 @@
       <c r="K13" s="28"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="69" t="s">
+      <c r="A14" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="70" t="s">
+      <c r="B14" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="70"/>
-      <c r="D14" s="70"/>
-      <c r="E14" s="70"/>
-      <c r="F14" s="70"/>
-      <c r="G14" s="70"/>
-      <c r="H14" s="70"/>
-      <c r="I14" s="70"/>
-      <c r="J14" s="70"/>
-      <c r="K14" s="70"/>
+      <c r="C14" s="67"/>
+      <c r="D14" s="67"/>
+      <c r="E14" s="67"/>
+      <c r="F14" s="67"/>
+      <c r="G14" s="67"/>
+      <c r="H14" s="67"/>
+      <c r="I14" s="67"/>
+      <c r="J14" s="67"/>
+      <c r="K14" s="67"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="69"/>
-      <c r="B15" s="65">
+      <c r="A15" s="66"/>
+      <c r="B15" s="29">
         <v>1</v>
       </c>
-      <c r="C15" s="65">
+      <c r="C15" s="29">
         <v>2</v>
       </c>
-      <c r="D15" s="65">
+      <c r="D15" s="29">
         <v>3</v>
       </c>
-      <c r="E15" s="65">
+      <c r="E15" s="29">
         <v>4</v>
       </c>
-      <c r="F15" s="65">
+      <c r="F15" s="29">
         <v>5</v>
       </c>
-      <c r="G15" s="65">
+      <c r="G15" s="29">
         <v>6</v>
       </c>
-      <c r="H15" s="65">
+      <c r="H15" s="29">
         <v>7</v>
       </c>
-      <c r="I15" s="65">
+      <c r="I15" s="29">
         <v>8</v>
       </c>
-      <c r="J15" s="65">
+      <c r="J15" s="29">
         <v>9</v>
       </c>
-      <c r="K15" s="65">
+      <c r="K15" s="29">
         <v>10</v>
       </c>
     </row>
@@ -7257,7 +7481,10 @@
       <c r="A19" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="B19" s="36"/>
+      <c r="B19" s="36">
+        <f>B16/B17</f>
+        <v>10.235294117647058</v>
+      </c>
       <c r="C19" s="36"/>
       <c r="D19" s="36"/>
       <c r="E19" s="36"/>
@@ -7269,37 +7496,37 @@
       <c r="K19" s="36"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="66" t="s">
+      <c r="A20" s="61" t="s">
         <v>127</v>
       </c>
-      <c r="B20" s="61">
+      <c r="B20" s="57">
         <v>12</v>
       </c>
-      <c r="C20" s="61">
+      <c r="C20" s="57">
         <v>5</v>
       </c>
-      <c r="D20" s="61">
+      <c r="D20" s="57">
         <v>8</v>
       </c>
-      <c r="E20" s="61">
+      <c r="E20" s="57">
         <v>9</v>
       </c>
-      <c r="F20" s="61">
+      <c r="F20" s="57">
         <v>12</v>
       </c>
-      <c r="G20" s="61">
+      <c r="G20" s="57">
         <v>13</v>
       </c>
-      <c r="H20" s="61">
+      <c r="H20" s="57">
         <v>10.5</v>
       </c>
-      <c r="I20" s="61">
+      <c r="I20" s="57">
         <v>8.5</v>
       </c>
-      <c r="J20" s="61">
+      <c r="J20" s="57">
         <v>9</v>
       </c>
-      <c r="K20" s="61">
+      <c r="K20" s="57">
         <v>10.5</v>
       </c>
     </row>
@@ -7307,7 +7534,10 @@
       <c r="A21" s="32" t="s">
         <v>140</v>
       </c>
-      <c r="B21" s="36"/>
+      <c r="B21" s="36">
+        <f>B18/B19</f>
+        <v>35.172413793103452</v>
+      </c>
       <c r="C21" s="36"/>
       <c r="D21" s="36"/>
       <c r="E21" s="36"/>
@@ -7322,7 +7552,10 @@
       <c r="A22" s="32" t="s">
         <v>141</v>
       </c>
-      <c r="B22" s="36"/>
+      <c r="B22" s="36">
+        <f>B18/B20</f>
+        <v>30</v>
+      </c>
       <c r="C22" s="36"/>
       <c r="D22" s="36"/>
       <c r="E22" s="36"/>
@@ -7337,7 +7570,10 @@
       <c r="A23" s="35" t="s">
         <v>128</v>
       </c>
-      <c r="B23" s="36"/>
+      <c r="B23" s="36">
+        <f>B16/B20</f>
+        <v>725</v>
+      </c>
       <c r="C23" s="36"/>
       <c r="D23" s="36"/>
       <c r="E23" s="36"/>
@@ -7352,7 +7588,10 @@
       <c r="A24" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="B24" s="36"/>
+      <c r="B24" s="36">
+        <f>B23-B17</f>
+        <v>-125</v>
+      </c>
       <c r="C24" s="36"/>
       <c r="D24" s="36"/>
       <c r="E24" s="36"/>
@@ -7376,12 +7615,12 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="105.59765625" customWidth="1"/>
-    <col min="3" max="3" width="13.59765625" customWidth="1"/>
+    <col min="1" max="1" width="105.5546875" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
@@ -7394,24 +7633,24 @@
         <v>131</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="17.75" x14ac:dyDescent="0.3">
-      <c r="A3" s="62" t="s">
+    <row r="3" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="A3" s="58" t="s">
         <v>132</v>
       </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-    </row>
-    <row r="4" spans="1:3" ht="17.75" x14ac:dyDescent="0.3">
-      <c r="A4" s="62" t="s">
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+    </row>
+    <row r="4" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="A4" s="58" t="s">
         <v>133</v>
       </c>
-      <c r="C4" s="63"/>
-    </row>
-    <row r="5" spans="1:3" ht="46.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="64" t="s">
+      <c r="C4" s="59"/>
+    </row>
+    <row r="5" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="60" t="s">
         <v>134</v>
       </c>
-      <c r="C5" s="63"/>
+      <c r="C5" s="59"/>
     </row>
     <row r="6" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
@@ -7428,8 +7667,8 @@
         <v>137</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="17.75" x14ac:dyDescent="0.3">
-      <c r="A10" s="62" t="s">
+    <row r="10" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="A10" s="58" t="s">
         <v>133</v>
       </c>
     </row>
@@ -7438,13 +7677,13 @@
         <v>138</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="17.75" x14ac:dyDescent="0.3">
-      <c r="A12" s="62" t="s">
+    <row r="12" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="A12" s="58" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="17.75" x14ac:dyDescent="0.3">
-      <c r="A13" s="62" t="s">
+    <row r="13" spans="1:3" ht="18" x14ac:dyDescent="0.3">
+      <c r="A13" s="58" t="s">
         <v>133</v>
       </c>
     </row>

--- a/3k2s/Экономика IT-компании/Лабораторная работа 1 ОС_с.xlsx
+++ b/3k2s/Экономика IT-компании/Лабораторная работа 1 ОС_с.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\УЧЁБА\3 курс\экономика\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\General\BELSTU\3k2s\Экономика IT-компании\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F936256F-099B-4C3A-88E9-26BE47C4AE06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18252" windowHeight="6768" firstSheet="4" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Задание 1 исх. данные, решение" sheetId="1" r:id="rId1"/>
@@ -22,7 +21,7 @@
     <sheet name="Задание 4 исх данные, решение" sheetId="9" r:id="rId7"/>
     <sheet name="Задание 4 порядок работы" sheetId="10" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -727,7 +726,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="[$-419]d\ mmm;@"/>
@@ -979,7 +978,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1001,14 +1000,8 @@
     <fill>
       <patternFill patternType="lightUp"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="5">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -1066,11 +1059,151 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1203,10 +1336,6 @@
       <alignment horizontal="justify" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="8" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="2" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1224,6 +1353,44 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="8" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1504,8 +1671,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P111"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист2"/>
+  <dimension ref="A1:S111"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.44140625" customWidth="1"/>
@@ -1516,7 +1684,7 @@
     <col min="16" max="16" width="9.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>28</v>
       </c>
@@ -1530,80 +1698,80 @@
       <c r="I1" s="9"/>
       <c r="J1" s="9"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A3" s="64" t="s">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A3" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="64" t="s">
+      <c r="B3" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="64" t="s">
+      <c r="C3" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="64" t="s">
+      <c r="D3" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="64" t="s">
+      <c r="E3" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="64" t="s">
+      <c r="F3" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="64" t="s">
+      <c r="G3" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="64" t="s">
+      <c r="H3" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="64" t="s">
+      <c r="I3" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="64" t="s">
+      <c r="J3" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="64" t="s">
+      <c r="K3" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="L3" s="64" t="s">
+      <c r="L3" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="64" t="s">
+      <c r="M3" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="N3" s="64" t="s">
+      <c r="N3" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="O3" s="64" t="s">
+      <c r="O3" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="P3" s="64" t="s">
+      <c r="P3" s="62" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="65"/>
-      <c r="B4" s="65"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
-      <c r="I4" s="65"/>
-      <c r="J4" s="65"/>
-      <c r="K4" s="65"/>
-      <c r="L4" s="65"/>
-      <c r="M4" s="65"/>
-      <c r="N4" s="65"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="65"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="63"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="63"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="63"/>
+      <c r="J4" s="63"/>
+      <c r="K4" s="63"/>
+      <c r="L4" s="63"/>
+      <c r="M4" s="63"/>
+      <c r="N4" s="63"/>
+      <c r="O4" s="63"/>
+      <c r="P4" s="63"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>16</v>
       </c>
@@ -1616,40 +1784,30 @@
       <c r="D5" s="13">
         <v>0</v>
       </c>
-      <c r="E5" s="12">
-        <v>0</v>
-      </c>
+      <c r="E5" s="12"/>
       <c r="F5" s="13">
         <v>24</v>
       </c>
       <c r="G5" s="14">
         <v>44986</v>
       </c>
-      <c r="H5" s="12">
-        <v>2</v>
-      </c>
-      <c r="I5" s="15">
-        <f>B5/B12*100</f>
-        <v>55.209260908281387</v>
-      </c>
-      <c r="J5" s="12">
-        <f>B5+C5-F5</f>
-        <v>3076</v>
-      </c>
-      <c r="K5" s="15">
-        <f>J5/J12*100</f>
-        <v>55.214503679770246</v>
-      </c>
-      <c r="L5" s="12">
-        <f>B5+C5*(E5/12)-F5*((12-H5)/12)</f>
-        <v>3080</v>
-      </c>
+      <c r="H5" s="12"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="68"/>
       <c r="M5" s="16"/>
       <c r="N5" s="16"/>
       <c r="O5" s="16"/>
       <c r="P5" s="16"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="S5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>17</v>
       </c>
@@ -1662,41 +1820,31 @@
       <c r="D6" s="14">
         <v>44958</v>
       </c>
-      <c r="E6" s="12">
-        <v>11</v>
-      </c>
+      <c r="E6" s="12"/>
       <c r="F6" s="13">
         <v>5</v>
       </c>
       <c r="G6" s="14">
         <v>45017</v>
       </c>
-      <c r="H6" s="12">
-        <v>3</v>
-      </c>
-      <c r="I6" s="15">
-        <f>B6/B12*100</f>
-        <v>3.5618878005342829</v>
-      </c>
-      <c r="J6" s="12">
-        <f t="shared" ref="J6:J11" si="0">B6+C6-F6</f>
-        <v>200</v>
-      </c>
-      <c r="K6" s="15">
-        <f>J6/J12*100</f>
-        <v>3.5900197451085982</v>
-      </c>
-      <c r="L6" s="12">
-        <f t="shared" ref="L6:L11" si="1">B6+C6*(E6/12)-F6*((12-H6)/12)</f>
-        <v>200.83333333333334</v>
-      </c>
+      <c r="H6" s="12"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="68"/>
       <c r="M6" s="16"/>
       <c r="N6" s="16"/>
       <c r="O6" s="16"/>
       <c r="P6" s="16"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A7" s="62" t="s">
+      <c r="R6">
+        <v>2</v>
+      </c>
+      <c r="S6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A7" s="69" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="12">
@@ -1708,41 +1856,31 @@
       <c r="D7" s="14">
         <v>45047</v>
       </c>
-      <c r="E7" s="12">
-        <v>8</v>
-      </c>
+      <c r="E7" s="12"/>
       <c r="F7" s="13">
         <v>16</v>
       </c>
       <c r="G7" s="14">
         <v>45139</v>
       </c>
-      <c r="H7" s="12">
-        <v>7</v>
-      </c>
-      <c r="I7" s="15">
-        <f>B7/B12*100</f>
-        <v>17.097061442564559</v>
-      </c>
-      <c r="J7" s="12">
-        <f t="shared" si="0"/>
-        <v>960</v>
-      </c>
-      <c r="K7" s="15">
-        <f>J7/J12*100</f>
-        <v>17.232094776521269</v>
-      </c>
-      <c r="L7" s="63">
-        <f t="shared" si="1"/>
-        <v>964</v>
-      </c>
+      <c r="H7" s="12"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="68"/>
       <c r="M7" s="16"/>
       <c r="N7" s="16"/>
       <c r="O7" s="16"/>
       <c r="P7" s="16"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A8" s="62" t="s">
+      <c r="R7">
+        <v>3</v>
+      </c>
+      <c r="S7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A8" s="69" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="12">
@@ -1754,41 +1892,31 @@
       <c r="D8" s="14">
         <v>45139</v>
       </c>
-      <c r="E8" s="12">
-        <v>5</v>
-      </c>
+      <c r="E8" s="12"/>
       <c r="F8" s="13">
         <v>17</v>
       </c>
       <c r="G8" s="14">
         <v>45170</v>
       </c>
-      <c r="H8" s="12">
-        <v>8</v>
-      </c>
-      <c r="I8" s="15">
-        <f>B8/B12*100</f>
-        <v>4.2742653606411398</v>
-      </c>
-      <c r="J8" s="12">
-        <f t="shared" si="0"/>
-        <v>233</v>
-      </c>
-      <c r="K8" s="15">
-        <f>J8/J12*100</f>
-        <v>4.1823730030515174</v>
-      </c>
-      <c r="L8" s="63">
-        <f t="shared" si="1"/>
-        <v>238.5</v>
-      </c>
+      <c r="H8" s="12"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="68"/>
       <c r="M8" s="16"/>
       <c r="N8" s="16"/>
       <c r="O8" s="16"/>
       <c r="P8" s="16"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
+      <c r="R8">
+        <v>4</v>
+      </c>
+      <c r="S8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A9" s="69" t="s">
         <v>20</v>
       </c>
       <c r="B9" s="12">
@@ -1800,41 +1928,31 @@
       <c r="D9" s="14">
         <v>45108</v>
       </c>
-      <c r="E9" s="12">
-        <v>6</v>
-      </c>
+      <c r="E9" s="12"/>
       <c r="F9" s="13">
         <v>11</v>
       </c>
       <c r="G9" s="14">
         <v>44958</v>
       </c>
-      <c r="H9" s="12">
-        <v>1</v>
-      </c>
-      <c r="I9" s="15">
-        <f>B9/B12*100</f>
-        <v>7.1237756010685658</v>
-      </c>
-      <c r="J9" s="12">
-        <f t="shared" si="0"/>
-        <v>401</v>
-      </c>
-      <c r="K9" s="15">
-        <f>J9/J12*100</f>
-        <v>7.1979895889427397</v>
-      </c>
-      <c r="L9" s="12">
-        <f t="shared" si="1"/>
-        <v>395.91666666666669</v>
-      </c>
+      <c r="H9" s="12"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="68"/>
       <c r="M9" s="16"/>
       <c r="N9" s="16"/>
       <c r="O9" s="16"/>
       <c r="P9" s="16"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A10" s="62" t="s">
+      <c r="R9">
+        <v>5</v>
+      </c>
+      <c r="S9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A10" s="69" t="s">
         <v>21</v>
       </c>
       <c r="B10" s="12">
@@ -1846,40 +1964,30 @@
       <c r="D10" s="14">
         <v>45200</v>
       </c>
-      <c r="E10" s="12">
-        <v>3</v>
-      </c>
+      <c r="E10" s="12"/>
       <c r="F10" s="13">
         <v>9</v>
       </c>
       <c r="G10" s="14">
         <v>45047</v>
       </c>
-      <c r="H10" s="12">
-        <v>4</v>
-      </c>
-      <c r="I10" s="15">
-        <f>B10/B12*100</f>
-        <v>11.041852181656278</v>
-      </c>
-      <c r="J10" s="12">
-        <f t="shared" si="0"/>
-        <v>614</v>
-      </c>
-      <c r="K10" s="15">
-        <f>J10/J12*100</f>
-        <v>11.021360617483396</v>
-      </c>
-      <c r="L10" s="63">
-        <f t="shared" si="1"/>
-        <v>614.75</v>
-      </c>
+      <c r="H10" s="12"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="68"/>
       <c r="M10" s="16"/>
       <c r="N10" s="16"/>
       <c r="O10" s="16"/>
       <c r="P10" s="16"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R10">
+        <v>6</v>
+      </c>
+      <c r="S10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>22</v>
       </c>
@@ -1892,40 +2000,30 @@
       <c r="D11" s="14">
         <v>45170</v>
       </c>
-      <c r="E11" s="12">
-        <v>4</v>
-      </c>
+      <c r="E11" s="12"/>
       <c r="F11" s="13">
         <v>8</v>
       </c>
       <c r="G11" s="14">
         <v>45231</v>
       </c>
-      <c r="H11" s="12">
-        <v>10</v>
-      </c>
-      <c r="I11" s="15">
-        <f>B11/B12*100</f>
-        <v>1.6918967052537845</v>
-      </c>
-      <c r="J11" s="12">
-        <f t="shared" si="0"/>
-        <v>87</v>
-      </c>
-      <c r="K11" s="15">
-        <f>J11/J12*100</f>
-        <v>1.5616585891222401</v>
-      </c>
-      <c r="L11" s="12">
-        <f t="shared" si="1"/>
-        <v>93.666666666666671</v>
-      </c>
+      <c r="H11" s="12"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="68"/>
       <c r="M11" s="16"/>
       <c r="N11" s="16"/>
       <c r="O11" s="16"/>
       <c r="P11" s="16"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R11">
+        <v>7</v>
+      </c>
+      <c r="S11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
         <v>23</v>
       </c>
@@ -1945,114 +2043,114 @@
       </c>
       <c r="G12" s="16"/>
       <c r="H12" s="16"/>
-      <c r="I12" s="19">
-        <f>SUM(I5:I11)</f>
-        <v>100</v>
-      </c>
-      <c r="J12" s="18">
-        <f>SUM(J5:J11)</f>
-        <v>5571</v>
-      </c>
-      <c r="K12" s="18">
-        <f>SUM(K5:K11)</f>
-        <v>100.00000000000001</v>
-      </c>
-      <c r="L12" s="18">
-        <f>SUM(L5:L11)</f>
-        <v>5587.6666666666679</v>
-      </c>
-      <c r="M12" s="20">
-        <f>C12/J12</f>
-        <v>8.2570454137497751E-3</v>
-      </c>
-      <c r="N12" s="20">
-        <f>F12/B12</f>
-        <v>1.6028495102404273E-2</v>
-      </c>
-      <c r="O12" s="19">
-        <f>(SUM(L7:L8,L10))/L12*100</f>
-        <v>32.522519835351659</v>
-      </c>
-      <c r="P12" s="19">
-        <f>(SUM(L5:L6,L9,L11))/L12*100</f>
-        <v>67.477480164648313</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="I12" s="19"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="18"/>
+      <c r="L12" s="18"/>
+      <c r="M12" s="20"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="R12">
+        <v>8</v>
+      </c>
+      <c r="S12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="10" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="64" t="s">
+      <c r="R13">
+        <v>9</v>
+      </c>
+      <c r="S13">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="64" t="s">
+      <c r="B14" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="C14" s="64" t="s">
+      <c r="C14" s="71" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="64" t="s">
+      <c r="D14" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="64" t="s">
+      <c r="E14" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="64" t="s">
+      <c r="F14" s="71" t="s">
         <v>35</v>
       </c>
-      <c r="G14" s="64" t="s">
+      <c r="G14" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="H14" s="64" t="s">
+      <c r="H14" s="71" t="s">
         <v>7</v>
       </c>
-      <c r="I14" s="64" t="s">
+      <c r="I14" s="71" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="64" t="s">
+      <c r="J14" s="71" t="s">
         <v>9</v>
       </c>
-      <c r="K14" s="64" t="s">
+      <c r="K14" s="71" t="s">
         <v>10</v>
       </c>
-      <c r="L14" s="64" t="s">
+      <c r="L14" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="M14" s="64" t="s">
+      <c r="M14" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="N14" s="64" t="s">
+      <c r="N14" s="71" t="s">
         <v>13</v>
       </c>
-      <c r="O14" s="64" t="s">
+      <c r="O14" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="P14" s="64" t="s">
+      <c r="P14" s="72" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" ht="35.549999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="65"/>
-      <c r="B15" s="65"/>
-      <c r="C15" s="65"/>
-      <c r="D15" s="65"/>
-      <c r="E15" s="65"/>
-      <c r="F15" s="65"/>
-      <c r="G15" s="65"/>
-      <c r="H15" s="65"/>
-      <c r="I15" s="65"/>
-      <c r="J15" s="65"/>
-      <c r="K15" s="65"/>
-      <c r="L15" s="65"/>
-      <c r="M15" s="65"/>
-      <c r="N15" s="65"/>
-      <c r="O15" s="65"/>
-      <c r="P15" s="65"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A16" s="11" t="s">
+      <c r="R14">
+        <v>10</v>
+      </c>
+      <c r="S14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="35.549999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="73"/>
+      <c r="B15" s="63"/>
+      <c r="C15" s="63"/>
+      <c r="D15" s="63"/>
+      <c r="E15" s="63"/>
+      <c r="F15" s="63"/>
+      <c r="G15" s="63"/>
+      <c r="H15" s="63"/>
+      <c r="I15" s="63"/>
+      <c r="J15" s="63"/>
+      <c r="K15" s="63"/>
+      <c r="L15" s="63"/>
+      <c r="M15" s="63"/>
+      <c r="N15" s="63"/>
+      <c r="O15" s="63"/>
+      <c r="P15" s="74"/>
+      <c r="R15">
+        <v>11</v>
+      </c>
+      <c r="S15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A16" s="75" t="s">
         <v>16</v>
       </c>
       <c r="B16" s="13">
@@ -2064,25 +2162,47 @@
       <c r="D16" s="13">
         <v>0</v>
       </c>
-      <c r="E16" s="12"/>
+      <c r="E16" s="12">
+        <v>0</v>
+      </c>
       <c r="F16" s="13">
         <v>42</v>
       </c>
       <c r="G16" s="14">
         <v>44958</v>
       </c>
-      <c r="H16" s="12"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="12"/>
+      <c r="H16" s="12">
+        <v>11</v>
+      </c>
+      <c r="I16" s="15">
+        <f>B16/$B$23*100</f>
+        <v>17.887403502165316</v>
+      </c>
+      <c r="J16" s="12">
+        <f>B16+C16-F16</f>
+        <v>908</v>
+      </c>
+      <c r="K16" s="15">
+        <f>J16/$J$23*100</f>
+        <v>16.554238833181405</v>
+      </c>
+      <c r="L16" s="12">
+        <f>B16+C16*(E16/12)-F16*((12-H16)/12)</f>
+        <v>946.5</v>
+      </c>
       <c r="M16" s="16"/>
       <c r="N16" s="16"/>
       <c r="O16" s="16"/>
-      <c r="P16" s="16"/>
+      <c r="P16" s="76"/>
+      <c r="R16">
+        <v>12</v>
+      </c>
+      <c r="S16">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="75" t="s">
         <v>17</v>
       </c>
       <c r="B17" s="13">
@@ -2094,25 +2214,41 @@
       <c r="D17" s="14">
         <v>44986</v>
       </c>
-      <c r="E17" s="12"/>
+      <c r="E17" s="12">
+        <v>10</v>
+      </c>
       <c r="F17" s="13">
         <v>30</v>
       </c>
       <c r="G17" s="14">
         <v>45139</v>
       </c>
-      <c r="H17" s="12"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="15"/>
-      <c r="L17" s="12"/>
+      <c r="H17" s="12">
+        <v>5</v>
+      </c>
+      <c r="I17" s="15">
+        <f t="shared" ref="I17:I22" si="0">B17/$B$23*100</f>
+        <v>4.4436076068536998</v>
+      </c>
+      <c r="J17" s="12">
+        <f t="shared" ref="J17:J22" si="1">B17+C17-F17</f>
+        <v>219</v>
+      </c>
+      <c r="K17" s="15">
+        <f t="shared" ref="K17:K22" si="2">J17/$J$23*100</f>
+        <v>3.9927073837739289</v>
+      </c>
+      <c r="L17" s="12">
+        <f t="shared" ref="L17:L22" si="3">B17+C17*(E17/12)-F17*((12-H17)/12)</f>
+        <v>229.33333333333334</v>
+      </c>
       <c r="M17" s="16"/>
       <c r="N17" s="16"/>
       <c r="O17" s="16"/>
-      <c r="P17" s="16"/>
+      <c r="P17" s="76"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="75" t="s">
         <v>18</v>
       </c>
       <c r="B18" s="13">
@@ -2124,25 +2260,41 @@
       <c r="D18" s="14">
         <v>45047</v>
       </c>
-      <c r="E18" s="12"/>
+      <c r="E18" s="12">
+        <v>8</v>
+      </c>
       <c r="F18" s="13">
         <v>15</v>
       </c>
       <c r="G18" s="14">
         <v>45078</v>
       </c>
-      <c r="H18" s="12"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="15"/>
-      <c r="L18" s="12"/>
+      <c r="H18" s="12">
+        <v>7</v>
+      </c>
+      <c r="I18" s="15">
+        <f t="shared" si="0"/>
+        <v>50.837883637733007</v>
+      </c>
+      <c r="J18" s="12">
+        <f t="shared" si="1"/>
+        <v>2917</v>
+      </c>
+      <c r="K18" s="15">
+        <f t="shared" si="2"/>
+        <v>53.181403828623516</v>
+      </c>
+      <c r="L18" s="12">
+        <f t="shared" si="3"/>
+        <v>2848.4166666666665</v>
+      </c>
       <c r="M18" s="16"/>
       <c r="N18" s="16"/>
       <c r="O18" s="16"/>
-      <c r="P18" s="16"/>
+      <c r="P18" s="76"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="75" t="s">
         <v>19</v>
       </c>
       <c r="B19" s="13">
@@ -2154,25 +2306,41 @@
       <c r="D19" s="14">
         <v>45170</v>
       </c>
-      <c r="E19" s="12"/>
+      <c r="E19" s="12">
+        <v>4</v>
+      </c>
       <c r="F19" s="13">
         <v>8</v>
       </c>
       <c r="G19" s="14">
         <v>45261</v>
       </c>
-      <c r="H19" s="12"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="15"/>
-      <c r="L19" s="12"/>
+      <c r="H19" s="12">
+        <v>1</v>
+      </c>
+      <c r="I19" s="15">
+        <f t="shared" si="0"/>
+        <v>11.862172848804368</v>
+      </c>
+      <c r="J19" s="12">
+        <f t="shared" si="1"/>
+        <v>639</v>
+      </c>
+      <c r="K19" s="15">
+        <f t="shared" si="2"/>
+        <v>11.649954421148587</v>
+      </c>
+      <c r="L19" s="12">
+        <f t="shared" si="3"/>
+        <v>628.33333333333326</v>
+      </c>
       <c r="M19" s="16"/>
       <c r="N19" s="16"/>
       <c r="O19" s="16"/>
-      <c r="P19" s="16"/>
+      <c r="P19" s="76"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="75" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="13">
@@ -2184,25 +2352,41 @@
       <c r="D20" s="13">
         <v>0</v>
       </c>
-      <c r="E20" s="12"/>
+      <c r="E20" s="12">
+        <v>0</v>
+      </c>
       <c r="F20" s="13">
         <v>16</v>
       </c>
       <c r="G20" s="14">
         <v>44986</v>
       </c>
-      <c r="H20" s="12"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="12"/>
-      <c r="K20" s="15"/>
-      <c r="L20" s="12"/>
+      <c r="H20" s="12">
+        <v>10</v>
+      </c>
+      <c r="I20" s="15">
+        <f t="shared" si="0"/>
+        <v>4.236490303144417</v>
+      </c>
+      <c r="J20" s="12">
+        <f t="shared" si="1"/>
+        <v>209</v>
+      </c>
+      <c r="K20" s="15">
+        <f t="shared" si="2"/>
+        <v>3.8103919781221509</v>
+      </c>
+      <c r="L20" s="12">
+        <f t="shared" si="3"/>
+        <v>222.33333333333334</v>
+      </c>
       <c r="M20" s="16"/>
       <c r="N20" s="16"/>
       <c r="O20" s="16"/>
-      <c r="P20" s="16"/>
+      <c r="P20" s="76"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="75" t="s">
         <v>21</v>
       </c>
       <c r="B21" s="13">
@@ -2214,25 +2398,41 @@
       <c r="D21" s="14">
         <v>45078</v>
       </c>
-      <c r="E21" s="12"/>
+      <c r="E21" s="12">
+        <v>7</v>
+      </c>
       <c r="F21" s="13">
         <v>10</v>
       </c>
       <c r="G21" s="14">
         <v>45108</v>
       </c>
-      <c r="H21" s="12"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="15"/>
-      <c r="L21" s="12"/>
+      <c r="H21" s="12">
+        <v>6</v>
+      </c>
+      <c r="I21" s="15">
+        <f t="shared" si="0"/>
+        <v>8.8495575221238933</v>
+      </c>
+      <c r="J21" s="12">
+        <f t="shared" si="1"/>
+        <v>488</v>
+      </c>
+      <c r="K21" s="15">
+        <f t="shared" si="2"/>
+        <v>8.8969917958067448</v>
+      </c>
+      <c r="L21" s="12">
+        <f t="shared" si="3"/>
+        <v>481.33333333333331</v>
+      </c>
       <c r="M21" s="16"/>
       <c r="N21" s="16"/>
       <c r="O21" s="16"/>
-      <c r="P21" s="16"/>
+      <c r="P21" s="76"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="75" t="s">
         <v>22</v>
       </c>
       <c r="B22" s="13">
@@ -2244,42 +2444,91 @@
       <c r="D22" s="14">
         <v>45017</v>
       </c>
-      <c r="E22" s="12"/>
+      <c r="E22" s="12">
+        <v>3</v>
+      </c>
       <c r="F22" s="13">
         <v>5</v>
       </c>
       <c r="G22" s="14">
         <v>45200</v>
       </c>
-      <c r="H22" s="12"/>
-      <c r="I22" s="15"/>
-      <c r="J22" s="12"/>
-      <c r="K22" s="15"/>
-      <c r="L22" s="12"/>
+      <c r="H22" s="12">
+        <v>3</v>
+      </c>
+      <c r="I22" s="15">
+        <f>B22/$B$23*100</f>
+        <v>1.8828845791752966</v>
+      </c>
+      <c r="J22" s="12">
+        <f t="shared" si="1"/>
+        <v>105</v>
+      </c>
+      <c r="K22" s="15">
+        <f t="shared" si="2"/>
+        <v>1.9143117593436645</v>
+      </c>
+      <c r="L22" s="12">
+        <f t="shared" si="3"/>
+        <v>98.75</v>
+      </c>
       <c r="M22" s="16"/>
       <c r="N22" s="16"/>
       <c r="O22" s="16"/>
-      <c r="P22" s="16"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A23" s="17" t="s">
+      <c r="P22" s="76"/>
+    </row>
+    <row r="23" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="21"/>
-      <c r="K23" s="21"/>
-      <c r="L23" s="18"/>
-      <c r="M23" s="20"/>
-      <c r="N23" s="20"/>
-      <c r="O23" s="19"/>
-      <c r="P23" s="19"/>
+      <c r="B23" s="78">
+        <f>SUM(B16:B22)</f>
+        <v>5311</v>
+      </c>
+      <c r="C23" s="79">
+        <f>SUM(C16:C22)</f>
+        <v>300</v>
+      </c>
+      <c r="D23" s="80"/>
+      <c r="E23" s="80"/>
+      <c r="F23" s="79">
+        <f>SUM(F16:F22)</f>
+        <v>126</v>
+      </c>
+      <c r="G23" s="80"/>
+      <c r="H23" s="80"/>
+      <c r="I23" s="78">
+        <f>SUM(I16:I22)</f>
+        <v>99.999999999999986</v>
+      </c>
+      <c r="J23" s="81">
+        <f>SUM(J16:J22)</f>
+        <v>5485</v>
+      </c>
+      <c r="K23" s="81">
+        <f>SUM(K16:K22)</f>
+        <v>100</v>
+      </c>
+      <c r="L23" s="78">
+        <f>SUM(L16:L22)</f>
+        <v>5454.9999999999991</v>
+      </c>
+      <c r="M23" s="82">
+        <f>C23/J23</f>
+        <v>5.4694621695533276E-2</v>
+      </c>
+      <c r="N23" s="82">
+        <f>F23/B23</f>
+        <v>2.3724345697608736E-2</v>
+      </c>
+      <c r="O23" s="81">
+        <f>(SUM(L18:L19,L21))/L23*100</f>
+        <v>72.558814543232515</v>
+      </c>
+      <c r="P23" s="83">
+        <f>(SUM(L16:L17,L20,L22))/L23*100</f>
+        <v>27.441185456767492</v>
+      </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A24" s="10" t="s">
@@ -2287,72 +2536,72 @@
       </c>
     </row>
     <row r="25" spans="1:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="64" t="s">
+      <c r="A25" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="B25" s="64" t="s">
+      <c r="B25" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="C25" s="64" t="s">
+      <c r="C25" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="64" t="s">
+      <c r="D25" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="E25" s="64" t="s">
+      <c r="E25" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="F25" s="64" t="s">
+      <c r="F25" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="G25" s="64" t="s">
+      <c r="G25" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="H25" s="64" t="s">
+      <c r="H25" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="I25" s="64" t="s">
+      <c r="I25" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="J25" s="64" t="s">
+      <c r="J25" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="K25" s="64" t="s">
+      <c r="K25" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="L25" s="64" t="s">
+      <c r="L25" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="M25" s="64" t="s">
+      <c r="M25" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="N25" s="64" t="s">
+      <c r="N25" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="O25" s="64" t="s">
+      <c r="O25" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="P25" s="64" t="s">
+      <c r="P25" s="62" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="65"/>
-      <c r="B26" s="65"/>
-      <c r="C26" s="65"/>
-      <c r="D26" s="65"/>
-      <c r="E26" s="65"/>
-      <c r="F26" s="65"/>
-      <c r="G26" s="65"/>
-      <c r="H26" s="65"/>
-      <c r="I26" s="65"/>
-      <c r="J26" s="65"/>
-      <c r="K26" s="65"/>
-      <c r="L26" s="65"/>
-      <c r="M26" s="65"/>
-      <c r="N26" s="65"/>
-      <c r="O26" s="65"/>
-      <c r="P26" s="65"/>
+      <c r="A26" s="63"/>
+      <c r="B26" s="63"/>
+      <c r="C26" s="63"/>
+      <c r="D26" s="63"/>
+      <c r="E26" s="63"/>
+      <c r="F26" s="63"/>
+      <c r="G26" s="63"/>
+      <c r="H26" s="63"/>
+      <c r="I26" s="63"/>
+      <c r="J26" s="63"/>
+      <c r="K26" s="63"/>
+      <c r="L26" s="63"/>
+      <c r="M26" s="63"/>
+      <c r="N26" s="63"/>
+      <c r="O26" s="63"/>
+      <c r="P26" s="63"/>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
@@ -2590,72 +2839,72 @@
       </c>
     </row>
     <row r="36" spans="1:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="64" t="s">
+      <c r="A36" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="B36" s="64" t="s">
+      <c r="B36" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="C36" s="64" t="s">
+      <c r="C36" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="D36" s="64" t="s">
+      <c r="D36" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="E36" s="64" t="s">
+      <c r="E36" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="F36" s="64" t="s">
+      <c r="F36" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="G36" s="64" t="s">
+      <c r="G36" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="H36" s="64" t="s">
+      <c r="H36" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="I36" s="64" t="s">
+      <c r="I36" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="J36" s="64" t="s">
+      <c r="J36" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="K36" s="64" t="s">
+      <c r="K36" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="L36" s="64" t="s">
+      <c r="L36" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="M36" s="64" t="s">
+      <c r="M36" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="N36" s="64" t="s">
+      <c r="N36" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="O36" s="64" t="s">
+      <c r="O36" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="P36" s="64" t="s">
+      <c r="P36" s="62" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="65"/>
-      <c r="B37" s="65"/>
-      <c r="C37" s="65"/>
-      <c r="D37" s="65"/>
-      <c r="E37" s="65"/>
-      <c r="F37" s="65"/>
-      <c r="G37" s="65"/>
-      <c r="H37" s="65"/>
-      <c r="I37" s="65"/>
-      <c r="J37" s="65"/>
-      <c r="K37" s="65"/>
-      <c r="L37" s="65"/>
-      <c r="M37" s="65"/>
-      <c r="N37" s="65"/>
-      <c r="O37" s="65"/>
-      <c r="P37" s="65"/>
+      <c r="A37" s="63"/>
+      <c r="B37" s="63"/>
+      <c r="C37" s="63"/>
+      <c r="D37" s="63"/>
+      <c r="E37" s="63"/>
+      <c r="F37" s="63"/>
+      <c r="G37" s="63"/>
+      <c r="H37" s="63"/>
+      <c r="I37" s="63"/>
+      <c r="J37" s="63"/>
+      <c r="K37" s="63"/>
+      <c r="L37" s="63"/>
+      <c r="M37" s="63"/>
+      <c r="N37" s="63"/>
+      <c r="O37" s="63"/>
+      <c r="P37" s="63"/>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
@@ -2893,72 +3142,72 @@
       </c>
     </row>
     <row r="47" spans="1:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="64" t="s">
+      <c r="A47" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="B47" s="64" t="s">
+      <c r="B47" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="C47" s="64" t="s">
+      <c r="C47" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="D47" s="64" t="s">
+      <c r="D47" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="E47" s="64" t="s">
+      <c r="E47" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="F47" s="64" t="s">
+      <c r="F47" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="G47" s="64" t="s">
+      <c r="G47" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="H47" s="64" t="s">
+      <c r="H47" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="I47" s="64" t="s">
+      <c r="I47" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="J47" s="64" t="s">
+      <c r="J47" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="K47" s="64" t="s">
+      <c r="K47" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="L47" s="64" t="s">
+      <c r="L47" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="M47" s="64" t="s">
+      <c r="M47" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="N47" s="64" t="s">
+      <c r="N47" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="O47" s="64" t="s">
+      <c r="O47" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="P47" s="64" t="s">
+      <c r="P47" s="62" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="48" spans="1:16" ht="37.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="65"/>
-      <c r="B48" s="65"/>
-      <c r="C48" s="65"/>
-      <c r="D48" s="65"/>
-      <c r="E48" s="65"/>
-      <c r="F48" s="65"/>
-      <c r="G48" s="65"/>
-      <c r="H48" s="65"/>
-      <c r="I48" s="65"/>
-      <c r="J48" s="65"/>
-      <c r="K48" s="65"/>
-      <c r="L48" s="65"/>
-      <c r="M48" s="65"/>
-      <c r="N48" s="65"/>
-      <c r="O48" s="65"/>
-      <c r="P48" s="65"/>
+      <c r="A48" s="63"/>
+      <c r="B48" s="63"/>
+      <c r="C48" s="63"/>
+      <c r="D48" s="63"/>
+      <c r="E48" s="63"/>
+      <c r="F48" s="63"/>
+      <c r="G48" s="63"/>
+      <c r="H48" s="63"/>
+      <c r="I48" s="63"/>
+      <c r="J48" s="63"/>
+      <c r="K48" s="63"/>
+      <c r="L48" s="63"/>
+      <c r="M48" s="63"/>
+      <c r="N48" s="63"/>
+      <c r="O48" s="63"/>
+      <c r="P48" s="63"/>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49" s="11" t="s">
@@ -3196,72 +3445,72 @@
       </c>
     </row>
     <row r="58" spans="1:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="64" t="s">
+      <c r="A58" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="B58" s="64" t="s">
+      <c r="B58" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="C58" s="64" t="s">
+      <c r="C58" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="D58" s="64" t="s">
+      <c r="D58" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="E58" s="64" t="s">
+      <c r="E58" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="F58" s="64" t="s">
+      <c r="F58" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="G58" s="64" t="s">
+      <c r="G58" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="H58" s="64" t="s">
+      <c r="H58" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="I58" s="64" t="s">
+      <c r="I58" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="J58" s="64" t="s">
+      <c r="J58" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="K58" s="64" t="s">
+      <c r="K58" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="L58" s="64" t="s">
+      <c r="L58" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="M58" s="64" t="s">
+      <c r="M58" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="N58" s="64" t="s">
+      <c r="N58" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="O58" s="64" t="s">
+      <c r="O58" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="P58" s="64" t="s">
+      <c r="P58" s="62" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="59" spans="1:16" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="65"/>
-      <c r="B59" s="65"/>
-      <c r="C59" s="65"/>
-      <c r="D59" s="65"/>
-      <c r="E59" s="65"/>
-      <c r="F59" s="65"/>
-      <c r="G59" s="65"/>
-      <c r="H59" s="65"/>
-      <c r="I59" s="65"/>
-      <c r="J59" s="65"/>
-      <c r="K59" s="65"/>
-      <c r="L59" s="65"/>
-      <c r="M59" s="65"/>
-      <c r="N59" s="65"/>
-      <c r="O59" s="65"/>
-      <c r="P59" s="65"/>
+      <c r="A59" s="63"/>
+      <c r="B59" s="63"/>
+      <c r="C59" s="63"/>
+      <c r="D59" s="63"/>
+      <c r="E59" s="63"/>
+      <c r="F59" s="63"/>
+      <c r="G59" s="63"/>
+      <c r="H59" s="63"/>
+      <c r="I59" s="63"/>
+      <c r="J59" s="63"/>
+      <c r="K59" s="63"/>
+      <c r="L59" s="63"/>
+      <c r="M59" s="63"/>
+      <c r="N59" s="63"/>
+      <c r="O59" s="63"/>
+      <c r="P59" s="63"/>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A60" s="11" t="s">
@@ -3499,72 +3748,72 @@
       </c>
     </row>
     <row r="69" spans="1:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="64" t="s">
+      <c r="A69" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="B69" s="64" t="s">
+      <c r="B69" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="C69" s="64" t="s">
+      <c r="C69" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="D69" s="64" t="s">
+      <c r="D69" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="E69" s="64" t="s">
+      <c r="E69" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="F69" s="64" t="s">
+      <c r="F69" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="G69" s="64" t="s">
+      <c r="G69" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="H69" s="64" t="s">
+      <c r="H69" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="I69" s="64" t="s">
+      <c r="I69" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="J69" s="64" t="s">
+      <c r="J69" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="K69" s="64" t="s">
+      <c r="K69" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="L69" s="64" t="s">
+      <c r="L69" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="M69" s="64" t="s">
+      <c r="M69" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="N69" s="64" t="s">
+      <c r="N69" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="O69" s="64" t="s">
+      <c r="O69" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="P69" s="64" t="s">
+      <c r="P69" s="62" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="70" spans="1:16" ht="39.299999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="65"/>
-      <c r="B70" s="65"/>
-      <c r="C70" s="65"/>
-      <c r="D70" s="65"/>
-      <c r="E70" s="65"/>
-      <c r="F70" s="65"/>
-      <c r="G70" s="65"/>
-      <c r="H70" s="65"/>
-      <c r="I70" s="65"/>
-      <c r="J70" s="65"/>
-      <c r="K70" s="65"/>
-      <c r="L70" s="65"/>
-      <c r="M70" s="65"/>
-      <c r="N70" s="65"/>
-      <c r="O70" s="65"/>
-      <c r="P70" s="65"/>
+      <c r="A70" s="63"/>
+      <c r="B70" s="63"/>
+      <c r="C70" s="63"/>
+      <c r="D70" s="63"/>
+      <c r="E70" s="63"/>
+      <c r="F70" s="63"/>
+      <c r="G70" s="63"/>
+      <c r="H70" s="63"/>
+      <c r="I70" s="63"/>
+      <c r="J70" s="63"/>
+      <c r="K70" s="63"/>
+      <c r="L70" s="63"/>
+      <c r="M70" s="63"/>
+      <c r="N70" s="63"/>
+      <c r="O70" s="63"/>
+      <c r="P70" s="63"/>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A71" s="11" t="s">
@@ -3802,72 +4051,72 @@
       </c>
     </row>
     <row r="80" spans="1:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="64" t="s">
+      <c r="A80" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="B80" s="64" t="s">
+      <c r="B80" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="C80" s="64" t="s">
+      <c r="C80" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="D80" s="64" t="s">
+      <c r="D80" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="E80" s="64" t="s">
+      <c r="E80" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="F80" s="64" t="s">
+      <c r="F80" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="G80" s="64" t="s">
+      <c r="G80" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="H80" s="64" t="s">
+      <c r="H80" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="I80" s="64" t="s">
+      <c r="I80" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="J80" s="64" t="s">
+      <c r="J80" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="K80" s="64" t="s">
+      <c r="K80" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="L80" s="64" t="s">
+      <c r="L80" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="M80" s="64" t="s">
+      <c r="M80" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="N80" s="64" t="s">
+      <c r="N80" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="O80" s="64" t="s">
+      <c r="O80" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="P80" s="64" t="s">
+      <c r="P80" s="62" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="81" spans="1:16" ht="38.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="65"/>
-      <c r="B81" s="65"/>
-      <c r="C81" s="65"/>
-      <c r="D81" s="65"/>
-      <c r="E81" s="65"/>
-      <c r="F81" s="65"/>
-      <c r="G81" s="65"/>
-      <c r="H81" s="65"/>
-      <c r="I81" s="65"/>
-      <c r="J81" s="65"/>
-      <c r="K81" s="65"/>
-      <c r="L81" s="65"/>
-      <c r="M81" s="65"/>
-      <c r="N81" s="65"/>
-      <c r="O81" s="65"/>
-      <c r="P81" s="65"/>
+      <c r="A81" s="63"/>
+      <c r="B81" s="63"/>
+      <c r="C81" s="63"/>
+      <c r="D81" s="63"/>
+      <c r="E81" s="63"/>
+      <c r="F81" s="63"/>
+      <c r="G81" s="63"/>
+      <c r="H81" s="63"/>
+      <c r="I81" s="63"/>
+      <c r="J81" s="63"/>
+      <c r="K81" s="63"/>
+      <c r="L81" s="63"/>
+      <c r="M81" s="63"/>
+      <c r="N81" s="63"/>
+      <c r="O81" s="63"/>
+      <c r="P81" s="63"/>
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A82" s="11" t="s">
@@ -4105,72 +4354,72 @@
       </c>
     </row>
     <row r="91" spans="1:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="64" t="s">
+      <c r="A91" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="B91" s="64" t="s">
+      <c r="B91" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="C91" s="64" t="s">
+      <c r="C91" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="D91" s="64" t="s">
+      <c r="D91" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="E91" s="64" t="s">
+      <c r="E91" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="F91" s="64" t="s">
+      <c r="F91" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="G91" s="64" t="s">
+      <c r="G91" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="H91" s="64" t="s">
+      <c r="H91" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="I91" s="64" t="s">
+      <c r="I91" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="J91" s="64" t="s">
+      <c r="J91" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="K91" s="64" t="s">
+      <c r="K91" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="L91" s="64" t="s">
+      <c r="L91" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="M91" s="64" t="s">
+      <c r="M91" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="N91" s="64" t="s">
+      <c r="N91" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="O91" s="64" t="s">
+      <c r="O91" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="P91" s="64" t="s">
+      <c r="P91" s="62" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="92" spans="1:16" ht="38.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="65"/>
-      <c r="B92" s="65"/>
-      <c r="C92" s="65"/>
-      <c r="D92" s="65"/>
-      <c r="E92" s="65"/>
-      <c r="F92" s="65"/>
-      <c r="G92" s="65"/>
-      <c r="H92" s="65"/>
-      <c r="I92" s="65"/>
-      <c r="J92" s="65"/>
-      <c r="K92" s="65"/>
-      <c r="L92" s="65"/>
-      <c r="M92" s="65"/>
-      <c r="N92" s="65"/>
-      <c r="O92" s="65"/>
-      <c r="P92" s="65"/>
+      <c r="A92" s="63"/>
+      <c r="B92" s="63"/>
+      <c r="C92" s="63"/>
+      <c r="D92" s="63"/>
+      <c r="E92" s="63"/>
+      <c r="F92" s="63"/>
+      <c r="G92" s="63"/>
+      <c r="H92" s="63"/>
+      <c r="I92" s="63"/>
+      <c r="J92" s="63"/>
+      <c r="K92" s="63"/>
+      <c r="L92" s="63"/>
+      <c r="M92" s="63"/>
+      <c r="N92" s="63"/>
+      <c r="O92" s="63"/>
+      <c r="P92" s="63"/>
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A93" s="11" t="s">
@@ -4408,72 +4657,72 @@
       </c>
     </row>
     <row r="102" spans="1:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="64" t="s">
+      <c r="A102" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="B102" s="64" t="s">
+      <c r="B102" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="C102" s="64" t="s">
+      <c r="C102" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="D102" s="64" t="s">
+      <c r="D102" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="E102" s="64" t="s">
+      <c r="E102" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="F102" s="64" t="s">
+      <c r="F102" s="62" t="s">
         <v>35</v>
       </c>
-      <c r="G102" s="64" t="s">
+      <c r="G102" s="62" t="s">
         <v>6</v>
       </c>
-      <c r="H102" s="64" t="s">
+      <c r="H102" s="62" t="s">
         <v>7</v>
       </c>
-      <c r="I102" s="64" t="s">
+      <c r="I102" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="J102" s="64" t="s">
+      <c r="J102" s="62" t="s">
         <v>9</v>
       </c>
-      <c r="K102" s="64" t="s">
+      <c r="K102" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="L102" s="64" t="s">
+      <c r="L102" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="M102" s="64" t="s">
+      <c r="M102" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="N102" s="64" t="s">
+      <c r="N102" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="O102" s="64" t="s">
+      <c r="O102" s="62" t="s">
         <v>14</v>
       </c>
-      <c r="P102" s="64" t="s">
+      <c r="P102" s="62" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="103" spans="1:16" ht="39.299999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="65"/>
-      <c r="B103" s="65"/>
-      <c r="C103" s="65"/>
-      <c r="D103" s="65"/>
-      <c r="E103" s="65"/>
-      <c r="F103" s="65"/>
-      <c r="G103" s="65"/>
-      <c r="H103" s="65"/>
-      <c r="I103" s="65"/>
-      <c r="J103" s="65"/>
-      <c r="K103" s="65"/>
-      <c r="L103" s="65"/>
-      <c r="M103" s="65"/>
-      <c r="N103" s="65"/>
-      <c r="O103" s="65"/>
-      <c r="P103" s="65"/>
+      <c r="A103" s="63"/>
+      <c r="B103" s="63"/>
+      <c r="C103" s="63"/>
+      <c r="D103" s="63"/>
+      <c r="E103" s="63"/>
+      <c r="F103" s="63"/>
+      <c r="G103" s="63"/>
+      <c r="H103" s="63"/>
+      <c r="I103" s="63"/>
+      <c r="J103" s="63"/>
+      <c r="K103" s="63"/>
+      <c r="L103" s="63"/>
+      <c r="M103" s="63"/>
+      <c r="N103" s="63"/>
+      <c r="O103" s="63"/>
+      <c r="P103" s="63"/>
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A104" s="11" t="s">
@@ -4707,6 +4956,142 @@
     </row>
   </sheetData>
   <mergeCells count="160">
+    <mergeCell ref="M102:M103"/>
+    <mergeCell ref="N102:N103"/>
+    <mergeCell ref="O102:O103"/>
+    <mergeCell ref="P102:P103"/>
+    <mergeCell ref="G102:G103"/>
+    <mergeCell ref="H102:H103"/>
+    <mergeCell ref="I102:I103"/>
+    <mergeCell ref="J102:J103"/>
+    <mergeCell ref="K102:K103"/>
+    <mergeCell ref="L102:L103"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="D102:D103"/>
+    <mergeCell ref="E102:E103"/>
+    <mergeCell ref="F102:F103"/>
+    <mergeCell ref="G91:G92"/>
+    <mergeCell ref="H91:H92"/>
+    <mergeCell ref="I91:I92"/>
+    <mergeCell ref="N80:N81"/>
+    <mergeCell ref="O80:O81"/>
+    <mergeCell ref="P80:P81"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="C91:C92"/>
+    <mergeCell ref="D91:D92"/>
+    <mergeCell ref="E91:E92"/>
+    <mergeCell ref="F91:F92"/>
+    <mergeCell ref="G80:G81"/>
+    <mergeCell ref="H80:H81"/>
+    <mergeCell ref="I80:I81"/>
+    <mergeCell ref="J80:J81"/>
+    <mergeCell ref="K80:K81"/>
+    <mergeCell ref="L80:L81"/>
+    <mergeCell ref="M91:M92"/>
+    <mergeCell ref="N91:N92"/>
+    <mergeCell ref="O91:O92"/>
+    <mergeCell ref="P91:P92"/>
+    <mergeCell ref="J91:J92"/>
+    <mergeCell ref="K91:K92"/>
+    <mergeCell ref="L91:L92"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="C80:C81"/>
+    <mergeCell ref="D80:D81"/>
+    <mergeCell ref="E80:E81"/>
+    <mergeCell ref="F80:F81"/>
+    <mergeCell ref="G69:G70"/>
+    <mergeCell ref="H69:H70"/>
+    <mergeCell ref="I69:I70"/>
+    <mergeCell ref="M58:M59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="M80:M81"/>
+    <mergeCell ref="N58:N59"/>
+    <mergeCell ref="O58:O59"/>
+    <mergeCell ref="P58:P59"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="B69:B70"/>
+    <mergeCell ref="C69:C70"/>
+    <mergeCell ref="D69:D70"/>
+    <mergeCell ref="E69:E70"/>
+    <mergeCell ref="F69:F70"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="L58:L59"/>
+    <mergeCell ref="M69:M70"/>
+    <mergeCell ref="N69:N70"/>
+    <mergeCell ref="O69:O70"/>
+    <mergeCell ref="P69:P70"/>
+    <mergeCell ref="J69:J70"/>
+    <mergeCell ref="K69:K70"/>
+    <mergeCell ref="L69:L70"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="M36:M37"/>
+    <mergeCell ref="N36:N37"/>
+    <mergeCell ref="O36:O37"/>
+    <mergeCell ref="P36:P37"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="I36:I37"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="K36:K37"/>
+    <mergeCell ref="L36:L37"/>
+    <mergeCell ref="M47:M48"/>
+    <mergeCell ref="N47:N48"/>
+    <mergeCell ref="O47:O48"/>
+    <mergeCell ref="P47:P48"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="L47:L48"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="O14:O15"/>
+    <mergeCell ref="P14:P15"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="M25:M26"/>
+    <mergeCell ref="N25:N26"/>
+    <mergeCell ref="O25:O26"/>
+    <mergeCell ref="P25:P26"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="K25:K26"/>
+    <mergeCell ref="L25:L26"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="N3:N4"/>
     <mergeCell ref="O3:O4"/>
@@ -4731,149 +5116,14 @@
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="M14:M15"/>
     <mergeCell ref="N14:N15"/>
-    <mergeCell ref="O14:O15"/>
-    <mergeCell ref="P14:P15"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="F25:F26"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="M25:M26"/>
-    <mergeCell ref="N25:N26"/>
-    <mergeCell ref="O25:O26"/>
-    <mergeCell ref="P25:P26"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="K25:K26"/>
-    <mergeCell ref="L25:L26"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="M36:M37"/>
-    <mergeCell ref="N36:N37"/>
-    <mergeCell ref="O36:O37"/>
-    <mergeCell ref="P36:P37"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="I36:I37"/>
-    <mergeCell ref="J36:J37"/>
-    <mergeCell ref="K36:K37"/>
-    <mergeCell ref="L36:L37"/>
-    <mergeCell ref="M47:M48"/>
-    <mergeCell ref="N47:N48"/>
-    <mergeCell ref="O47:O48"/>
-    <mergeCell ref="P47:P48"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="L47:L48"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="N58:N59"/>
-    <mergeCell ref="O58:O59"/>
-    <mergeCell ref="P58:P59"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="B69:B70"/>
-    <mergeCell ref="C69:C70"/>
-    <mergeCell ref="D69:D70"/>
-    <mergeCell ref="E69:E70"/>
-    <mergeCell ref="F69:F70"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="H58:H59"/>
-    <mergeCell ref="I58:I59"/>
-    <mergeCell ref="J58:J59"/>
-    <mergeCell ref="K58:K59"/>
-    <mergeCell ref="L58:L59"/>
-    <mergeCell ref="M69:M70"/>
-    <mergeCell ref="N69:N70"/>
-    <mergeCell ref="O69:O70"/>
-    <mergeCell ref="P69:P70"/>
-    <mergeCell ref="J69:J70"/>
-    <mergeCell ref="K69:K70"/>
-    <mergeCell ref="L69:L70"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C80:C81"/>
-    <mergeCell ref="D80:D81"/>
-    <mergeCell ref="E80:E81"/>
-    <mergeCell ref="F80:F81"/>
-    <mergeCell ref="G69:G70"/>
-    <mergeCell ref="H69:H70"/>
-    <mergeCell ref="I69:I70"/>
-    <mergeCell ref="M58:M59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="E58:E59"/>
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="M80:M81"/>
-    <mergeCell ref="N80:N81"/>
-    <mergeCell ref="O80:O81"/>
-    <mergeCell ref="P80:P81"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="C91:C92"/>
-    <mergeCell ref="D91:D92"/>
-    <mergeCell ref="E91:E92"/>
-    <mergeCell ref="F91:F92"/>
-    <mergeCell ref="G80:G81"/>
-    <mergeCell ref="H80:H81"/>
-    <mergeCell ref="I80:I81"/>
-    <mergeCell ref="J80:J81"/>
-    <mergeCell ref="K80:K81"/>
-    <mergeCell ref="L80:L81"/>
-    <mergeCell ref="M91:M92"/>
-    <mergeCell ref="N91:N92"/>
-    <mergeCell ref="O91:O92"/>
-    <mergeCell ref="P91:P92"/>
-    <mergeCell ref="J91:J92"/>
-    <mergeCell ref="K91:K92"/>
-    <mergeCell ref="L91:L92"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="C102:C103"/>
-    <mergeCell ref="D102:D103"/>
-    <mergeCell ref="E102:E103"/>
-    <mergeCell ref="F102:F103"/>
-    <mergeCell ref="G91:G92"/>
-    <mergeCell ref="H91:H92"/>
-    <mergeCell ref="I91:I92"/>
-    <mergeCell ref="M102:M103"/>
-    <mergeCell ref="N102:N103"/>
-    <mergeCell ref="O102:O103"/>
-    <mergeCell ref="P102:P103"/>
-    <mergeCell ref="G102:G103"/>
-    <mergeCell ref="H102:H103"/>
-    <mergeCell ref="I102:I103"/>
-    <mergeCell ref="J102:J103"/>
-    <mergeCell ref="K102:K103"/>
-    <mergeCell ref="L102:L103"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист3"/>
   <dimension ref="A1:A15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4955,7 +5205,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист4"/>
   <dimension ref="A1:K20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -4993,24 +5244,24 @@
       <c r="K2" s="28"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="66" t="s">
+      <c r="A3" s="64" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="67" t="s">
+      <c r="B3" s="65" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="67"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="65"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="66"/>
+      <c r="A4" s="64"/>
       <c r="B4" s="29">
         <v>1</v>
       </c>
@@ -5291,10 +5542,10 @@
       <c r="A12" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="B12" s="33">
+      <c r="B12" s="33"/>
+      <c r="C12" s="33">
         <v>9</v>
       </c>
-      <c r="C12" s="33"/>
       <c r="D12" s="33"/>
       <c r="E12" s="33"/>
       <c r="F12" s="33"/>
@@ -5378,10 +5629,10 @@
       <c r="A15" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="33">
+      <c r="B15" s="33"/>
+      <c r="C15" s="33">
         <v>10.5</v>
       </c>
-      <c r="C15" s="33"/>
       <c r="D15" s="33"/>
       <c r="E15" s="33"/>
       <c r="F15" s="33"/>
@@ -5430,11 +5681,11 @@
       <c r="A17" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="B17" s="36">
-        <f>(B5-SUM(B6:B9))+((B10/1000)*B12/12)-((B13/1000)*(12-B15)/12)</f>
-        <v>896</v>
-      </c>
-      <c r="C17" s="36"/>
+      <c r="B17" s="36"/>
+      <c r="C17" s="36">
+        <f>(C5-SUM(C6:C9))+((C10/1000)*C12/12)-((C13/1000)*(12-C15)/12)</f>
+        <v>1340</v>
+      </c>
       <c r="D17" s="36"/>
       <c r="E17" s="36"/>
       <c r="F17" s="36"/>
@@ -5448,11 +5699,11 @@
       <c r="A18" s="35" t="s">
         <v>63</v>
       </c>
-      <c r="B18" s="36">
-        <f>B16*100/B17</f>
-        <v>11.383928571428571</v>
-      </c>
-      <c r="C18" s="36"/>
+      <c r="B18" s="36"/>
+      <c r="C18" s="36">
+        <f>C16*100/C17</f>
+        <v>11.567164179104477</v>
+      </c>
       <c r="D18" s="36"/>
       <c r="E18" s="36"/>
       <c r="F18" s="36"/>
@@ -5501,11 +5752,11 @@
       <c r="A20" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="B20" s="41">
-        <f>B16*B19/B17</f>
-        <v>0.45535714285714285</v>
-      </c>
-      <c r="C20" s="41"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="41">
+        <f>C16*C19/C17</f>
+        <v>0.69402985074626866</v>
+      </c>
       <c r="D20" s="41"/>
       <c r="E20" s="41"/>
       <c r="F20" s="41"/>
@@ -5525,7 +5776,8 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист5"/>
   <dimension ref="A1:A13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -5599,13 +5851,15 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист1"/>
   <dimension ref="A1:W36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.88671875" customWidth="1"/>
     <col min="13" max="13" width="17.6640625" customWidth="1"/>
-    <col min="14" max="14" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="15" max="15" width="9.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="18" x14ac:dyDescent="0.35">
@@ -5672,29 +5926,29 @@
       </c>
     </row>
     <row r="3" spans="1:23" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="68" t="s">
+      <c r="A3" s="66" t="s">
         <v>100</v>
       </c>
-      <c r="B3" s="69" t="s">
+      <c r="B3" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="69"/>
-      <c r="K3" s="69"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="67"/>
+      <c r="K3" s="67"/>
       <c r="M3" s="46" t="s">
         <v>72</v>
       </c>
-      <c r="N3" s="47">
-        <f>N15/N9*100</f>
-        <v>93.81808278867102</v>
-      </c>
-      <c r="O3" s="47"/>
+      <c r="N3" s="47"/>
+      <c r="O3" s="47">
+        <f>O15/O9*100</f>
+        <v>98.00948794444173</v>
+      </c>
       <c r="P3" s="47"/>
       <c r="Q3" s="47"/>
       <c r="R3" s="47"/>
@@ -5705,7 +5959,7 @@
       <c r="W3" s="47"/>
     </row>
     <row r="4" spans="1:23" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="68"/>
+      <c r="A4" s="66"/>
       <c r="B4" s="48">
         <v>1</v>
       </c>
@@ -5739,11 +5993,11 @@
       <c r="M4" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="N4" s="47">
-        <f>N16/N10*100</f>
-        <v>106.58925979680696</v>
-      </c>
-      <c r="O4" s="47"/>
+      <c r="N4" s="47"/>
+      <c r="O4" s="47">
+        <f>O16/O10*100</f>
+        <v>106.88955422488355</v>
+      </c>
       <c r="P4" s="47"/>
       <c r="Q4" s="47"/>
       <c r="R4" s="47"/>
@@ -5770,11 +6024,11 @@
       <c r="M5" s="46" t="s">
         <v>75</v>
       </c>
-      <c r="N5" s="47">
-        <f>N17/N11*100</f>
-        <v>112.29946524064169</v>
-      </c>
-      <c r="O5" s="47"/>
+      <c r="N5" s="47"/>
+      <c r="O5" s="47">
+        <f>O17/O11*100</f>
+        <v>117.64705882352942</v>
+      </c>
       <c r="P5" s="47"/>
       <c r="Q5" s="47"/>
       <c r="R5" s="47"/>
@@ -5801,11 +6055,11 @@
       <c r="M6" s="46" t="s">
         <v>77</v>
       </c>
-      <c r="N6" s="47">
-        <f>N18/N12*100</f>
-        <v>112.65846453012227</v>
-      </c>
-      <c r="O6" s="47"/>
+      <c r="N6" s="47"/>
+      <c r="O6" s="47">
+        <f>O18/O12*100</f>
+        <v>118.56319694896986</v>
+      </c>
       <c r="P6" s="47"/>
       <c r="Q6" s="47"/>
       <c r="R6" s="47"/>
@@ -5852,11 +6106,11 @@
       <c r="M7" s="46" t="s">
         <v>79</v>
       </c>
-      <c r="N7" s="47">
-        <f>N19/N13*100</f>
-        <v>76.919339164237115</v>
-      </c>
-      <c r="O7" s="47"/>
+      <c r="N7" s="47"/>
+      <c r="O7" s="47">
+        <f>O19/O13*100</f>
+        <v>119.76911976911975</v>
+      </c>
       <c r="P7" s="47"/>
       <c r="Q7" s="47"/>
       <c r="R7" s="47"/>
@@ -5951,11 +6205,11 @@
       <c r="M9" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="N9" s="47">
-        <f>(B7*B11+B8*B12+B9*B13)/(B18*1000)</f>
-        <v>1.5793548387096774</v>
-      </c>
-      <c r="O9" s="47"/>
+      <c r="N9" s="47"/>
+      <c r="O9" s="47">
+        <f>(C7*C11+C8*C12+C9*C13)/(C18*1000)</f>
+        <v>2.0570422535211268</v>
+      </c>
       <c r="P9" s="47"/>
       <c r="Q9" s="47"/>
       <c r="R9" s="47"/>
@@ -5982,11 +6236,11 @@
       <c r="M10" s="46" t="s">
         <v>85</v>
       </c>
-      <c r="N10" s="47">
-        <f>B18*1000/(B7*B11+B8*B12+B9*B13)</f>
-        <v>0.63316993464052285</v>
-      </c>
-      <c r="O10" s="47"/>
+      <c r="N10" s="47"/>
+      <c r="O10" s="47">
+        <f>C18*1000/(C7*C11+C8*C12+C9*C13)</f>
+        <v>0.48613488531324889</v>
+      </c>
       <c r="P10" s="47"/>
       <c r="Q10" s="47"/>
       <c r="R10" s="47"/>
@@ -6033,11 +6287,11 @@
       <c r="M11" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="N11" s="47">
-        <f>B18*1000/B20</f>
-        <v>349.88713318284425</v>
-      </c>
-      <c r="O11" s="47"/>
+      <c r="N11" s="47"/>
+      <c r="O11" s="47">
+        <f>C18*1000/C20</f>
+        <v>217.79141104294479</v>
+      </c>
       <c r="P11" s="47"/>
       <c r="Q11" s="47"/>
       <c r="R11" s="47"/>
@@ -6084,11 +6338,11 @@
       <c r="M12" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="N12" s="47">
-        <f>(B18-B19)*1000/B20</f>
-        <v>322.79909706546277</v>
-      </c>
-      <c r="O12" s="47"/>
+      <c r="N12" s="47"/>
+      <c r="O12" s="47">
+        <f>(C18-C19)*1000/C20</f>
+        <v>197.85276073619633</v>
+      </c>
       <c r="P12" s="47"/>
       <c r="Q12" s="47"/>
       <c r="R12" s="47"/>
@@ -6135,11 +6389,11 @@
       <c r="M13" s="46" t="s">
         <v>88</v>
       </c>
-      <c r="N13" s="47">
-        <f>((B11-B15)*B7+(B12-B16)*B8+(B13-B17)*B9)/(B18*1000)*100</f>
-        <v>50.580645161290327</v>
-      </c>
-      <c r="O13" s="47"/>
+      <c r="N13" s="47"/>
+      <c r="O13" s="47">
+        <f>((C11-C15)*C7+(C12-C16)*C8+(C13-C17)*C9)/(C18*1000)*100</f>
+        <v>44.366197183098592</v>
+      </c>
       <c r="P13" s="47"/>
       <c r="Q13" s="47"/>
       <c r="R13" s="47"/>
@@ -6214,11 +6468,11 @@
       <c r="M15" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="N15" s="47">
-        <f>(B23*B27+B24*B28+B25*B29)/(((B18*105)/100)*1000)</f>
-        <v>1.4817204301075269</v>
-      </c>
-      <c r="O15" s="47"/>
+      <c r="N15" s="47"/>
+      <c r="O15" s="47">
+        <f>(C23*C27+C24*C28+C25*C29)/(((C18*105)/100)*1000)</f>
+        <v>2.0160965794768613</v>
+      </c>
       <c r="P15" s="47"/>
       <c r="Q15" s="47"/>
       <c r="R15" s="47"/>
@@ -6265,11 +6519,11 @@
       <c r="M16" s="46" t="s">
         <v>85</v>
       </c>
-      <c r="N16" s="47">
-        <f>(((B18*(100+B34))/100)*1000)/(B23*B27+B24*B28+B25*B29)</f>
-        <v>0.67489114658925975</v>
-      </c>
-      <c r="O16" s="47"/>
+      <c r="N16" s="47"/>
+      <c r="O16" s="47">
+        <f>(((C18*(100+C34))/100)*1000)/(C23*C27+C24*C28+C25*C29)</f>
+        <v>0.51962741184298067</v>
+      </c>
       <c r="P16" s="47"/>
       <c r="Q16" s="47"/>
       <c r="R16" s="47"/>
@@ -6316,11 +6570,11 @@
       <c r="M17" s="46" t="s">
         <v>86</v>
       </c>
-      <c r="N17" s="47">
-        <f>(((B18*(100+B34))/100)*1000)/((B20*(100-6.5))/100)</f>
-        <v>392.92137951014593</v>
-      </c>
-      <c r="O17" s="47"/>
+      <c r="N17" s="47"/>
+      <c r="O17" s="47">
+        <f>(((C18*(100+C34))/100)*1000)/((C20*(100-6.5))/100)</f>
+        <v>256.22518946228797</v>
+      </c>
       <c r="P17" s="47"/>
       <c r="Q17" s="47"/>
       <c r="R17" s="47"/>
@@ -6367,11 +6621,11 @@
       <c r="M18" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="N18" s="47">
-        <f>((((B18*(100+B34))/100)*1000)-(((B19*(100+B35))/100)*1000))/((B20*(100-6.5))/100)</f>
-        <v>363.66050627104937</v>
-      </c>
-      <c r="O18" s="47"/>
+      <c r="N18" s="47"/>
+      <c r="O18" s="47">
+        <f>((((C18*(100+C34))/100)*1000)-(((C19*(100+C35))/100)*1000))/((C20*(100-6.5))/100)</f>
+        <v>234.58055838063058</v>
+      </c>
       <c r="P18" s="47"/>
       <c r="Q18" s="47"/>
       <c r="R18" s="47"/>
@@ -6418,11 +6672,11 @@
       <c r="M19" s="46" t="s">
         <v>88</v>
       </c>
-      <c r="N19" s="47">
-        <f>((B27-B31)*B23+(B28-B32)*B24+(B29-B33)*B25)/(((B18*(100+B34))/100)*1000)*100</f>
-        <v>38.906298003072202</v>
-      </c>
-      <c r="O19" s="47"/>
+      <c r="N19" s="47"/>
+      <c r="O19" s="47">
+        <f>((C27-C31)*C23+(C28-C32)*C24+(C29-C33)*C25)/(((C18*(100+C34))/100)*1000)*100</f>
+        <v>53.137003841229188</v>
+      </c>
       <c r="P19" s="47"/>
       <c r="Q19" s="47"/>
       <c r="R19" s="47"/>
@@ -6964,12 +7218,13 @@
     <mergeCell ref="B3:K3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист6"/>
   <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7035,7 +7290,8 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист7"/>
   <dimension ref="A1:K24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7064,24 +7320,24 @@
       <c r="K2" s="28"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="66" t="s">
+      <c r="A3" s="64" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="67" t="s">
+      <c r="B3" s="65" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="67"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="65"/>
+      <c r="K3" s="65"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="66"/>
+      <c r="A4" s="64"/>
       <c r="B4" s="29">
         <v>1</v>
       </c>
@@ -7257,11 +7513,11 @@
       <c r="A9" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="B9" s="36">
-        <f>B8/B5*B7</f>
-        <v>2016</v>
-      </c>
-      <c r="C9" s="36"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="36">
+        <f>C8/C5*C7</f>
+        <v>335.45454545454544</v>
+      </c>
       <c r="D9" s="36"/>
       <c r="E9" s="36"/>
       <c r="F9" s="36"/>
@@ -7275,11 +7531,11 @@
       <c r="A10" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="B10" s="36">
-        <f>B8/B6*B7</f>
-        <v>2371.7647058823532</v>
-      </c>
-      <c r="C10" s="36"/>
+      <c r="B10" s="36"/>
+      <c r="C10" s="36">
+        <f>C8/C6*C7</f>
+        <v>553.5</v>
+      </c>
       <c r="D10" s="36"/>
       <c r="E10" s="36"/>
       <c r="F10" s="36"/>
@@ -7293,11 +7549,11 @@
       <c r="A11" s="35" t="s">
         <v>122</v>
       </c>
-      <c r="B11" s="36">
-        <f>B10-B9</f>
-        <v>355.76470588235316</v>
-      </c>
-      <c r="C11" s="36"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="36">
+        <f>C10-C9</f>
+        <v>218.04545454545456</v>
+      </c>
       <c r="D11" s="36"/>
       <c r="E11" s="36"/>
       <c r="F11" s="36"/>
@@ -7323,24 +7579,24 @@
       <c r="K13" s="28"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="66" t="s">
+      <c r="A14" s="64" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="67" t="s">
+      <c r="B14" s="65" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="67"/>
-      <c r="D14" s="67"/>
-      <c r="E14" s="67"/>
-      <c r="F14" s="67"/>
-      <c r="G14" s="67"/>
-      <c r="H14" s="67"/>
-      <c r="I14" s="67"/>
-      <c r="J14" s="67"/>
-      <c r="K14" s="67"/>
+      <c r="C14" s="65"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="65"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="65"/>
+      <c r="I14" s="65"/>
+      <c r="J14" s="65"/>
+      <c r="K14" s="65"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="66"/>
+      <c r="A15" s="64"/>
       <c r="B15" s="29">
         <v>1</v>
       </c>
@@ -7481,11 +7737,11 @@
       <c r="A19" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="B19" s="36">
-        <f>B16/B17</f>
-        <v>10.235294117647058</v>
-      </c>
-      <c r="C19" s="36"/>
+      <c r="B19" s="36"/>
+      <c r="C19" s="36">
+        <f>C16/C17</f>
+        <v>3.4358974358974357</v>
+      </c>
       <c r="D19" s="36"/>
       <c r="E19" s="36"/>
       <c r="F19" s="36"/>
@@ -7534,11 +7790,11 @@
       <c r="A21" s="32" t="s">
         <v>140</v>
       </c>
-      <c r="B21" s="36">
-        <f>B18/B19</f>
-        <v>35.172413793103452</v>
-      </c>
-      <c r="C21" s="36"/>
+      <c r="B21" s="36"/>
+      <c r="C21" s="36">
+        <f>C18/C19</f>
+        <v>104.77611940298507</v>
+      </c>
       <c r="D21" s="36"/>
       <c r="E21" s="36"/>
       <c r="F21" s="36"/>
@@ -7552,11 +7808,11 @@
       <c r="A22" s="32" t="s">
         <v>141</v>
       </c>
-      <c r="B22" s="36">
-        <f>B18/B20</f>
-        <v>30</v>
-      </c>
-      <c r="C22" s="36"/>
+      <c r="B22" s="36"/>
+      <c r="C22" s="36">
+        <f>C18/C20</f>
+        <v>72</v>
+      </c>
       <c r="D22" s="36"/>
       <c r="E22" s="36"/>
       <c r="F22" s="36"/>
@@ -7570,11 +7826,11 @@
       <c r="A23" s="35" t="s">
         <v>128</v>
       </c>
-      <c r="B23" s="36">
-        <f>B16/B20</f>
-        <v>725</v>
-      </c>
-      <c r="C23" s="36"/>
+      <c r="B23" s="36"/>
+      <c r="C23" s="36">
+        <f>C16/C20</f>
+        <v>134</v>
+      </c>
       <c r="D23" s="36"/>
       <c r="E23" s="36"/>
       <c r="F23" s="36"/>
@@ -7588,11 +7844,11 @@
       <c r="A24" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="B24" s="36">
-        <f>B23-B17</f>
-        <v>-125</v>
-      </c>
-      <c r="C24" s="36"/>
+      <c r="B24" s="36"/>
+      <c r="C24" s="36">
+        <f>C23-C17</f>
+        <v>-61</v>
+      </c>
       <c r="D24" s="36"/>
       <c r="E24" s="36"/>
       <c r="F24" s="36"/>
@@ -7615,7 +7871,8 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Лист8"/>
   <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>

--- a/3k2s/Экономика IT-компании/Лабораторная работа 1 ОС_с.xlsx
+++ b/3k2s/Экономика IT-компании/Лабораторная работа 1 ОС_с.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18252" windowHeight="6768" firstSheet="4" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18252" windowHeight="6768"/>
   </bookViews>
   <sheets>
     <sheet name="Задание 1 исх. данные, решение" sheetId="1" r:id="rId1"/>
@@ -1203,7 +1203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1336,43 +1336,10 @@
       <alignment horizontal="justify" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="8" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1391,6 +1358,42 @@
     </xf>
     <xf numFmtId="2" fontId="9" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1673,7 +1676,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Лист2"/>
-  <dimension ref="A1:S111"/>
+  <dimension ref="A1:AE111"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.44140625" customWidth="1"/>
@@ -1684,7 +1687,7 @@
     <col min="16" max="16" width="9.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>28</v>
       </c>
@@ -1698,80 +1701,80 @@
       <c r="I1" s="9"/>
       <c r="J1" s="9"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" s="62" t="s">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A3" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="62" t="s">
+      <c r="C3" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="62" t="s">
+      <c r="D3" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="62" t="s">
+      <c r="E3" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="62" t="s">
+      <c r="F3" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="62" t="s">
+      <c r="G3" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="62" t="s">
+      <c r="H3" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="62" t="s">
+      <c r="I3" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="62" t="s">
+      <c r="J3" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="62" t="s">
+      <c r="K3" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="L3" s="62" t="s">
+      <c r="L3" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="62" t="s">
+      <c r="M3" s="73" t="s">
         <v>12</v>
       </c>
-      <c r="N3" s="62" t="s">
+      <c r="N3" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="O3" s="62" t="s">
+      <c r="O3" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="P3" s="62" t="s">
+      <c r="P3" s="73" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="63"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="63"/>
-      <c r="K4" s="63"/>
-      <c r="L4" s="63"/>
-      <c r="M4" s="63"/>
-      <c r="N4" s="63"/>
-      <c r="O4" s="63"/>
-      <c r="P4" s="63"/>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="74"/>
+      <c r="B4" s="74"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+      <c r="J4" s="74"/>
+      <c r="K4" s="74"/>
+      <c r="L4" s="74"/>
+      <c r="M4" s="74"/>
+      <c r="N4" s="74"/>
+      <c r="O4" s="74"/>
+      <c r="P4" s="74"/>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>16</v>
       </c>
@@ -1795,19 +1798,13 @@
       <c r="I5" s="15"/>
       <c r="J5" s="12"/>
       <c r="K5" s="15"/>
-      <c r="L5" s="68"/>
+      <c r="L5" s="62"/>
       <c r="M5" s="16"/>
       <c r="N5" s="16"/>
       <c r="O5" s="16"/>
       <c r="P5" s="16"/>
-      <c r="R5">
-        <v>1</v>
-      </c>
-      <c r="S5">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>17</v>
       </c>
@@ -1831,20 +1828,14 @@
       <c r="I6" s="15"/>
       <c r="J6" s="12"/>
       <c r="K6" s="15"/>
-      <c r="L6" s="68"/>
+      <c r="L6" s="62"/>
       <c r="M6" s="16"/>
       <c r="N6" s="16"/>
       <c r="O6" s="16"/>
       <c r="P6" s="16"/>
-      <c r="R6">
-        <v>2</v>
-      </c>
-      <c r="S6">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A7" s="69" t="s">
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A7" s="63" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="12">
@@ -1867,20 +1858,14 @@
       <c r="I7" s="15"/>
       <c r="J7" s="12"/>
       <c r="K7" s="15"/>
-      <c r="L7" s="68"/>
+      <c r="L7" s="62"/>
       <c r="M7" s="16"/>
       <c r="N7" s="16"/>
       <c r="O7" s="16"/>
       <c r="P7" s="16"/>
-      <c r="R7">
-        <v>3</v>
-      </c>
-      <c r="S7">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A8" s="69" t="s">
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A8" s="63" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="12">
@@ -1903,20 +1888,14 @@
       <c r="I8" s="15"/>
       <c r="J8" s="12"/>
       <c r="K8" s="15"/>
-      <c r="L8" s="68"/>
+      <c r="L8" s="62"/>
       <c r="M8" s="16"/>
       <c r="N8" s="16"/>
       <c r="O8" s="16"/>
       <c r="P8" s="16"/>
-      <c r="R8">
-        <v>4</v>
-      </c>
-      <c r="S8">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A9" s="69" t="s">
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A9" s="63" t="s">
         <v>20</v>
       </c>
       <c r="B9" s="12">
@@ -1939,20 +1918,14 @@
       <c r="I9" s="15"/>
       <c r="J9" s="12"/>
       <c r="K9" s="15"/>
-      <c r="L9" s="68"/>
+      <c r="L9" s="62"/>
       <c r="M9" s="16"/>
       <c r="N9" s="16"/>
       <c r="O9" s="16"/>
       <c r="P9" s="16"/>
-      <c r="R9">
-        <v>5</v>
-      </c>
-      <c r="S9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A10" s="69" t="s">
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A10" s="63" t="s">
         <v>21</v>
       </c>
       <c r="B10" s="12">
@@ -1975,19 +1948,13 @@
       <c r="I10" s="15"/>
       <c r="J10" s="12"/>
       <c r="K10" s="15"/>
-      <c r="L10" s="68"/>
+      <c r="L10" s="62"/>
       <c r="M10" s="16"/>
       <c r="N10" s="16"/>
       <c r="O10" s="16"/>
       <c r="P10" s="16"/>
-      <c r="R10">
-        <v>6</v>
-      </c>
-      <c r="S10">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>22</v>
       </c>
@@ -2011,19 +1978,13 @@
       <c r="I11" s="15"/>
       <c r="J11" s="12"/>
       <c r="K11" s="15"/>
-      <c r="L11" s="68"/>
+      <c r="L11" s="62"/>
       <c r="M11" s="16"/>
       <c r="N11" s="16"/>
       <c r="O11" s="16"/>
       <c r="P11" s="16"/>
-      <c r="R11">
-        <v>7</v>
-      </c>
-      <c r="S11">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
         <v>23</v>
       </c>
@@ -2051,106 +2012,116 @@
       <c r="N12" s="20"/>
       <c r="O12" s="19"/>
       <c r="P12" s="19"/>
-      <c r="R12">
-        <v>8</v>
-      </c>
-      <c r="S12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="R13">
+    </row>
+    <row r="14" spans="1:31" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="78" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14" s="75" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="75" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="75" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="75" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="75" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" s="75" t="s">
+        <v>6</v>
+      </c>
+      <c r="H14" s="75" t="s">
+        <v>7</v>
+      </c>
+      <c r="I14" s="75" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="S13">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="70" t="s">
+      <c r="K14" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="L14" s="75" t="s">
+        <v>11</v>
+      </c>
+      <c r="M14" s="75" t="s">
+        <v>12</v>
+      </c>
+      <c r="N14" s="75" t="s">
+        <v>13</v>
+      </c>
+      <c r="O14" s="75" t="s">
+        <v>14</v>
+      </c>
+      <c r="P14" s="76" t="s">
+        <v>15</v>
+      </c>
+      <c r="R14">
+        <v>1</v>
+      </c>
+      <c r="S14">
+        <v>12</v>
+      </c>
+      <c r="U14" s="84"/>
+      <c r="V14" s="84"/>
+      <c r="W14" s="84"/>
+      <c r="X14" s="84"/>
+      <c r="Y14" s="84"/>
+      <c r="Z14" s="84"/>
+      <c r="AA14" s="84"/>
+      <c r="AB14" s="84"/>
+      <c r="AC14" s="84"/>
+      <c r="AD14" s="84"/>
+      <c r="AE14" s="84"/>
+    </row>
+    <row r="15" spans="1:31" ht="35.549999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="79"/>
+      <c r="B15" s="74"/>
+      <c r="C15" s="74"/>
+      <c r="D15" s="74"/>
+      <c r="E15" s="74"/>
+      <c r="F15" s="74"/>
+      <c r="G15" s="74"/>
+      <c r="H15" s="74"/>
+      <c r="I15" s="74"/>
+      <c r="J15" s="74"/>
+      <c r="K15" s="74"/>
+      <c r="L15" s="74"/>
+      <c r="M15" s="74"/>
+      <c r="N15" s="74"/>
+      <c r="O15" s="74"/>
+      <c r="P15" s="77"/>
+      <c r="R15">
         <v>2</v>
       </c>
-      <c r="B14" s="71" t="s">
-        <v>3</v>
-      </c>
-      <c r="C14" s="71" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" s="71" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="71" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="71" t="s">
-        <v>35</v>
-      </c>
-      <c r="G14" s="71" t="s">
-        <v>6</v>
-      </c>
-      <c r="H14" s="71" t="s">
-        <v>7</v>
-      </c>
-      <c r="I14" s="71" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="71" t="s">
-        <v>9</v>
-      </c>
-      <c r="K14" s="71" t="s">
-        <v>10</v>
-      </c>
-      <c r="L14" s="71" t="s">
+      <c r="S15">
         <v>11</v>
       </c>
-      <c r="M14" s="71" t="s">
-        <v>12</v>
-      </c>
-      <c r="N14" s="71" t="s">
-        <v>13</v>
-      </c>
-      <c r="O14" s="71" t="s">
-        <v>14</v>
-      </c>
-      <c r="P14" s="72" t="s">
-        <v>15</v>
-      </c>
-      <c r="R14">
-        <v>10</v>
-      </c>
-      <c r="S14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" ht="35.549999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="73"/>
-      <c r="B15" s="63"/>
-      <c r="C15" s="63"/>
-      <c r="D15" s="63"/>
-      <c r="E15" s="63"/>
-      <c r="F15" s="63"/>
-      <c r="G15" s="63"/>
-      <c r="H15" s="63"/>
-      <c r="I15" s="63"/>
-      <c r="J15" s="63"/>
-      <c r="K15" s="63"/>
-      <c r="L15" s="63"/>
-      <c r="M15" s="63"/>
-      <c r="N15" s="63"/>
-      <c r="O15" s="63"/>
-      <c r="P15" s="74"/>
-      <c r="R15">
-        <v>11</v>
-      </c>
-      <c r="S15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A16" s="75" t="s">
+      <c r="U15" s="84"/>
+      <c r="V15" s="84"/>
+      <c r="W15" s="84"/>
+      <c r="X15" s="84"/>
+      <c r="Y15" s="84"/>
+      <c r="Z15" s="84"/>
+      <c r="AA15" s="84"/>
+      <c r="AB15" s="84"/>
+      <c r="AC15" s="84"/>
+      <c r="AD15" s="84"/>
+      <c r="AE15" s="84"/>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A16" s="64" t="s">
         <v>16</v>
       </c>
       <c r="B16" s="13">
@@ -2193,16 +2164,27 @@
       <c r="M16" s="16"/>
       <c r="N16" s="16"/>
       <c r="O16" s="16"/>
-      <c r="P16" s="76"/>
+      <c r="P16" s="65"/>
       <c r="R16">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="S16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A17" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="U16" s="84"/>
+      <c r="V16" s="84"/>
+      <c r="W16" s="84"/>
+      <c r="X16" s="84"/>
+      <c r="Y16" s="84"/>
+      <c r="Z16" s="84"/>
+      <c r="AA16" s="84"/>
+      <c r="AB16" s="84"/>
+      <c r="AC16" s="84"/>
+      <c r="AD16" s="84"/>
+      <c r="AE16" s="84"/>
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A17" s="64" t="s">
         <v>17</v>
       </c>
       <c r="B17" s="13">
@@ -2227,7 +2209,7 @@
         <v>5</v>
       </c>
       <c r="I17" s="15">
-        <f t="shared" ref="I17:I22" si="0">B17/$B$23*100</f>
+        <f t="shared" ref="I17:I21" si="0">B17/$B$23*100</f>
         <v>4.4436076068536998</v>
       </c>
       <c r="J17" s="12">
@@ -2245,10 +2227,27 @@
       <c r="M17" s="16"/>
       <c r="N17" s="16"/>
       <c r="O17" s="16"/>
-      <c r="P17" s="76"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A18" s="75" t="s">
+      <c r="P17" s="65"/>
+      <c r="R17">
+        <v>4</v>
+      </c>
+      <c r="S17">
+        <v>9</v>
+      </c>
+      <c r="U17" s="84"/>
+      <c r="V17" s="84"/>
+      <c r="W17" s="84"/>
+      <c r="X17" s="84"/>
+      <c r="Y17" s="84"/>
+      <c r="Z17" s="84"/>
+      <c r="AA17" s="84"/>
+      <c r="AB17" s="84"/>
+      <c r="AC17" s="84"/>
+      <c r="AD17" s="84"/>
+      <c r="AE17" s="84"/>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A18" s="64" t="s">
         <v>18</v>
       </c>
       <c r="B18" s="13">
@@ -2291,10 +2290,27 @@
       <c r="M18" s="16"/>
       <c r="N18" s="16"/>
       <c r="O18" s="16"/>
-      <c r="P18" s="76"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A19" s="75" t="s">
+      <c r="P18" s="65"/>
+      <c r="R18">
+        <v>5</v>
+      </c>
+      <c r="S18">
+        <v>8</v>
+      </c>
+      <c r="U18" s="84"/>
+      <c r="V18" s="84"/>
+      <c r="W18" s="84"/>
+      <c r="X18" s="84"/>
+      <c r="Y18" s="84"/>
+      <c r="Z18" s="84"/>
+      <c r="AA18" s="84"/>
+      <c r="AB18" s="84"/>
+      <c r="AC18" s="84"/>
+      <c r="AD18" s="84"/>
+      <c r="AE18" s="84"/>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A19" s="64" t="s">
         <v>19</v>
       </c>
       <c r="B19" s="13">
@@ -2337,10 +2353,27 @@
       <c r="M19" s="16"/>
       <c r="N19" s="16"/>
       <c r="O19" s="16"/>
-      <c r="P19" s="76"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A20" s="75" t="s">
+      <c r="P19" s="65"/>
+      <c r="R19">
+        <v>6</v>
+      </c>
+      <c r="S19">
+        <v>7</v>
+      </c>
+      <c r="U19" s="84"/>
+      <c r="V19" s="84"/>
+      <c r="W19" s="84"/>
+      <c r="X19" s="84"/>
+      <c r="Y19" s="84"/>
+      <c r="Z19" s="84"/>
+      <c r="AA19" s="84"/>
+      <c r="AB19" s="84"/>
+      <c r="AC19" s="84"/>
+      <c r="AD19" s="84"/>
+      <c r="AE19" s="84"/>
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A20" s="64" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="13">
@@ -2383,10 +2416,27 @@
       <c r="M20" s="16"/>
       <c r="N20" s="16"/>
       <c r="O20" s="16"/>
-      <c r="P20" s="76"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A21" s="75" t="s">
+      <c r="P20" s="65"/>
+      <c r="R20">
+        <v>7</v>
+      </c>
+      <c r="S20">
+        <v>6</v>
+      </c>
+      <c r="U20" s="84"/>
+      <c r="V20" s="84"/>
+      <c r="W20" s="84"/>
+      <c r="X20" s="84"/>
+      <c r="Y20" s="84"/>
+      <c r="Z20" s="84"/>
+      <c r="AA20" s="84"/>
+      <c r="AB20" s="84"/>
+      <c r="AC20" s="84"/>
+      <c r="AD20" s="84"/>
+      <c r="AE20" s="84"/>
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A21" s="64" t="s">
         <v>21</v>
       </c>
       <c r="B21" s="13">
@@ -2429,10 +2479,27 @@
       <c r="M21" s="16"/>
       <c r="N21" s="16"/>
       <c r="O21" s="16"/>
-      <c r="P21" s="76"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A22" s="75" t="s">
+      <c r="P21" s="65"/>
+      <c r="R21">
+        <v>8</v>
+      </c>
+      <c r="S21">
+        <v>5</v>
+      </c>
+      <c r="U21" s="84"/>
+      <c r="V21" s="84"/>
+      <c r="W21" s="84"/>
+      <c r="X21" s="84"/>
+      <c r="Y21" s="84"/>
+      <c r="Z21" s="84"/>
+      <c r="AA21" s="84"/>
+      <c r="AB21" s="84"/>
+      <c r="AC21" s="84"/>
+      <c r="AD21" s="84"/>
+      <c r="AE21" s="84"/>
+    </row>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A22" s="64" t="s">
         <v>22</v>
       </c>
       <c r="B22" s="13">
@@ -2475,135 +2542,203 @@
       <c r="M22" s="16"/>
       <c r="N22" s="16"/>
       <c r="O22" s="16"/>
-      <c r="P22" s="76"/>
-    </row>
-    <row r="23" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="77" t="s">
+      <c r="P22" s="65"/>
+      <c r="R22">
+        <v>9</v>
+      </c>
+      <c r="S22">
+        <v>4</v>
+      </c>
+      <c r="U22" s="84"/>
+      <c r="V22" s="84"/>
+      <c r="W22" s="84"/>
+      <c r="X22" s="84"/>
+      <c r="Y22" s="84"/>
+      <c r="Z22" s="84"/>
+      <c r="AA22" s="84"/>
+      <c r="AB22" s="84"/>
+      <c r="AC22" s="84"/>
+      <c r="AD22" s="84"/>
+      <c r="AE22" s="84"/>
+    </row>
+    <row r="23" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="66" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="78">
+      <c r="B23" s="67">
         <f>SUM(B16:B22)</f>
         <v>5311</v>
       </c>
-      <c r="C23" s="79">
+      <c r="C23" s="68">
         <f>SUM(C16:C22)</f>
         <v>300</v>
       </c>
-      <c r="D23" s="80"/>
-      <c r="E23" s="80"/>
-      <c r="F23" s="79">
+      <c r="D23" s="69"/>
+      <c r="E23" s="69"/>
+      <c r="F23" s="68">
         <f>SUM(F16:F22)</f>
         <v>126</v>
       </c>
-      <c r="G23" s="80"/>
-      <c r="H23" s="80"/>
-      <c r="I23" s="78">
+      <c r="G23" s="69"/>
+      <c r="H23" s="69"/>
+      <c r="I23" s="67">
         <f>SUM(I16:I22)</f>
         <v>99.999999999999986</v>
       </c>
-      <c r="J23" s="81">
+      <c r="J23" s="70">
         <f>SUM(J16:J22)</f>
         <v>5485</v>
       </c>
-      <c r="K23" s="81">
+      <c r="K23" s="70">
         <f>SUM(K16:K22)</f>
         <v>100</v>
       </c>
-      <c r="L23" s="78">
+      <c r="L23" s="67">
         <f>SUM(L16:L22)</f>
         <v>5454.9999999999991</v>
       </c>
-      <c r="M23" s="82">
+      <c r="M23" s="71">
         <f>C23/J23</f>
         <v>5.4694621695533276E-2</v>
       </c>
-      <c r="N23" s="82">
+      <c r="N23" s="71">
         <f>F23/B23</f>
         <v>2.3724345697608736E-2</v>
       </c>
-      <c r="O23" s="81">
+      <c r="O23" s="70">
         <f>(SUM(L18:L19,L21))/L23*100</f>
         <v>72.558814543232515</v>
       </c>
-      <c r="P23" s="83">
+      <c r="P23" s="72">
         <f>(SUM(L16:L17,L20,L22))/L23*100</f>
         <v>27.441185456767492</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R23">
+        <v>10</v>
+      </c>
+      <c r="S23">
+        <v>3</v>
+      </c>
+      <c r="U23" s="84"/>
+      <c r="V23" s="84"/>
+      <c r="W23" s="84"/>
+      <c r="X23" s="84"/>
+      <c r="Y23" s="84"/>
+      <c r="Z23" s="84"/>
+      <c r="AA23" s="84"/>
+      <c r="AB23" s="84"/>
+      <c r="AC23" s="84"/>
+      <c r="AD23" s="84"/>
+      <c r="AE23" s="84"/>
+    </row>
+    <row r="24" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A24" s="10" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="25" spans="1:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="62" t="s">
+      <c r="R24">
+        <v>11</v>
+      </c>
+      <c r="S24">
         <v>2</v>
       </c>
-      <c r="B25" s="62" t="s">
+      <c r="U24" s="84"/>
+      <c r="V24" s="84"/>
+      <c r="W24" s="84"/>
+      <c r="X24" s="84"/>
+      <c r="Y24" s="84"/>
+      <c r="Z24" s="84"/>
+      <c r="AA24" s="84"/>
+      <c r="AB24" s="84"/>
+      <c r="AC24" s="84"/>
+      <c r="AD24" s="84"/>
+      <c r="AE24" s="84"/>
+    </row>
+    <row r="25" spans="1:31" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="73" t="s">
+        <v>2</v>
+      </c>
+      <c r="B25" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="C25" s="62" t="s">
+      <c r="C25" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="62" t="s">
+      <c r="D25" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="E25" s="62" t="s">
+      <c r="E25" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="F25" s="62" t="s">
+      <c r="F25" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="G25" s="62" t="s">
+      <c r="G25" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="H25" s="62" t="s">
+      <c r="H25" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="I25" s="62" t="s">
+      <c r="I25" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="J25" s="62" t="s">
+      <c r="J25" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="K25" s="62" t="s">
+      <c r="K25" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="L25" s="62" t="s">
+      <c r="L25" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="M25" s="62" t="s">
+      <c r="M25" s="73" t="s">
         <v>12</v>
       </c>
-      <c r="N25" s="62" t="s">
+      <c r="N25" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="O25" s="62" t="s">
+      <c r="O25" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="P25" s="62" t="s">
+      <c r="P25" s="73" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="26" spans="1:16" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="63"/>
-      <c r="B26" s="63"/>
-      <c r="C26" s="63"/>
-      <c r="D26" s="63"/>
-      <c r="E26" s="63"/>
-      <c r="F26" s="63"/>
-      <c r="G26" s="63"/>
-      <c r="H26" s="63"/>
-      <c r="I26" s="63"/>
-      <c r="J26" s="63"/>
-      <c r="K26" s="63"/>
-      <c r="L26" s="63"/>
-      <c r="M26" s="63"/>
-      <c r="N26" s="63"/>
-      <c r="O26" s="63"/>
-      <c r="P26" s="63"/>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="R25">
+        <v>12</v>
+      </c>
+      <c r="S25">
+        <v>1</v>
+      </c>
+      <c r="U25" s="84"/>
+      <c r="V25" s="84"/>
+      <c r="W25" s="84"/>
+      <c r="X25" s="84"/>
+      <c r="Y25" s="84"/>
+      <c r="Z25" s="84"/>
+      <c r="AA25" s="84"/>
+      <c r="AB25" s="84"/>
+      <c r="AC25" s="84"/>
+      <c r="AD25" s="84"/>
+      <c r="AE25" s="84"/>
+    </row>
+    <row r="26" spans="1:31" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="74"/>
+      <c r="B26" s="74"/>
+      <c r="C26" s="74"/>
+      <c r="D26" s="74"/>
+      <c r="E26" s="74"/>
+      <c r="F26" s="74"/>
+      <c r="G26" s="74"/>
+      <c r="H26" s="74"/>
+      <c r="I26" s="74"/>
+      <c r="J26" s="74"/>
+      <c r="K26" s="74"/>
+      <c r="L26" s="74"/>
+      <c r="M26" s="74"/>
+      <c r="N26" s="74"/>
+      <c r="O26" s="74"/>
+      <c r="P26" s="74"/>
+    </row>
+    <row r="27" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>16</v>
       </c>
@@ -2633,7 +2768,7 @@
       <c r="O27" s="16"/>
       <c r="P27" s="16"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A28" s="11" t="s">
         <v>17</v>
       </c>
@@ -2663,7 +2798,7 @@
       <c r="O28" s="16"/>
       <c r="P28" s="16"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
         <v>18</v>
       </c>
@@ -2693,7 +2828,7 @@
       <c r="O29" s="16"/>
       <c r="P29" s="16"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>19</v>
       </c>
@@ -2723,7 +2858,7 @@
       <c r="O30" s="16"/>
       <c r="P30" s="16"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
         <v>20</v>
       </c>
@@ -2753,7 +2888,7 @@
       <c r="O31" s="16"/>
       <c r="P31" s="16"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
         <v>21</v>
       </c>
@@ -2839,72 +2974,72 @@
       </c>
     </row>
     <row r="36" spans="1:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="62" t="s">
+      <c r="A36" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="B36" s="62" t="s">
+      <c r="B36" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="C36" s="62" t="s">
+      <c r="C36" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="D36" s="62" t="s">
+      <c r="D36" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="E36" s="62" t="s">
+      <c r="E36" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="F36" s="62" t="s">
+      <c r="F36" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="G36" s="62" t="s">
+      <c r="G36" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="H36" s="62" t="s">
+      <c r="H36" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="I36" s="62" t="s">
+      <c r="I36" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="J36" s="62" t="s">
+      <c r="J36" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="K36" s="62" t="s">
+      <c r="K36" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="L36" s="62" t="s">
+      <c r="L36" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="M36" s="62" t="s">
+      <c r="M36" s="73" t="s">
         <v>12</v>
       </c>
-      <c r="N36" s="62" t="s">
+      <c r="N36" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="O36" s="62" t="s">
+      <c r="O36" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="P36" s="62" t="s">
+      <c r="P36" s="73" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="63"/>
-      <c r="B37" s="63"/>
-      <c r="C37" s="63"/>
-      <c r="D37" s="63"/>
-      <c r="E37" s="63"/>
-      <c r="F37" s="63"/>
-      <c r="G37" s="63"/>
-      <c r="H37" s="63"/>
-      <c r="I37" s="63"/>
-      <c r="J37" s="63"/>
-      <c r="K37" s="63"/>
-      <c r="L37" s="63"/>
-      <c r="M37" s="63"/>
-      <c r="N37" s="63"/>
-      <c r="O37" s="63"/>
-      <c r="P37" s="63"/>
+      <c r="A37" s="74"/>
+      <c r="B37" s="74"/>
+      <c r="C37" s="74"/>
+      <c r="D37" s="74"/>
+      <c r="E37" s="74"/>
+      <c r="F37" s="74"/>
+      <c r="G37" s="74"/>
+      <c r="H37" s="74"/>
+      <c r="I37" s="74"/>
+      <c r="J37" s="74"/>
+      <c r="K37" s="74"/>
+      <c r="L37" s="74"/>
+      <c r="M37" s="74"/>
+      <c r="N37" s="74"/>
+      <c r="O37" s="74"/>
+      <c r="P37" s="74"/>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
@@ -3142,72 +3277,72 @@
       </c>
     </row>
     <row r="47" spans="1:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="62" t="s">
+      <c r="A47" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="B47" s="62" t="s">
+      <c r="B47" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="C47" s="62" t="s">
+      <c r="C47" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="D47" s="62" t="s">
+      <c r="D47" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="E47" s="62" t="s">
+      <c r="E47" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="F47" s="62" t="s">
+      <c r="F47" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="G47" s="62" t="s">
+      <c r="G47" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="H47" s="62" t="s">
+      <c r="H47" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="I47" s="62" t="s">
+      <c r="I47" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="J47" s="62" t="s">
+      <c r="J47" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="K47" s="62" t="s">
+      <c r="K47" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="L47" s="62" t="s">
+      <c r="L47" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="M47" s="62" t="s">
+      <c r="M47" s="73" t="s">
         <v>12</v>
       </c>
-      <c r="N47" s="62" t="s">
+      <c r="N47" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="O47" s="62" t="s">
+      <c r="O47" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="P47" s="62" t="s">
+      <c r="P47" s="73" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="48" spans="1:16" ht="37.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="63"/>
-      <c r="B48" s="63"/>
-      <c r="C48" s="63"/>
-      <c r="D48" s="63"/>
-      <c r="E48" s="63"/>
-      <c r="F48" s="63"/>
-      <c r="G48" s="63"/>
-      <c r="H48" s="63"/>
-      <c r="I48" s="63"/>
-      <c r="J48" s="63"/>
-      <c r="K48" s="63"/>
-      <c r="L48" s="63"/>
-      <c r="M48" s="63"/>
-      <c r="N48" s="63"/>
-      <c r="O48" s="63"/>
-      <c r="P48" s="63"/>
+      <c r="A48" s="74"/>
+      <c r="B48" s="74"/>
+      <c r="C48" s="74"/>
+      <c r="D48" s="74"/>
+      <c r="E48" s="74"/>
+      <c r="F48" s="74"/>
+      <c r="G48" s="74"/>
+      <c r="H48" s="74"/>
+      <c r="I48" s="74"/>
+      <c r="J48" s="74"/>
+      <c r="K48" s="74"/>
+      <c r="L48" s="74"/>
+      <c r="M48" s="74"/>
+      <c r="N48" s="74"/>
+      <c r="O48" s="74"/>
+      <c r="P48" s="74"/>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49" s="11" t="s">
@@ -3445,72 +3580,72 @@
       </c>
     </row>
     <row r="58" spans="1:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="62" t="s">
+      <c r="A58" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="B58" s="62" t="s">
+      <c r="B58" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="C58" s="62" t="s">
+      <c r="C58" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="D58" s="62" t="s">
+      <c r="D58" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="E58" s="62" t="s">
+      <c r="E58" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="F58" s="62" t="s">
+      <c r="F58" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="G58" s="62" t="s">
+      <c r="G58" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="H58" s="62" t="s">
+      <c r="H58" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="I58" s="62" t="s">
+      <c r="I58" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="J58" s="62" t="s">
+      <c r="J58" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="K58" s="62" t="s">
+      <c r="K58" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="L58" s="62" t="s">
+      <c r="L58" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="M58" s="62" t="s">
+      <c r="M58" s="73" t="s">
         <v>12</v>
       </c>
-      <c r="N58" s="62" t="s">
+      <c r="N58" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="O58" s="62" t="s">
+      <c r="O58" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="P58" s="62" t="s">
+      <c r="P58" s="73" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="59" spans="1:16" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="63"/>
-      <c r="B59" s="63"/>
-      <c r="C59" s="63"/>
-      <c r="D59" s="63"/>
-      <c r="E59" s="63"/>
-      <c r="F59" s="63"/>
-      <c r="G59" s="63"/>
-      <c r="H59" s="63"/>
-      <c r="I59" s="63"/>
-      <c r="J59" s="63"/>
-      <c r="K59" s="63"/>
-      <c r="L59" s="63"/>
-      <c r="M59" s="63"/>
-      <c r="N59" s="63"/>
-      <c r="O59" s="63"/>
-      <c r="P59" s="63"/>
+      <c r="A59" s="74"/>
+      <c r="B59" s="74"/>
+      <c r="C59" s="74"/>
+      <c r="D59" s="74"/>
+      <c r="E59" s="74"/>
+      <c r="F59" s="74"/>
+      <c r="G59" s="74"/>
+      <c r="H59" s="74"/>
+      <c r="I59" s="74"/>
+      <c r="J59" s="74"/>
+      <c r="K59" s="74"/>
+      <c r="L59" s="74"/>
+      <c r="M59" s="74"/>
+      <c r="N59" s="74"/>
+      <c r="O59" s="74"/>
+      <c r="P59" s="74"/>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A60" s="11" t="s">
@@ -3748,72 +3883,72 @@
       </c>
     </row>
     <row r="69" spans="1:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="62" t="s">
+      <c r="A69" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="B69" s="62" t="s">
+      <c r="B69" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="C69" s="62" t="s">
+      <c r="C69" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="D69" s="62" t="s">
+      <c r="D69" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="E69" s="62" t="s">
+      <c r="E69" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="F69" s="62" t="s">
+      <c r="F69" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="G69" s="62" t="s">
+      <c r="G69" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="H69" s="62" t="s">
+      <c r="H69" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="I69" s="62" t="s">
+      <c r="I69" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="J69" s="62" t="s">
+      <c r="J69" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="K69" s="62" t="s">
+      <c r="K69" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="L69" s="62" t="s">
+      <c r="L69" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="M69" s="62" t="s">
+      <c r="M69" s="73" t="s">
         <v>12</v>
       </c>
-      <c r="N69" s="62" t="s">
+      <c r="N69" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="O69" s="62" t="s">
+      <c r="O69" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="P69" s="62" t="s">
+      <c r="P69" s="73" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="70" spans="1:16" ht="39.299999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="63"/>
-      <c r="B70" s="63"/>
-      <c r="C70" s="63"/>
-      <c r="D70" s="63"/>
-      <c r="E70" s="63"/>
-      <c r="F70" s="63"/>
-      <c r="G70" s="63"/>
-      <c r="H70" s="63"/>
-      <c r="I70" s="63"/>
-      <c r="J70" s="63"/>
-      <c r="K70" s="63"/>
-      <c r="L70" s="63"/>
-      <c r="M70" s="63"/>
-      <c r="N70" s="63"/>
-      <c r="O70" s="63"/>
-      <c r="P70" s="63"/>
+      <c r="A70" s="74"/>
+      <c r="B70" s="74"/>
+      <c r="C70" s="74"/>
+      <c r="D70" s="74"/>
+      <c r="E70" s="74"/>
+      <c r="F70" s="74"/>
+      <c r="G70" s="74"/>
+      <c r="H70" s="74"/>
+      <c r="I70" s="74"/>
+      <c r="J70" s="74"/>
+      <c r="K70" s="74"/>
+      <c r="L70" s="74"/>
+      <c r="M70" s="74"/>
+      <c r="N70" s="74"/>
+      <c r="O70" s="74"/>
+      <c r="P70" s="74"/>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A71" s="11" t="s">
@@ -4051,72 +4186,72 @@
       </c>
     </row>
     <row r="80" spans="1:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="62" t="s">
+      <c r="A80" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="B80" s="62" t="s">
+      <c r="B80" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="C80" s="62" t="s">
+      <c r="C80" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="D80" s="62" t="s">
+      <c r="D80" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="E80" s="62" t="s">
+      <c r="E80" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="F80" s="62" t="s">
+      <c r="F80" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="G80" s="62" t="s">
+      <c r="G80" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="H80" s="62" t="s">
+      <c r="H80" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="I80" s="62" t="s">
+      <c r="I80" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="J80" s="62" t="s">
+      <c r="J80" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="K80" s="62" t="s">
+      <c r="K80" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="L80" s="62" t="s">
+      <c r="L80" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="M80" s="62" t="s">
+      <c r="M80" s="73" t="s">
         <v>12</v>
       </c>
-      <c r="N80" s="62" t="s">
+      <c r="N80" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="O80" s="62" t="s">
+      <c r="O80" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="P80" s="62" t="s">
+      <c r="P80" s="73" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="81" spans="1:16" ht="38.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="63"/>
-      <c r="B81" s="63"/>
-      <c r="C81" s="63"/>
-      <c r="D81" s="63"/>
-      <c r="E81" s="63"/>
-      <c r="F81" s="63"/>
-      <c r="G81" s="63"/>
-      <c r="H81" s="63"/>
-      <c r="I81" s="63"/>
-      <c r="J81" s="63"/>
-      <c r="K81" s="63"/>
-      <c r="L81" s="63"/>
-      <c r="M81" s="63"/>
-      <c r="N81" s="63"/>
-      <c r="O81" s="63"/>
-      <c r="P81" s="63"/>
+      <c r="A81" s="74"/>
+      <c r="B81" s="74"/>
+      <c r="C81" s="74"/>
+      <c r="D81" s="74"/>
+      <c r="E81" s="74"/>
+      <c r="F81" s="74"/>
+      <c r="G81" s="74"/>
+      <c r="H81" s="74"/>
+      <c r="I81" s="74"/>
+      <c r="J81" s="74"/>
+      <c r="K81" s="74"/>
+      <c r="L81" s="74"/>
+      <c r="M81" s="74"/>
+      <c r="N81" s="74"/>
+      <c r="O81" s="74"/>
+      <c r="P81" s="74"/>
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A82" s="11" t="s">
@@ -4354,72 +4489,72 @@
       </c>
     </row>
     <row r="91" spans="1:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="62" t="s">
+      <c r="A91" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="B91" s="62" t="s">
+      <c r="B91" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="C91" s="62" t="s">
+      <c r="C91" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="D91" s="62" t="s">
+      <c r="D91" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="E91" s="62" t="s">
+      <c r="E91" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="F91" s="62" t="s">
+      <c r="F91" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="G91" s="62" t="s">
+      <c r="G91" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="H91" s="62" t="s">
+      <c r="H91" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="I91" s="62" t="s">
+      <c r="I91" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="J91" s="62" t="s">
+      <c r="J91" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="K91" s="62" t="s">
+      <c r="K91" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="L91" s="62" t="s">
+      <c r="L91" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="M91" s="62" t="s">
+      <c r="M91" s="73" t="s">
         <v>12</v>
       </c>
-      <c r="N91" s="62" t="s">
+      <c r="N91" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="O91" s="62" t="s">
+      <c r="O91" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="P91" s="62" t="s">
+      <c r="P91" s="73" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="92" spans="1:16" ht="38.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="63"/>
-      <c r="B92" s="63"/>
-      <c r="C92" s="63"/>
-      <c r="D92" s="63"/>
-      <c r="E92" s="63"/>
-      <c r="F92" s="63"/>
-      <c r="G92" s="63"/>
-      <c r="H92" s="63"/>
-      <c r="I92" s="63"/>
-      <c r="J92" s="63"/>
-      <c r="K92" s="63"/>
-      <c r="L92" s="63"/>
-      <c r="M92" s="63"/>
-      <c r="N92" s="63"/>
-      <c r="O92" s="63"/>
-      <c r="P92" s="63"/>
+      <c r="A92" s="74"/>
+      <c r="B92" s="74"/>
+      <c r="C92" s="74"/>
+      <c r="D92" s="74"/>
+      <c r="E92" s="74"/>
+      <c r="F92" s="74"/>
+      <c r="G92" s="74"/>
+      <c r="H92" s="74"/>
+      <c r="I92" s="74"/>
+      <c r="J92" s="74"/>
+      <c r="K92" s="74"/>
+      <c r="L92" s="74"/>
+      <c r="M92" s="74"/>
+      <c r="N92" s="74"/>
+      <c r="O92" s="74"/>
+      <c r="P92" s="74"/>
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A93" s="11" t="s">
@@ -4657,72 +4792,72 @@
       </c>
     </row>
     <row r="102" spans="1:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="62" t="s">
+      <c r="A102" s="73" t="s">
         <v>2</v>
       </c>
-      <c r="B102" s="62" t="s">
+      <c r="B102" s="73" t="s">
         <v>3</v>
       </c>
-      <c r="C102" s="62" t="s">
+      <c r="C102" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="D102" s="62" t="s">
+      <c r="D102" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="E102" s="62" t="s">
+      <c r="E102" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="F102" s="62" t="s">
+      <c r="F102" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="G102" s="62" t="s">
+      <c r="G102" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="H102" s="62" t="s">
+      <c r="H102" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="I102" s="62" t="s">
+      <c r="I102" s="73" t="s">
         <v>8</v>
       </c>
-      <c r="J102" s="62" t="s">
+      <c r="J102" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="K102" s="62" t="s">
+      <c r="K102" s="73" t="s">
         <v>10</v>
       </c>
-      <c r="L102" s="62" t="s">
+      <c r="L102" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="M102" s="62" t="s">
+      <c r="M102" s="73" t="s">
         <v>12</v>
       </c>
-      <c r="N102" s="62" t="s">
+      <c r="N102" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="O102" s="62" t="s">
+      <c r="O102" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="P102" s="62" t="s">
+      <c r="P102" s="73" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="103" spans="1:16" ht="39.299999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="63"/>
-      <c r="B103" s="63"/>
-      <c r="C103" s="63"/>
-      <c r="D103" s="63"/>
-      <c r="E103" s="63"/>
-      <c r="F103" s="63"/>
-      <c r="G103" s="63"/>
-      <c r="H103" s="63"/>
-      <c r="I103" s="63"/>
-      <c r="J103" s="63"/>
-      <c r="K103" s="63"/>
-      <c r="L103" s="63"/>
-      <c r="M103" s="63"/>
-      <c r="N103" s="63"/>
-      <c r="O103" s="63"/>
-      <c r="P103" s="63"/>
+      <c r="A103" s="74"/>
+      <c r="B103" s="74"/>
+      <c r="C103" s="74"/>
+      <c r="D103" s="74"/>
+      <c r="E103" s="74"/>
+      <c r="F103" s="74"/>
+      <c r="G103" s="74"/>
+      <c r="H103" s="74"/>
+      <c r="I103" s="74"/>
+      <c r="J103" s="74"/>
+      <c r="K103" s="74"/>
+      <c r="L103" s="74"/>
+      <c r="M103" s="74"/>
+      <c r="N103" s="74"/>
+      <c r="O103" s="74"/>
+      <c r="P103" s="74"/>
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A104" s="11" t="s">
@@ -4955,26 +5090,125 @@
       <c r="P111" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="160">
-    <mergeCell ref="M102:M103"/>
-    <mergeCell ref="N102:N103"/>
-    <mergeCell ref="O102:O103"/>
-    <mergeCell ref="P102:P103"/>
-    <mergeCell ref="G102:G103"/>
-    <mergeCell ref="H102:H103"/>
-    <mergeCell ref="I102:I103"/>
-    <mergeCell ref="J102:J103"/>
-    <mergeCell ref="K102:K103"/>
-    <mergeCell ref="L102:L103"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="C102:C103"/>
-    <mergeCell ref="D102:D103"/>
-    <mergeCell ref="E102:E103"/>
-    <mergeCell ref="F102:F103"/>
-    <mergeCell ref="G91:G92"/>
-    <mergeCell ref="H91:H92"/>
-    <mergeCell ref="I91:I92"/>
+  <mergeCells count="161">
+    <mergeCell ref="U14:AE25"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="P3:P4"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="M14:M15"/>
+    <mergeCell ref="N14:N15"/>
+    <mergeCell ref="O14:O15"/>
+    <mergeCell ref="P14:P15"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="M25:M26"/>
+    <mergeCell ref="N25:N26"/>
+    <mergeCell ref="O25:O26"/>
+    <mergeCell ref="P25:P26"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="K25:K26"/>
+    <mergeCell ref="L25:L26"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="M36:M37"/>
+    <mergeCell ref="N36:N37"/>
+    <mergeCell ref="O36:O37"/>
+    <mergeCell ref="P36:P37"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="I36:I37"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="K36:K37"/>
+    <mergeCell ref="L36:L37"/>
+    <mergeCell ref="M47:M48"/>
+    <mergeCell ref="N47:N48"/>
+    <mergeCell ref="O47:O48"/>
+    <mergeCell ref="P47:P48"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="L47:L48"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="N58:N59"/>
+    <mergeCell ref="O58:O59"/>
+    <mergeCell ref="P58:P59"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="B69:B70"/>
+    <mergeCell ref="C69:C70"/>
+    <mergeCell ref="D69:D70"/>
+    <mergeCell ref="E69:E70"/>
+    <mergeCell ref="F69:F70"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="L58:L59"/>
+    <mergeCell ref="M69:M70"/>
+    <mergeCell ref="N69:N70"/>
+    <mergeCell ref="O69:O70"/>
+    <mergeCell ref="P69:P70"/>
+    <mergeCell ref="J69:J70"/>
+    <mergeCell ref="K69:K70"/>
+    <mergeCell ref="L69:L70"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C80:C81"/>
+    <mergeCell ref="D80:D81"/>
+    <mergeCell ref="E80:E81"/>
+    <mergeCell ref="F80:F81"/>
+    <mergeCell ref="G69:G70"/>
+    <mergeCell ref="H69:H70"/>
+    <mergeCell ref="I69:I70"/>
+    <mergeCell ref="M58:M59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="M80:M81"/>
     <mergeCell ref="N80:N81"/>
     <mergeCell ref="O80:O81"/>
     <mergeCell ref="P80:P81"/>
@@ -4999,123 +5233,25 @@
     <mergeCell ref="L91:L92"/>
     <mergeCell ref="A80:A81"/>
     <mergeCell ref="B80:B81"/>
-    <mergeCell ref="C80:C81"/>
-    <mergeCell ref="D80:D81"/>
-    <mergeCell ref="E80:E81"/>
-    <mergeCell ref="F80:F81"/>
-    <mergeCell ref="G69:G70"/>
-    <mergeCell ref="H69:H70"/>
-    <mergeCell ref="I69:I70"/>
-    <mergeCell ref="M58:M59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="E58:E59"/>
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="M80:M81"/>
-    <mergeCell ref="N58:N59"/>
-    <mergeCell ref="O58:O59"/>
-    <mergeCell ref="P58:P59"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="B69:B70"/>
-    <mergeCell ref="C69:C70"/>
-    <mergeCell ref="D69:D70"/>
-    <mergeCell ref="E69:E70"/>
-    <mergeCell ref="F69:F70"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="H58:H59"/>
-    <mergeCell ref="I58:I59"/>
-    <mergeCell ref="J58:J59"/>
-    <mergeCell ref="K58:K59"/>
-    <mergeCell ref="L58:L59"/>
-    <mergeCell ref="M69:M70"/>
-    <mergeCell ref="N69:N70"/>
-    <mergeCell ref="O69:O70"/>
-    <mergeCell ref="P69:P70"/>
-    <mergeCell ref="J69:J70"/>
-    <mergeCell ref="K69:K70"/>
-    <mergeCell ref="L69:L70"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="M36:M37"/>
-    <mergeCell ref="N36:N37"/>
-    <mergeCell ref="O36:O37"/>
-    <mergeCell ref="P36:P37"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="I36:I37"/>
-    <mergeCell ref="J36:J37"/>
-    <mergeCell ref="K36:K37"/>
-    <mergeCell ref="L36:L37"/>
-    <mergeCell ref="M47:M48"/>
-    <mergeCell ref="N47:N48"/>
-    <mergeCell ref="O47:O48"/>
-    <mergeCell ref="P47:P48"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="L47:L48"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="O14:O15"/>
-    <mergeCell ref="P14:P15"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="F25:F26"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="M25:M26"/>
-    <mergeCell ref="N25:N26"/>
-    <mergeCell ref="O25:O26"/>
-    <mergeCell ref="P25:P26"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="K25:K26"/>
-    <mergeCell ref="L25:L26"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="M14:M15"/>
-    <mergeCell ref="N14:N15"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="D102:D103"/>
+    <mergeCell ref="E102:E103"/>
+    <mergeCell ref="F102:F103"/>
+    <mergeCell ref="G91:G92"/>
+    <mergeCell ref="H91:H92"/>
+    <mergeCell ref="I91:I92"/>
+    <mergeCell ref="M102:M103"/>
+    <mergeCell ref="N102:N103"/>
+    <mergeCell ref="O102:O103"/>
+    <mergeCell ref="P102:P103"/>
+    <mergeCell ref="G102:G103"/>
+    <mergeCell ref="H102:H103"/>
+    <mergeCell ref="I102:I103"/>
+    <mergeCell ref="J102:J103"/>
+    <mergeCell ref="K102:K103"/>
+    <mergeCell ref="L102:L103"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5244,24 +5380,24 @@
       <c r="K2" s="28"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="80" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="65" t="s">
+      <c r="B3" s="81" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="65"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="81"/>
+      <c r="K3" s="81"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="64"/>
+      <c r="A4" s="80"/>
       <c r="B4" s="29">
         <v>1</v>
       </c>
@@ -5926,21 +6062,21 @@
       </c>
     </row>
     <row r="3" spans="1:23" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="66" t="s">
+      <c r="A3" s="82" t="s">
         <v>100</v>
       </c>
-      <c r="B3" s="67" t="s">
+      <c r="B3" s="83" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="67"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="83"/>
+      <c r="I3" s="83"/>
+      <c r="J3" s="83"/>
+      <c r="K3" s="83"/>
       <c r="M3" s="46" t="s">
         <v>72</v>
       </c>
@@ -5959,7 +6095,7 @@
       <c r="W3" s="47"/>
     </row>
     <row r="4" spans="1:23" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="66"/>
+      <c r="A4" s="82"/>
       <c r="B4" s="48">
         <v>1</v>
       </c>
@@ -7320,24 +7456,24 @@
       <c r="K2" s="28"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="80" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="65" t="s">
+      <c r="B3" s="81" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="65"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="65"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
-      <c r="I3" s="65"/>
-      <c r="J3" s="65"/>
-      <c r="K3" s="65"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="81"/>
+      <c r="K3" s="81"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="64"/>
+      <c r="A4" s="80"/>
       <c r="B4" s="29">
         <v>1</v>
       </c>
@@ -7579,24 +7715,24 @@
       <c r="K13" s="28"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="64" t="s">
+      <c r="A14" s="80" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="65" t="s">
+      <c r="B14" s="81" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="65"/>
-      <c r="D14" s="65"/>
-      <c r="E14" s="65"/>
-      <c r="F14" s="65"/>
-      <c r="G14" s="65"/>
-      <c r="H14" s="65"/>
-      <c r="I14" s="65"/>
-      <c r="J14" s="65"/>
-      <c r="K14" s="65"/>
+      <c r="C14" s="81"/>
+      <c r="D14" s="81"/>
+      <c r="E14" s="81"/>
+      <c r="F14" s="81"/>
+      <c r="G14" s="81"/>
+      <c r="H14" s="81"/>
+      <c r="I14" s="81"/>
+      <c r="J14" s="81"/>
+      <c r="K14" s="81"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="64"/>
+      <c r="A15" s="80"/>
       <c r="B15" s="29">
         <v>1</v>
       </c>

--- a/3k2s/Экономика IT-компании/Лабораторная работа 1 ОС_с.xlsx
+++ b/3k2s/Экономика IT-компании/Лабораторная работа 1 ОС_с.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="18252" windowHeight="6768"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18252" windowHeight="6768" firstSheet="5" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Задание 1 исх. данные, решение" sheetId="1" r:id="rId1"/>
@@ -978,7 +978,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -999,6 +999,12 @@
     </fill>
     <fill>
       <patternFill patternType="lightUp"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="15">
@@ -1203,7 +1209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1359,10 +1365,19 @@
     <xf numFmtId="2" fontId="9" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="2" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="8" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1372,12 +1387,6 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="8" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1392,9 +1401,7 @@
     <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1707,72 +1714,72 @@
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A3" s="73" t="s">
+      <c r="A3" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="73" t="s">
+      <c r="B3" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="73" t="s">
+      <c r="C3" s="74" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="73" t="s">
+      <c r="D3" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="73" t="s">
+      <c r="E3" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="73" t="s">
+      <c r="F3" s="74" t="s">
         <v>35</v>
       </c>
-      <c r="G3" s="73" t="s">
+      <c r="G3" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="73" t="s">
+      <c r="H3" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="73" t="s">
+      <c r="I3" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="73" t="s">
+      <c r="J3" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="73" t="s">
+      <c r="K3" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="L3" s="73" t="s">
+      <c r="L3" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="M3" s="73" t="s">
+      <c r="M3" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="N3" s="73" t="s">
+      <c r="N3" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="O3" s="73" t="s">
+      <c r="O3" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="P3" s="73" t="s">
+      <c r="P3" s="74" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:31" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="74"/>
-      <c r="B4" s="74"/>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-      <c r="J4" s="74"/>
-      <c r="K4" s="74"/>
-      <c r="L4" s="74"/>
-      <c r="M4" s="74"/>
-      <c r="N4" s="74"/>
-      <c r="O4" s="74"/>
-      <c r="P4" s="74"/>
+      <c r="A4" s="75"/>
+      <c r="B4" s="75"/>
+      <c r="C4" s="75"/>
+      <c r="D4" s="75"/>
+      <c r="E4" s="75"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
+      <c r="K4" s="75"/>
+      <c r="L4" s="75"/>
+      <c r="M4" s="75"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="75"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
@@ -2019,52 +2026,52 @@
       </c>
     </row>
     <row r="14" spans="1:31" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="78" t="s">
+      <c r="A14" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="75" t="s">
+      <c r="B14" s="78" t="s">
         <v>3</v>
       </c>
-      <c r="C14" s="75" t="s">
+      <c r="C14" s="78" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="75" t="s">
+      <c r="D14" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="E14" s="75" t="s">
+      <c r="E14" s="78" t="s">
         <v>5</v>
       </c>
-      <c r="F14" s="75" t="s">
+      <c r="F14" s="78" t="s">
         <v>35</v>
       </c>
-      <c r="G14" s="75" t="s">
+      <c r="G14" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="H14" s="75" t="s">
+      <c r="H14" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="I14" s="75" t="s">
+      <c r="I14" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="75" t="s">
+      <c r="J14" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="K14" s="75" t="s">
+      <c r="K14" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="L14" s="75" t="s">
+      <c r="L14" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="M14" s="75" t="s">
+      <c r="M14" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="N14" s="75" t="s">
+      <c r="N14" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="O14" s="75" t="s">
+      <c r="O14" s="78" t="s">
         <v>14</v>
       </c>
-      <c r="P14" s="76" t="s">
+      <c r="P14" s="79" t="s">
         <v>15</v>
       </c>
       <c r="R14">
@@ -2073,52 +2080,52 @@
       <c r="S14">
         <v>12</v>
       </c>
-      <c r="U14" s="84"/>
-      <c r="V14" s="84"/>
-      <c r="W14" s="84"/>
-      <c r="X14" s="84"/>
-      <c r="Y14" s="84"/>
-      <c r="Z14" s="84"/>
-      <c r="AA14" s="84"/>
-      <c r="AB14" s="84"/>
-      <c r="AC14" s="84"/>
-      <c r="AD14" s="84"/>
-      <c r="AE14" s="84"/>
+      <c r="U14" s="73"/>
+      <c r="V14" s="73"/>
+      <c r="W14" s="73"/>
+      <c r="X14" s="73"/>
+      <c r="Y14" s="73"/>
+      <c r="Z14" s="73"/>
+      <c r="AA14" s="73"/>
+      <c r="AB14" s="73"/>
+      <c r="AC14" s="73"/>
+      <c r="AD14" s="73"/>
+      <c r="AE14" s="73"/>
     </row>
     <row r="15" spans="1:31" ht="35.549999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="79"/>
-      <c r="B15" s="74"/>
-      <c r="C15" s="74"/>
-      <c r="D15" s="74"/>
-      <c r="E15" s="74"/>
-      <c r="F15" s="74"/>
-      <c r="G15" s="74"/>
-      <c r="H15" s="74"/>
-      <c r="I15" s="74"/>
-      <c r="J15" s="74"/>
-      <c r="K15" s="74"/>
-      <c r="L15" s="74"/>
-      <c r="M15" s="74"/>
-      <c r="N15" s="74"/>
-      <c r="O15" s="74"/>
-      <c r="P15" s="77"/>
+      <c r="A15" s="77"/>
+      <c r="B15" s="75"/>
+      <c r="C15" s="75"/>
+      <c r="D15" s="75"/>
+      <c r="E15" s="75"/>
+      <c r="F15" s="75"/>
+      <c r="G15" s="75"/>
+      <c r="H15" s="75"/>
+      <c r="I15" s="75"/>
+      <c r="J15" s="75"/>
+      <c r="K15" s="75"/>
+      <c r="L15" s="75"/>
+      <c r="M15" s="75"/>
+      <c r="N15" s="75"/>
+      <c r="O15" s="75"/>
+      <c r="P15" s="80"/>
       <c r="R15">
         <v>2</v>
       </c>
       <c r="S15">
         <v>11</v>
       </c>
-      <c r="U15" s="84"/>
-      <c r="V15" s="84"/>
-      <c r="W15" s="84"/>
-      <c r="X15" s="84"/>
-      <c r="Y15" s="84"/>
-      <c r="Z15" s="84"/>
-      <c r="AA15" s="84"/>
-      <c r="AB15" s="84"/>
-      <c r="AC15" s="84"/>
-      <c r="AD15" s="84"/>
-      <c r="AE15" s="84"/>
+      <c r="U15" s="73"/>
+      <c r="V15" s="73"/>
+      <c r="W15" s="73"/>
+      <c r="X15" s="73"/>
+      <c r="Y15" s="73"/>
+      <c r="Z15" s="73"/>
+      <c r="AA15" s="73"/>
+      <c r="AB15" s="73"/>
+      <c r="AC15" s="73"/>
+      <c r="AD15" s="73"/>
+      <c r="AE15" s="73"/>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A16" s="64" t="s">
@@ -2143,7 +2150,7 @@
         <v>44958</v>
       </c>
       <c r="H16" s="12">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I16" s="15">
         <f>B16/$B$23*100</f>
@@ -2159,7 +2166,7 @@
       </c>
       <c r="L16" s="12">
         <f>B16+C16*(E16/12)-F16*((12-H16)/12)</f>
-        <v>946.5</v>
+        <v>911.5</v>
       </c>
       <c r="M16" s="16"/>
       <c r="N16" s="16"/>
@@ -2171,17 +2178,17 @@
       <c r="S16">
         <v>10</v>
       </c>
-      <c r="U16" s="84"/>
-      <c r="V16" s="84"/>
-      <c r="W16" s="84"/>
-      <c r="X16" s="84"/>
-      <c r="Y16" s="84"/>
-      <c r="Z16" s="84"/>
-      <c r="AA16" s="84"/>
-      <c r="AB16" s="84"/>
-      <c r="AC16" s="84"/>
-      <c r="AD16" s="84"/>
-      <c r="AE16" s="84"/>
+      <c r="U16" s="73"/>
+      <c r="V16" s="73"/>
+      <c r="W16" s="73"/>
+      <c r="X16" s="73"/>
+      <c r="Y16" s="73"/>
+      <c r="Z16" s="73"/>
+      <c r="AA16" s="73"/>
+      <c r="AB16" s="73"/>
+      <c r="AC16" s="73"/>
+      <c r="AD16" s="73"/>
+      <c r="AE16" s="73"/>
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A17" s="64" t="s">
@@ -2206,7 +2213,7 @@
         <v>45139</v>
       </c>
       <c r="H17" s="12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I17" s="15">
         <f t="shared" ref="I17:I21" si="0">B17/$B$23*100</f>
@@ -2222,7 +2229,7 @@
       </c>
       <c r="L17" s="12">
         <f t="shared" ref="L17:L22" si="3">B17+C17*(E17/12)-F17*((12-H17)/12)</f>
-        <v>229.33333333333334</v>
+        <v>234.33333333333334</v>
       </c>
       <c r="M17" s="16"/>
       <c r="N17" s="16"/>
@@ -2234,20 +2241,20 @@
       <c r="S17">
         <v>9</v>
       </c>
-      <c r="U17" s="84"/>
-      <c r="V17" s="84"/>
-      <c r="W17" s="84"/>
-      <c r="X17" s="84"/>
-      <c r="Y17" s="84"/>
-      <c r="Z17" s="84"/>
-      <c r="AA17" s="84"/>
-      <c r="AB17" s="84"/>
-      <c r="AC17" s="84"/>
-      <c r="AD17" s="84"/>
-      <c r="AE17" s="84"/>
+      <c r="U17" s="73"/>
+      <c r="V17" s="73"/>
+      <c r="W17" s="73"/>
+      <c r="X17" s="73"/>
+      <c r="Y17" s="73"/>
+      <c r="Z17" s="73"/>
+      <c r="AA17" s="73"/>
+      <c r="AB17" s="73"/>
+      <c r="AC17" s="73"/>
+      <c r="AD17" s="73"/>
+      <c r="AE17" s="73"/>
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A18" s="64" t="s">
+      <c r="A18" s="85" t="s">
         <v>18</v>
       </c>
       <c r="B18" s="13">
@@ -2269,7 +2276,7 @@
         <v>45078</v>
       </c>
       <c r="H18" s="12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I18" s="15">
         <f t="shared" si="0"/>
@@ -2285,7 +2292,7 @@
       </c>
       <c r="L18" s="12">
         <f t="shared" si="3"/>
-        <v>2848.4166666666665</v>
+        <v>2845.9166666666665</v>
       </c>
       <c r="M18" s="16"/>
       <c r="N18" s="16"/>
@@ -2297,20 +2304,20 @@
       <c r="S18">
         <v>8</v>
       </c>
-      <c r="U18" s="84"/>
-      <c r="V18" s="84"/>
-      <c r="W18" s="84"/>
-      <c r="X18" s="84"/>
-      <c r="Y18" s="84"/>
-      <c r="Z18" s="84"/>
-      <c r="AA18" s="84"/>
-      <c r="AB18" s="84"/>
-      <c r="AC18" s="84"/>
-      <c r="AD18" s="84"/>
-      <c r="AE18" s="84"/>
+      <c r="U18" s="73"/>
+      <c r="V18" s="73"/>
+      <c r="W18" s="73"/>
+      <c r="X18" s="73"/>
+      <c r="Y18" s="73"/>
+      <c r="Z18" s="73"/>
+      <c r="AA18" s="73"/>
+      <c r="AB18" s="73"/>
+      <c r="AC18" s="73"/>
+      <c r="AD18" s="73"/>
+      <c r="AE18" s="73"/>
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A19" s="64" t="s">
+      <c r="A19" s="85" t="s">
         <v>19</v>
       </c>
       <c r="B19" s="13">
@@ -2332,7 +2339,7 @@
         <v>45261</v>
       </c>
       <c r="H19" s="12">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I19" s="15">
         <f t="shared" si="0"/>
@@ -2348,7 +2355,7 @@
       </c>
       <c r="L19" s="12">
         <f t="shared" si="3"/>
-        <v>628.33333333333326</v>
+        <v>635</v>
       </c>
       <c r="M19" s="16"/>
       <c r="N19" s="16"/>
@@ -2360,17 +2367,17 @@
       <c r="S19">
         <v>7</v>
       </c>
-      <c r="U19" s="84"/>
-      <c r="V19" s="84"/>
-      <c r="W19" s="84"/>
-      <c r="X19" s="84"/>
-      <c r="Y19" s="84"/>
-      <c r="Z19" s="84"/>
-      <c r="AA19" s="84"/>
-      <c r="AB19" s="84"/>
-      <c r="AC19" s="84"/>
-      <c r="AD19" s="84"/>
-      <c r="AE19" s="84"/>
+      <c r="U19" s="73"/>
+      <c r="V19" s="73"/>
+      <c r="W19" s="73"/>
+      <c r="X19" s="73"/>
+      <c r="Y19" s="73"/>
+      <c r="Z19" s="73"/>
+      <c r="AA19" s="73"/>
+      <c r="AB19" s="73"/>
+      <c r="AC19" s="73"/>
+      <c r="AD19" s="73"/>
+      <c r="AE19" s="73"/>
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A20" s="64" t="s">
@@ -2395,7 +2402,7 @@
         <v>44986</v>
       </c>
       <c r="H20" s="12">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I20" s="15">
         <f t="shared" si="0"/>
@@ -2411,7 +2418,7 @@
       </c>
       <c r="L20" s="12">
         <f t="shared" si="3"/>
-        <v>222.33333333333334</v>
+        <v>211.66666666666666</v>
       </c>
       <c r="M20" s="16"/>
       <c r="N20" s="16"/>
@@ -2423,20 +2430,20 @@
       <c r="S20">
         <v>6</v>
       </c>
-      <c r="U20" s="84"/>
-      <c r="V20" s="84"/>
-      <c r="W20" s="84"/>
-      <c r="X20" s="84"/>
-      <c r="Y20" s="84"/>
-      <c r="Z20" s="84"/>
-      <c r="AA20" s="84"/>
-      <c r="AB20" s="84"/>
-      <c r="AC20" s="84"/>
-      <c r="AD20" s="84"/>
-      <c r="AE20" s="84"/>
+      <c r="U20" s="73"/>
+      <c r="V20" s="73"/>
+      <c r="W20" s="73"/>
+      <c r="X20" s="73"/>
+      <c r="Y20" s="73"/>
+      <c r="Z20" s="73"/>
+      <c r="AA20" s="73"/>
+      <c r="AB20" s="73"/>
+      <c r="AC20" s="73"/>
+      <c r="AD20" s="73"/>
+      <c r="AE20" s="73"/>
     </row>
     <row r="21" spans="1:31" x14ac:dyDescent="0.3">
-      <c r="A21" s="64" t="s">
+      <c r="A21" s="85" t="s">
         <v>21</v>
       </c>
       <c r="B21" s="13">
@@ -2486,17 +2493,17 @@
       <c r="S21">
         <v>5</v>
       </c>
-      <c r="U21" s="84"/>
-      <c r="V21" s="84"/>
-      <c r="W21" s="84"/>
-      <c r="X21" s="84"/>
-      <c r="Y21" s="84"/>
-      <c r="Z21" s="84"/>
-      <c r="AA21" s="84"/>
-      <c r="AB21" s="84"/>
-      <c r="AC21" s="84"/>
-      <c r="AD21" s="84"/>
-      <c r="AE21" s="84"/>
+      <c r="U21" s="73"/>
+      <c r="V21" s="73"/>
+      <c r="W21" s="73"/>
+      <c r="X21" s="73"/>
+      <c r="Y21" s="73"/>
+      <c r="Z21" s="73"/>
+      <c r="AA21" s="73"/>
+      <c r="AB21" s="73"/>
+      <c r="AC21" s="73"/>
+      <c r="AD21" s="73"/>
+      <c r="AE21" s="73"/>
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A22" s="64" t="s">
@@ -2512,7 +2519,7 @@
         <v>45017</v>
       </c>
       <c r="E22" s="12">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F22" s="13">
         <v>5</v>
@@ -2521,7 +2528,7 @@
         <v>45200</v>
       </c>
       <c r="H22" s="12">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I22" s="15">
         <f>B22/$B$23*100</f>
@@ -2537,7 +2544,7 @@
       </c>
       <c r="L22" s="12">
         <f t="shared" si="3"/>
-        <v>98.75</v>
+        <v>106.25</v>
       </c>
       <c r="M22" s="16"/>
       <c r="N22" s="16"/>
@@ -2549,17 +2556,17 @@
       <c r="S22">
         <v>4</v>
       </c>
-      <c r="U22" s="84"/>
-      <c r="V22" s="84"/>
-      <c r="W22" s="84"/>
-      <c r="X22" s="84"/>
-      <c r="Y22" s="84"/>
-      <c r="Z22" s="84"/>
-      <c r="AA22" s="84"/>
-      <c r="AB22" s="84"/>
-      <c r="AC22" s="84"/>
-      <c r="AD22" s="84"/>
-      <c r="AE22" s="84"/>
+      <c r="U22" s="73"/>
+      <c r="V22" s="73"/>
+      <c r="W22" s="73"/>
+      <c r="X22" s="73"/>
+      <c r="Y22" s="73"/>
+      <c r="Z22" s="73"/>
+      <c r="AA22" s="73"/>
+      <c r="AB22" s="73"/>
+      <c r="AC22" s="73"/>
+      <c r="AD22" s="73"/>
+      <c r="AE22" s="73"/>
     </row>
     <row r="23" spans="1:31" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="66" t="s">
@@ -2595,7 +2602,7 @@
       </c>
       <c r="L23" s="67">
         <f>SUM(L16:L22)</f>
-        <v>5454.9999999999991</v>
+        <v>5426</v>
       </c>
       <c r="M23" s="71">
         <f>C23/J23</f>
@@ -2607,11 +2614,11 @@
       </c>
       <c r="O23" s="70">
         <f>(SUM(L18:L19,L21))/L23*100</f>
-        <v>72.558814543232515</v>
+        <v>73.023405823811288</v>
       </c>
       <c r="P23" s="72">
         <f>(SUM(L16:L17,L20,L22))/L23*100</f>
-        <v>27.441185456767492</v>
+        <v>26.976594176188723</v>
       </c>
       <c r="R23">
         <v>10</v>
@@ -2619,17 +2626,17 @@
       <c r="S23">
         <v>3</v>
       </c>
-      <c r="U23" s="84"/>
-      <c r="V23" s="84"/>
-      <c r="W23" s="84"/>
-      <c r="X23" s="84"/>
-      <c r="Y23" s="84"/>
-      <c r="Z23" s="84"/>
-      <c r="AA23" s="84"/>
-      <c r="AB23" s="84"/>
-      <c r="AC23" s="84"/>
-      <c r="AD23" s="84"/>
-      <c r="AE23" s="84"/>
+      <c r="U23" s="73"/>
+      <c r="V23" s="73"/>
+      <c r="W23" s="73"/>
+      <c r="X23" s="73"/>
+      <c r="Y23" s="73"/>
+      <c r="Z23" s="73"/>
+      <c r="AA23" s="73"/>
+      <c r="AB23" s="73"/>
+      <c r="AC23" s="73"/>
+      <c r="AD23" s="73"/>
+      <c r="AE23" s="73"/>
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A24" s="10" t="s">
@@ -2641,65 +2648,65 @@
       <c r="S24">
         <v>2</v>
       </c>
-      <c r="U24" s="84"/>
-      <c r="V24" s="84"/>
-      <c r="W24" s="84"/>
-      <c r="X24" s="84"/>
-      <c r="Y24" s="84"/>
-      <c r="Z24" s="84"/>
-      <c r="AA24" s="84"/>
-      <c r="AB24" s="84"/>
-      <c r="AC24" s="84"/>
-      <c r="AD24" s="84"/>
-      <c r="AE24" s="84"/>
+      <c r="U24" s="73"/>
+      <c r="V24" s="73"/>
+      <c r="W24" s="73"/>
+      <c r="X24" s="73"/>
+      <c r="Y24" s="73"/>
+      <c r="Z24" s="73"/>
+      <c r="AA24" s="73"/>
+      <c r="AB24" s="73"/>
+      <c r="AC24" s="73"/>
+      <c r="AD24" s="73"/>
+      <c r="AE24" s="73"/>
     </row>
     <row r="25" spans="1:31" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="73" t="s">
+      <c r="A25" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="B25" s="73" t="s">
+      <c r="B25" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="C25" s="73" t="s">
+      <c r="C25" s="74" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="73" t="s">
+      <c r="D25" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="E25" s="73" t="s">
+      <c r="E25" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="F25" s="73" t="s">
+      <c r="F25" s="74" t="s">
         <v>35</v>
       </c>
-      <c r="G25" s="73" t="s">
+      <c r="G25" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="H25" s="73" t="s">
+      <c r="H25" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="I25" s="73" t="s">
+      <c r="I25" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="J25" s="73" t="s">
+      <c r="J25" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="K25" s="73" t="s">
+      <c r="K25" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="L25" s="73" t="s">
+      <c r="L25" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="M25" s="73" t="s">
+      <c r="M25" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="N25" s="73" t="s">
+      <c r="N25" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="O25" s="73" t="s">
+      <c r="O25" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="P25" s="73" t="s">
+      <c r="P25" s="74" t="s">
         <v>15</v>
       </c>
       <c r="R25">
@@ -2708,35 +2715,35 @@
       <c r="S25">
         <v>1</v>
       </c>
-      <c r="U25" s="84"/>
-      <c r="V25" s="84"/>
-      <c r="W25" s="84"/>
-      <c r="X25" s="84"/>
-      <c r="Y25" s="84"/>
-      <c r="Z25" s="84"/>
-      <c r="AA25" s="84"/>
-      <c r="AB25" s="84"/>
-      <c r="AC25" s="84"/>
-      <c r="AD25" s="84"/>
-      <c r="AE25" s="84"/>
+      <c r="U25" s="73"/>
+      <c r="V25" s="73"/>
+      <c r="W25" s="73"/>
+      <c r="X25" s="73"/>
+      <c r="Y25" s="73"/>
+      <c r="Z25" s="73"/>
+      <c r="AA25" s="73"/>
+      <c r="AB25" s="73"/>
+      <c r="AC25" s="73"/>
+      <c r="AD25" s="73"/>
+      <c r="AE25" s="73"/>
     </row>
     <row r="26" spans="1:31" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="74"/>
-      <c r="B26" s="74"/>
-      <c r="C26" s="74"/>
-      <c r="D26" s="74"/>
-      <c r="E26" s="74"/>
-      <c r="F26" s="74"/>
-      <c r="G26" s="74"/>
-      <c r="H26" s="74"/>
-      <c r="I26" s="74"/>
-      <c r="J26" s="74"/>
-      <c r="K26" s="74"/>
-      <c r="L26" s="74"/>
-      <c r="M26" s="74"/>
-      <c r="N26" s="74"/>
-      <c r="O26" s="74"/>
-      <c r="P26" s="74"/>
+      <c r="A26" s="75"/>
+      <c r="B26" s="75"/>
+      <c r="C26" s="75"/>
+      <c r="D26" s="75"/>
+      <c r="E26" s="75"/>
+      <c r="F26" s="75"/>
+      <c r="G26" s="75"/>
+      <c r="H26" s="75"/>
+      <c r="I26" s="75"/>
+      <c r="J26" s="75"/>
+      <c r="K26" s="75"/>
+      <c r="L26" s="75"/>
+      <c r="M26" s="75"/>
+      <c r="N26" s="75"/>
+      <c r="O26" s="75"/>
+      <c r="P26" s="75"/>
     </row>
     <row r="27" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
@@ -2974,72 +2981,72 @@
       </c>
     </row>
     <row r="36" spans="1:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="73" t="s">
+      <c r="A36" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="B36" s="73" t="s">
+      <c r="B36" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="C36" s="73" t="s">
+      <c r="C36" s="74" t="s">
         <v>34</v>
       </c>
-      <c r="D36" s="73" t="s">
+      <c r="D36" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="E36" s="73" t="s">
+      <c r="E36" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="F36" s="73" t="s">
+      <c r="F36" s="74" t="s">
         <v>35</v>
       </c>
-      <c r="G36" s="73" t="s">
+      <c r="G36" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="H36" s="73" t="s">
+      <c r="H36" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="I36" s="73" t="s">
+      <c r="I36" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="J36" s="73" t="s">
+      <c r="J36" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="K36" s="73" t="s">
+      <c r="K36" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="L36" s="73" t="s">
+      <c r="L36" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="M36" s="73" t="s">
+      <c r="M36" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="N36" s="73" t="s">
+      <c r="N36" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="O36" s="73" t="s">
+      <c r="O36" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="P36" s="73" t="s">
+      <c r="P36" s="74" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="42.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="74"/>
-      <c r="B37" s="74"/>
-      <c r="C37" s="74"/>
-      <c r="D37" s="74"/>
-      <c r="E37" s="74"/>
-      <c r="F37" s="74"/>
-      <c r="G37" s="74"/>
-      <c r="H37" s="74"/>
-      <c r="I37" s="74"/>
-      <c r="J37" s="74"/>
-      <c r="K37" s="74"/>
-      <c r="L37" s="74"/>
-      <c r="M37" s="74"/>
-      <c r="N37" s="74"/>
-      <c r="O37" s="74"/>
-      <c r="P37" s="74"/>
+      <c r="A37" s="75"/>
+      <c r="B37" s="75"/>
+      <c r="C37" s="75"/>
+      <c r="D37" s="75"/>
+      <c r="E37" s="75"/>
+      <c r="F37" s="75"/>
+      <c r="G37" s="75"/>
+      <c r="H37" s="75"/>
+      <c r="I37" s="75"/>
+      <c r="J37" s="75"/>
+      <c r="K37" s="75"/>
+      <c r="L37" s="75"/>
+      <c r="M37" s="75"/>
+      <c r="N37" s="75"/>
+      <c r="O37" s="75"/>
+      <c r="P37" s="75"/>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
@@ -3277,72 +3284,72 @@
       </c>
     </row>
     <row r="47" spans="1:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="73" t="s">
+      <c r="A47" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="B47" s="73" t="s">
+      <c r="B47" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="C47" s="73" t="s">
+      <c r="C47" s="74" t="s">
         <v>34</v>
       </c>
-      <c r="D47" s="73" t="s">
+      <c r="D47" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="E47" s="73" t="s">
+      <c r="E47" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="F47" s="73" t="s">
+      <c r="F47" s="74" t="s">
         <v>35</v>
       </c>
-      <c r="G47" s="73" t="s">
+      <c r="G47" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="H47" s="73" t="s">
+      <c r="H47" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="I47" s="73" t="s">
+      <c r="I47" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="J47" s="73" t="s">
+      <c r="J47" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="K47" s="73" t="s">
+      <c r="K47" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="L47" s="73" t="s">
+      <c r="L47" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="M47" s="73" t="s">
+      <c r="M47" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="N47" s="73" t="s">
+      <c r="N47" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="O47" s="73" t="s">
+      <c r="O47" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="P47" s="73" t="s">
+      <c r="P47" s="74" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="48" spans="1:16" ht="37.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="74"/>
-      <c r="B48" s="74"/>
-      <c r="C48" s="74"/>
-      <c r="D48" s="74"/>
-      <c r="E48" s="74"/>
-      <c r="F48" s="74"/>
-      <c r="G48" s="74"/>
-      <c r="H48" s="74"/>
-      <c r="I48" s="74"/>
-      <c r="J48" s="74"/>
-      <c r="K48" s="74"/>
-      <c r="L48" s="74"/>
-      <c r="M48" s="74"/>
-      <c r="N48" s="74"/>
-      <c r="O48" s="74"/>
-      <c r="P48" s="74"/>
+      <c r="A48" s="75"/>
+      <c r="B48" s="75"/>
+      <c r="C48" s="75"/>
+      <c r="D48" s="75"/>
+      <c r="E48" s="75"/>
+      <c r="F48" s="75"/>
+      <c r="G48" s="75"/>
+      <c r="H48" s="75"/>
+      <c r="I48" s="75"/>
+      <c r="J48" s="75"/>
+      <c r="K48" s="75"/>
+      <c r="L48" s="75"/>
+      <c r="M48" s="75"/>
+      <c r="N48" s="75"/>
+      <c r="O48" s="75"/>
+      <c r="P48" s="75"/>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49" s="11" t="s">
@@ -3580,72 +3587,72 @@
       </c>
     </row>
     <row r="58" spans="1:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="73" t="s">
+      <c r="A58" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="B58" s="73" t="s">
+      <c r="B58" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="C58" s="73" t="s">
+      <c r="C58" s="74" t="s">
         <v>34</v>
       </c>
-      <c r="D58" s="73" t="s">
+      <c r="D58" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="E58" s="73" t="s">
+      <c r="E58" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="F58" s="73" t="s">
+      <c r="F58" s="74" t="s">
         <v>35</v>
       </c>
-      <c r="G58" s="73" t="s">
+      <c r="G58" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="H58" s="73" t="s">
+      <c r="H58" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="I58" s="73" t="s">
+      <c r="I58" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="J58" s="73" t="s">
+      <c r="J58" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="K58" s="73" t="s">
+      <c r="K58" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="L58" s="73" t="s">
+      <c r="L58" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="M58" s="73" t="s">
+      <c r="M58" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="N58" s="73" t="s">
+      <c r="N58" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="O58" s="73" t="s">
+      <c r="O58" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="P58" s="73" t="s">
+      <c r="P58" s="74" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="59" spans="1:16" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="74"/>
-      <c r="B59" s="74"/>
-      <c r="C59" s="74"/>
-      <c r="D59" s="74"/>
-      <c r="E59" s="74"/>
-      <c r="F59" s="74"/>
-      <c r="G59" s="74"/>
-      <c r="H59" s="74"/>
-      <c r="I59" s="74"/>
-      <c r="J59" s="74"/>
-      <c r="K59" s="74"/>
-      <c r="L59" s="74"/>
-      <c r="M59" s="74"/>
-      <c r="N59" s="74"/>
-      <c r="O59" s="74"/>
-      <c r="P59" s="74"/>
+      <c r="A59" s="75"/>
+      <c r="B59" s="75"/>
+      <c r="C59" s="75"/>
+      <c r="D59" s="75"/>
+      <c r="E59" s="75"/>
+      <c r="F59" s="75"/>
+      <c r="G59" s="75"/>
+      <c r="H59" s="75"/>
+      <c r="I59" s="75"/>
+      <c r="J59" s="75"/>
+      <c r="K59" s="75"/>
+      <c r="L59" s="75"/>
+      <c r="M59" s="75"/>
+      <c r="N59" s="75"/>
+      <c r="O59" s="75"/>
+      <c r="P59" s="75"/>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A60" s="11" t="s">
@@ -3883,72 +3890,72 @@
       </c>
     </row>
     <row r="69" spans="1:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="73" t="s">
+      <c r="A69" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="B69" s="73" t="s">
+      <c r="B69" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="C69" s="73" t="s">
+      <c r="C69" s="74" t="s">
         <v>34</v>
       </c>
-      <c r="D69" s="73" t="s">
+      <c r="D69" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="E69" s="73" t="s">
+      <c r="E69" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="F69" s="73" t="s">
+      <c r="F69" s="74" t="s">
         <v>35</v>
       </c>
-      <c r="G69" s="73" t="s">
+      <c r="G69" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="H69" s="73" t="s">
+      <c r="H69" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="I69" s="73" t="s">
+      <c r="I69" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="J69" s="73" t="s">
+      <c r="J69" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="K69" s="73" t="s">
+      <c r="K69" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="L69" s="73" t="s">
+      <c r="L69" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="M69" s="73" t="s">
+      <c r="M69" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="N69" s="73" t="s">
+      <c r="N69" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="O69" s="73" t="s">
+      <c r="O69" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="P69" s="73" t="s">
+      <c r="P69" s="74" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="70" spans="1:16" ht="39.299999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="74"/>
-      <c r="B70" s="74"/>
-      <c r="C70" s="74"/>
-      <c r="D70" s="74"/>
-      <c r="E70" s="74"/>
-      <c r="F70" s="74"/>
-      <c r="G70" s="74"/>
-      <c r="H70" s="74"/>
-      <c r="I70" s="74"/>
-      <c r="J70" s="74"/>
-      <c r="K70" s="74"/>
-      <c r="L70" s="74"/>
-      <c r="M70" s="74"/>
-      <c r="N70" s="74"/>
-      <c r="O70" s="74"/>
-      <c r="P70" s="74"/>
+      <c r="A70" s="75"/>
+      <c r="B70" s="75"/>
+      <c r="C70" s="75"/>
+      <c r="D70" s="75"/>
+      <c r="E70" s="75"/>
+      <c r="F70" s="75"/>
+      <c r="G70" s="75"/>
+      <c r="H70" s="75"/>
+      <c r="I70" s="75"/>
+      <c r="J70" s="75"/>
+      <c r="K70" s="75"/>
+      <c r="L70" s="75"/>
+      <c r="M70" s="75"/>
+      <c r="N70" s="75"/>
+      <c r="O70" s="75"/>
+      <c r="P70" s="75"/>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A71" s="11" t="s">
@@ -4186,72 +4193,72 @@
       </c>
     </row>
     <row r="80" spans="1:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="73" t="s">
+      <c r="A80" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="B80" s="73" t="s">
+      <c r="B80" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="C80" s="73" t="s">
+      <c r="C80" s="74" t="s">
         <v>34</v>
       </c>
-      <c r="D80" s="73" t="s">
+      <c r="D80" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="E80" s="73" t="s">
+      <c r="E80" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="F80" s="73" t="s">
+      <c r="F80" s="74" t="s">
         <v>35</v>
       </c>
-      <c r="G80" s="73" t="s">
+      <c r="G80" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="H80" s="73" t="s">
+      <c r="H80" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="I80" s="73" t="s">
+      <c r="I80" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="J80" s="73" t="s">
+      <c r="J80" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="K80" s="73" t="s">
+      <c r="K80" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="L80" s="73" t="s">
+      <c r="L80" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="M80" s="73" t="s">
+      <c r="M80" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="N80" s="73" t="s">
+      <c r="N80" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="O80" s="73" t="s">
+      <c r="O80" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="P80" s="73" t="s">
+      <c r="P80" s="74" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="81" spans="1:16" ht="38.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="74"/>
-      <c r="B81" s="74"/>
-      <c r="C81" s="74"/>
-      <c r="D81" s="74"/>
-      <c r="E81" s="74"/>
-      <c r="F81" s="74"/>
-      <c r="G81" s="74"/>
-      <c r="H81" s="74"/>
-      <c r="I81" s="74"/>
-      <c r="J81" s="74"/>
-      <c r="K81" s="74"/>
-      <c r="L81" s="74"/>
-      <c r="M81" s="74"/>
-      <c r="N81" s="74"/>
-      <c r="O81" s="74"/>
-      <c r="P81" s="74"/>
+      <c r="A81" s="75"/>
+      <c r="B81" s="75"/>
+      <c r="C81" s="75"/>
+      <c r="D81" s="75"/>
+      <c r="E81" s="75"/>
+      <c r="F81" s="75"/>
+      <c r="G81" s="75"/>
+      <c r="H81" s="75"/>
+      <c r="I81" s="75"/>
+      <c r="J81" s="75"/>
+      <c r="K81" s="75"/>
+      <c r="L81" s="75"/>
+      <c r="M81" s="75"/>
+      <c r="N81" s="75"/>
+      <c r="O81" s="75"/>
+      <c r="P81" s="75"/>
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A82" s="11" t="s">
@@ -4489,72 +4496,72 @@
       </c>
     </row>
     <row r="91" spans="1:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="73" t="s">
+      <c r="A91" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="B91" s="73" t="s">
+      <c r="B91" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="C91" s="73" t="s">
+      <c r="C91" s="74" t="s">
         <v>34</v>
       </c>
-      <c r="D91" s="73" t="s">
+      <c r="D91" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="E91" s="73" t="s">
+      <c r="E91" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="F91" s="73" t="s">
+      <c r="F91" s="74" t="s">
         <v>35</v>
       </c>
-      <c r="G91" s="73" t="s">
+      <c r="G91" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="H91" s="73" t="s">
+      <c r="H91" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="I91" s="73" t="s">
+      <c r="I91" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="J91" s="73" t="s">
+      <c r="J91" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="K91" s="73" t="s">
+      <c r="K91" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="L91" s="73" t="s">
+      <c r="L91" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="M91" s="73" t="s">
+      <c r="M91" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="N91" s="73" t="s">
+      <c r="N91" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="O91" s="73" t="s">
+      <c r="O91" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="P91" s="73" t="s">
+      <c r="P91" s="74" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="92" spans="1:16" ht="38.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="74"/>
-      <c r="B92" s="74"/>
-      <c r="C92" s="74"/>
-      <c r="D92" s="74"/>
-      <c r="E92" s="74"/>
-      <c r="F92" s="74"/>
-      <c r="G92" s="74"/>
-      <c r="H92" s="74"/>
-      <c r="I92" s="74"/>
-      <c r="J92" s="74"/>
-      <c r="K92" s="74"/>
-      <c r="L92" s="74"/>
-      <c r="M92" s="74"/>
-      <c r="N92" s="74"/>
-      <c r="O92" s="74"/>
-      <c r="P92" s="74"/>
+      <c r="A92" s="75"/>
+      <c r="B92" s="75"/>
+      <c r="C92" s="75"/>
+      <c r="D92" s="75"/>
+      <c r="E92" s="75"/>
+      <c r="F92" s="75"/>
+      <c r="G92" s="75"/>
+      <c r="H92" s="75"/>
+      <c r="I92" s="75"/>
+      <c r="J92" s="75"/>
+      <c r="K92" s="75"/>
+      <c r="L92" s="75"/>
+      <c r="M92" s="75"/>
+      <c r="N92" s="75"/>
+      <c r="O92" s="75"/>
+      <c r="P92" s="75"/>
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A93" s="11" t="s">
@@ -4792,72 +4799,72 @@
       </c>
     </row>
     <row r="102" spans="1:16" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="73" t="s">
+      <c r="A102" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="B102" s="73" t="s">
+      <c r="B102" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="C102" s="73" t="s">
+      <c r="C102" s="74" t="s">
         <v>34</v>
       </c>
-      <c r="D102" s="73" t="s">
+      <c r="D102" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="E102" s="73" t="s">
+      <c r="E102" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="F102" s="73" t="s">
+      <c r="F102" s="74" t="s">
         <v>35</v>
       </c>
-      <c r="G102" s="73" t="s">
+      <c r="G102" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="H102" s="73" t="s">
+      <c r="H102" s="74" t="s">
         <v>7</v>
       </c>
-      <c r="I102" s="73" t="s">
+      <c r="I102" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="J102" s="73" t="s">
+      <c r="J102" s="74" t="s">
         <v>9</v>
       </c>
-      <c r="K102" s="73" t="s">
+      <c r="K102" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="L102" s="73" t="s">
+      <c r="L102" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="M102" s="73" t="s">
+      <c r="M102" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="N102" s="73" t="s">
+      <c r="N102" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="O102" s="73" t="s">
+      <c r="O102" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="P102" s="73" t="s">
+      <c r="P102" s="74" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="103" spans="1:16" ht="39.299999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="74"/>
-      <c r="B103" s="74"/>
-      <c r="C103" s="74"/>
-      <c r="D103" s="74"/>
-      <c r="E103" s="74"/>
-      <c r="F103" s="74"/>
-      <c r="G103" s="74"/>
-      <c r="H103" s="74"/>
-      <c r="I103" s="74"/>
-      <c r="J103" s="74"/>
-      <c r="K103" s="74"/>
-      <c r="L103" s="74"/>
-      <c r="M103" s="74"/>
-      <c r="N103" s="74"/>
-      <c r="O103" s="74"/>
-      <c r="P103" s="74"/>
+      <c r="A103" s="75"/>
+      <c r="B103" s="75"/>
+      <c r="C103" s="75"/>
+      <c r="D103" s="75"/>
+      <c r="E103" s="75"/>
+      <c r="F103" s="75"/>
+      <c r="G103" s="75"/>
+      <c r="H103" s="75"/>
+      <c r="I103" s="75"/>
+      <c r="J103" s="75"/>
+      <c r="K103" s="75"/>
+      <c r="L103" s="75"/>
+      <c r="M103" s="75"/>
+      <c r="N103" s="75"/>
+      <c r="O103" s="75"/>
+      <c r="P103" s="75"/>
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A104" s="11" t="s">
@@ -5091,6 +5098,143 @@
     </row>
   </sheetData>
   <mergeCells count="161">
+    <mergeCell ref="M102:M103"/>
+    <mergeCell ref="N102:N103"/>
+    <mergeCell ref="O102:O103"/>
+    <mergeCell ref="P102:P103"/>
+    <mergeCell ref="G102:G103"/>
+    <mergeCell ref="H102:H103"/>
+    <mergeCell ref="I102:I103"/>
+    <mergeCell ref="J102:J103"/>
+    <mergeCell ref="K102:K103"/>
+    <mergeCell ref="L102:L103"/>
+    <mergeCell ref="A102:A103"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="C102:C103"/>
+    <mergeCell ref="D102:D103"/>
+    <mergeCell ref="E102:E103"/>
+    <mergeCell ref="F102:F103"/>
+    <mergeCell ref="G91:G92"/>
+    <mergeCell ref="H91:H92"/>
+    <mergeCell ref="I91:I92"/>
+    <mergeCell ref="N80:N81"/>
+    <mergeCell ref="O80:O81"/>
+    <mergeCell ref="P80:P81"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="B91:B92"/>
+    <mergeCell ref="C91:C92"/>
+    <mergeCell ref="D91:D92"/>
+    <mergeCell ref="E91:E92"/>
+    <mergeCell ref="F91:F92"/>
+    <mergeCell ref="G80:G81"/>
+    <mergeCell ref="H80:H81"/>
+    <mergeCell ref="I80:I81"/>
+    <mergeCell ref="J80:J81"/>
+    <mergeCell ref="K80:K81"/>
+    <mergeCell ref="L80:L81"/>
+    <mergeCell ref="M91:M92"/>
+    <mergeCell ref="N91:N92"/>
+    <mergeCell ref="O91:O92"/>
+    <mergeCell ref="P91:P92"/>
+    <mergeCell ref="J91:J92"/>
+    <mergeCell ref="K91:K92"/>
+    <mergeCell ref="L91:L92"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="C80:C81"/>
+    <mergeCell ref="D80:D81"/>
+    <mergeCell ref="E80:E81"/>
+    <mergeCell ref="F80:F81"/>
+    <mergeCell ref="G69:G70"/>
+    <mergeCell ref="H69:H70"/>
+    <mergeCell ref="I69:I70"/>
+    <mergeCell ref="M58:M59"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="D58:D59"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="M80:M81"/>
+    <mergeCell ref="N58:N59"/>
+    <mergeCell ref="O58:O59"/>
+    <mergeCell ref="P58:P59"/>
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="B69:B70"/>
+    <mergeCell ref="C69:C70"/>
+    <mergeCell ref="D69:D70"/>
+    <mergeCell ref="E69:E70"/>
+    <mergeCell ref="F69:F70"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="L58:L59"/>
+    <mergeCell ref="M69:M70"/>
+    <mergeCell ref="N69:N70"/>
+    <mergeCell ref="O69:O70"/>
+    <mergeCell ref="P69:P70"/>
+    <mergeCell ref="J69:J70"/>
+    <mergeCell ref="K69:K70"/>
+    <mergeCell ref="L69:L70"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="M36:M37"/>
+    <mergeCell ref="N36:N37"/>
+    <mergeCell ref="O36:O37"/>
+    <mergeCell ref="P36:P37"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="I36:I37"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="K36:K37"/>
+    <mergeCell ref="L36:L37"/>
+    <mergeCell ref="M47:M48"/>
+    <mergeCell ref="N47:N48"/>
+    <mergeCell ref="O47:O48"/>
+    <mergeCell ref="P47:P48"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="L47:L48"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G25:G26"/>
+    <mergeCell ref="H25:H26"/>
+    <mergeCell ref="I25:I26"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="N14:N15"/>
+    <mergeCell ref="O14:O15"/>
+    <mergeCell ref="P14:P15"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="E25:E26"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="J14:J15"/>
+    <mergeCell ref="K14:K15"/>
+    <mergeCell ref="L14:L15"/>
+    <mergeCell ref="M25:M26"/>
+    <mergeCell ref="N25:N26"/>
+    <mergeCell ref="O25:O26"/>
+    <mergeCell ref="P25:P26"/>
+    <mergeCell ref="J25:J26"/>
+    <mergeCell ref="K25:K26"/>
+    <mergeCell ref="L25:L26"/>
     <mergeCell ref="U14:AE25"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="N3:N4"/>
@@ -5115,143 +5259,6 @@
     <mergeCell ref="E3:E4"/>
     <mergeCell ref="F3:F4"/>
     <mergeCell ref="M14:M15"/>
-    <mergeCell ref="N14:N15"/>
-    <mergeCell ref="O14:O15"/>
-    <mergeCell ref="P14:P15"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="E25:E26"/>
-    <mergeCell ref="F25:F26"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="J14:J15"/>
-    <mergeCell ref="K14:K15"/>
-    <mergeCell ref="L14:L15"/>
-    <mergeCell ref="M25:M26"/>
-    <mergeCell ref="N25:N26"/>
-    <mergeCell ref="O25:O26"/>
-    <mergeCell ref="P25:P26"/>
-    <mergeCell ref="J25:J26"/>
-    <mergeCell ref="K25:K26"/>
-    <mergeCell ref="L25:L26"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:D37"/>
-    <mergeCell ref="E36:E37"/>
-    <mergeCell ref="F36:F37"/>
-    <mergeCell ref="G25:G26"/>
-    <mergeCell ref="H25:H26"/>
-    <mergeCell ref="I25:I26"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="M36:M37"/>
-    <mergeCell ref="N36:N37"/>
-    <mergeCell ref="O36:O37"/>
-    <mergeCell ref="P36:P37"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="G36:G37"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="I36:I37"/>
-    <mergeCell ref="J36:J37"/>
-    <mergeCell ref="K36:K37"/>
-    <mergeCell ref="L36:L37"/>
-    <mergeCell ref="M47:M48"/>
-    <mergeCell ref="N47:N48"/>
-    <mergeCell ref="O47:O48"/>
-    <mergeCell ref="P47:P48"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="L47:L48"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="N58:N59"/>
-    <mergeCell ref="O58:O59"/>
-    <mergeCell ref="P58:P59"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="B69:B70"/>
-    <mergeCell ref="C69:C70"/>
-    <mergeCell ref="D69:D70"/>
-    <mergeCell ref="E69:E70"/>
-    <mergeCell ref="F69:F70"/>
-    <mergeCell ref="G58:G59"/>
-    <mergeCell ref="H58:H59"/>
-    <mergeCell ref="I58:I59"/>
-    <mergeCell ref="J58:J59"/>
-    <mergeCell ref="K58:K59"/>
-    <mergeCell ref="L58:L59"/>
-    <mergeCell ref="M69:M70"/>
-    <mergeCell ref="N69:N70"/>
-    <mergeCell ref="O69:O70"/>
-    <mergeCell ref="P69:P70"/>
-    <mergeCell ref="J69:J70"/>
-    <mergeCell ref="K69:K70"/>
-    <mergeCell ref="L69:L70"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C80:C81"/>
-    <mergeCell ref="D80:D81"/>
-    <mergeCell ref="E80:E81"/>
-    <mergeCell ref="F80:F81"/>
-    <mergeCell ref="G69:G70"/>
-    <mergeCell ref="H69:H70"/>
-    <mergeCell ref="I69:I70"/>
-    <mergeCell ref="M58:M59"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="D58:D59"/>
-    <mergeCell ref="E58:E59"/>
-    <mergeCell ref="F58:F59"/>
-    <mergeCell ref="M80:M81"/>
-    <mergeCell ref="N80:N81"/>
-    <mergeCell ref="O80:O81"/>
-    <mergeCell ref="P80:P81"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="B91:B92"/>
-    <mergeCell ref="C91:C92"/>
-    <mergeCell ref="D91:D92"/>
-    <mergeCell ref="E91:E92"/>
-    <mergeCell ref="F91:F92"/>
-    <mergeCell ref="G80:G81"/>
-    <mergeCell ref="H80:H81"/>
-    <mergeCell ref="I80:I81"/>
-    <mergeCell ref="J80:J81"/>
-    <mergeCell ref="K80:K81"/>
-    <mergeCell ref="L80:L81"/>
-    <mergeCell ref="M91:M92"/>
-    <mergeCell ref="N91:N92"/>
-    <mergeCell ref="O91:O92"/>
-    <mergeCell ref="P91:P92"/>
-    <mergeCell ref="J91:J92"/>
-    <mergeCell ref="K91:K92"/>
-    <mergeCell ref="L91:L92"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="A102:A103"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="C102:C103"/>
-    <mergeCell ref="D102:D103"/>
-    <mergeCell ref="E102:E103"/>
-    <mergeCell ref="F102:F103"/>
-    <mergeCell ref="G91:G92"/>
-    <mergeCell ref="H91:H92"/>
-    <mergeCell ref="I91:I92"/>
-    <mergeCell ref="M102:M103"/>
-    <mergeCell ref="N102:N103"/>
-    <mergeCell ref="O102:O103"/>
-    <mergeCell ref="P102:P103"/>
-    <mergeCell ref="G102:G103"/>
-    <mergeCell ref="H102:H103"/>
-    <mergeCell ref="I102:I103"/>
-    <mergeCell ref="J102:J103"/>
-    <mergeCell ref="K102:K103"/>
-    <mergeCell ref="L102:L103"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5380,24 +5387,24 @@
       <c r="K2" s="28"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="80" t="s">
+      <c r="A3" s="81" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="81" t="s">
+      <c r="B3" s="82" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="81"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="81"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
-      <c r="J3" s="81"/>
-      <c r="K3" s="81"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="82"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="80"/>
+      <c r="A4" s="81"/>
       <c r="B4" s="29">
         <v>1</v>
       </c>
@@ -5680,7 +5687,7 @@
       </c>
       <c r="B12" s="33"/>
       <c r="C12" s="33">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D12" s="33"/>
       <c r="E12" s="33"/>
@@ -5767,7 +5774,7 @@
       </c>
       <c r="B15" s="33"/>
       <c r="C15" s="33">
-        <v>10.5</v>
+        <v>6.5</v>
       </c>
       <c r="D15" s="33"/>
       <c r="E15" s="33"/>
@@ -5820,7 +5827,7 @@
       <c r="B17" s="36"/>
       <c r="C17" s="36">
         <f>(C5-SUM(C6:C9))+((C10/1000)*C12/12)-((C13/1000)*(12-C15)/12)</f>
-        <v>1340</v>
+        <v>1117</v>
       </c>
       <c r="D17" s="36"/>
       <c r="E17" s="36"/>
@@ -5838,7 +5845,7 @@
       <c r="B18" s="36"/>
       <c r="C18" s="36">
         <f>C16*100/C17</f>
-        <v>11.567164179104477</v>
+        <v>13.876454789615041</v>
       </c>
       <c r="D18" s="36"/>
       <c r="E18" s="36"/>
@@ -5891,7 +5898,7 @@
       <c r="B20" s="41"/>
       <c r="C20" s="41">
         <f>C16*C19/C17</f>
-        <v>0.69402985074626866</v>
+        <v>0.83258728737690246</v>
       </c>
       <c r="D20" s="41"/>
       <c r="E20" s="41"/>
@@ -6062,28 +6069,28 @@
       </c>
     </row>
     <row r="3" spans="1:23" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="82" t="s">
+      <c r="A3" s="83" t="s">
         <v>100</v>
       </c>
-      <c r="B3" s="83" t="s">
+      <c r="B3" s="84" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
-      <c r="K3" s="83"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="84"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="84"/>
+      <c r="H3" s="84"/>
+      <c r="I3" s="84"/>
+      <c r="J3" s="84"/>
+      <c r="K3" s="84"/>
       <c r="M3" s="46" t="s">
         <v>72</v>
       </c>
       <c r="N3" s="47"/>
       <c r="O3" s="47">
         <f>O15/O9*100</f>
-        <v>98.00948794444173</v>
+        <v>93.554511219694376</v>
       </c>
       <c r="P3" s="47"/>
       <c r="Q3" s="47"/>
@@ -6095,7 +6102,7 @@
       <c r="W3" s="47"/>
     </row>
     <row r="4" spans="1:23" ht="10.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="82"/>
+      <c r="A4" s="83"/>
       <c r="B4" s="48">
         <v>1</v>
       </c>
@@ -6163,7 +6170,7 @@
       <c r="N5" s="47"/>
       <c r="O5" s="47">
         <f>O17/O11*100</f>
-        <v>117.64705882352942</v>
+        <v>118.27956989247311</v>
       </c>
       <c r="P5" s="47"/>
       <c r="Q5" s="47"/>
@@ -6194,7 +6201,7 @@
       <c r="N6" s="47"/>
       <c r="O6" s="47">
         <f>O18/O12*100</f>
-        <v>118.56319694896986</v>
+        <v>119.20063349170624</v>
       </c>
       <c r="P6" s="47"/>
       <c r="Q6" s="47"/>
@@ -6606,8 +6613,8 @@
       </c>
       <c r="N15" s="47"/>
       <c r="O15" s="47">
-        <f>(C23*C27+C24*C28+C25*C29)/(((C18*105)/100)*1000)</f>
-        <v>2.0160965794768613</v>
+        <f>(C23*C27+C24*C28+C25*C29)/(((C18*110)/100)*1000)</f>
+        <v>1.9244558258642765</v>
       </c>
       <c r="P15" s="47"/>
       <c r="Q15" s="47"/>
@@ -6708,8 +6715,8 @@
       </c>
       <c r="N17" s="47"/>
       <c r="O17" s="47">
-        <f>(((C18*(100+C34))/100)*1000)/((C20*(100-6.5))/100)</f>
-        <v>256.22518946228797</v>
+        <f>(((C18*(100+C34))/100)*1000)/((C20*(100-C36))/100)</f>
+        <v>257.60274424434328</v>
       </c>
       <c r="P17" s="47"/>
       <c r="Q17" s="47"/>
@@ -6759,8 +6766,8 @@
       </c>
       <c r="N18" s="47"/>
       <c r="O18" s="47">
-        <f>((((C18*(100+C34))/100)*1000)-(((C19*(100+C35))/100)*1000))/((C20*(100-6.5))/100)</f>
-        <v>234.58055838063058</v>
+        <f>((((C18*(100+C34))/100)*1000)-(((C19*(100+C35))/100)*1000))/((C20*(100-C36))/100)</f>
+        <v>235.84174417837588</v>
       </c>
       <c r="P18" s="47"/>
       <c r="Q18" s="47"/>
@@ -7456,24 +7463,24 @@
       <c r="K2" s="28"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="80" t="s">
+      <c r="A3" s="81" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="81" t="s">
+      <c r="B3" s="82" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="81"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="81"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
-      <c r="J3" s="81"/>
-      <c r="K3" s="81"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="82"/>
+      <c r="J3" s="82"/>
+      <c r="K3" s="82"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="80"/>
+      <c r="A4" s="81"/>
       <c r="B4" s="29">
         <v>1</v>
       </c>
@@ -7715,24 +7722,24 @@
       <c r="K13" s="28"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="80" t="s">
+      <c r="A14" s="81" t="s">
         <v>49</v>
       </c>
-      <c r="B14" s="81" t="s">
+      <c r="B14" s="82" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="81"/>
-      <c r="D14" s="81"/>
-      <c r="E14" s="81"/>
-      <c r="F14" s="81"/>
-      <c r="G14" s="81"/>
-      <c r="H14" s="81"/>
-      <c r="I14" s="81"/>
-      <c r="J14" s="81"/>
-      <c r="K14" s="81"/>
+      <c r="C14" s="82"/>
+      <c r="D14" s="82"/>
+      <c r="E14" s="82"/>
+      <c r="F14" s="82"/>
+      <c r="G14" s="82"/>
+      <c r="H14" s="82"/>
+      <c r="I14" s="82"/>
+      <c r="J14" s="82"/>
+      <c r="K14" s="82"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="80"/>
+      <c r="A15" s="81"/>
       <c r="B15" s="29">
         <v>1</v>
       </c>
